--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06DDE32-3A60-4566-B1A1-F5D1EA0633F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="13170" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="4" r:id="rId1"/>
@@ -17,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sprint Backlog'!$A$2:$J$181</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,13 +34,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
-    <author>tc={148E080D-CE22-4CE0-8311-B67C30FEF121}</author>
   </authors>
   <commentList>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -58,12 +56,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="1" shapeId="0" xr:uid="{148E080D-CE22-4CE0-8311-B67C30FEF121}">
+    <comment ref="E6" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Get client verification</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -71,12 +78,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="H2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -102,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -126,7 +133,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+    <comment ref="C12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -150,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
+    <comment ref="C15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -174,7 +181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
+    <comment ref="C18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -198,7 +205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
+    <comment ref="C26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -223,7 +230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
+    <comment ref="C29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -247,7 +254,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
+    <comment ref="C31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -271,7 +278,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
+    <comment ref="C38" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -295,7 +302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C46" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
+    <comment ref="C46" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -319,7 +326,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
+    <comment ref="C50" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -343,7 +350,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
+    <comment ref="C59" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -367,7 +374,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000D000000}">
+    <comment ref="C65" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -391,7 +398,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C77" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
+    <comment ref="C77" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -415,7 +422,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C88" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000F000000}">
+    <comment ref="C88" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -439,7 +446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C101" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000010000000}">
+    <comment ref="C101" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -463,7 +470,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C110" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000011000000}">
+    <comment ref="C110" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -487,7 +494,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C116" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000012000000}">
+    <comment ref="C116" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -511,7 +518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C127" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000013000000}">
+    <comment ref="C127" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -535,7 +542,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C137" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000014000000}">
+    <comment ref="C137" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -559,7 +566,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C142" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000015000000}">
+    <comment ref="C142" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -583,7 +590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000016000000}">
+    <comment ref="C157" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -607,7 +614,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000017000000}">
+    <comment ref="C161" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -631,7 +638,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C168" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000018000000}">
+    <comment ref="C168" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -655,7 +662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C174" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000019000000}">
+    <comment ref="C174" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -684,12 +691,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="H2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -720,14 +727,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -2593,7 +2600,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="11">
     <font>
       <sz val="11"/>
@@ -2889,16 +2896,19 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2908,17 +2918,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4105,9 +4112,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4145,9 +4152,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4182,7 +4189,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4217,7 +4224,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4398,25 +4405,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="35.6640625" customWidth="1"/>
-    <col min="5" max="5" width="51.109375" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" customWidth="1"/>
+    <col min="5" max="5" width="51.140625" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="10"/>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
     </row>
@@ -4440,7 +4447,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="100.8">
+    <row r="3" spans="1:6" ht="105">
       <c r="A3" s="16">
         <v>1</v>
       </c>
@@ -4491,7 +4498,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="86.4">
+    <row r="6" spans="1:6" ht="90">
       <c r="A6" s="15">
         <v>4</v>
       </c>
@@ -4542,32 +4549,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J181"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1">
       <c r="A2" s="10" t="s">
@@ -4602,632 +4609,632 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="50">
+      <c r="A3" s="51">
         <v>1</v>
       </c>
-      <c r="B3" s="51">
+      <c r="B3" s="45">
         <v>1</v>
       </c>
-      <c r="C3" s="51">
+      <c r="C3" s="45">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="48" t="s">
+      <c r="E3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="48" cm="1">
+      <c r="F3" s="49" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="50"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
       <c r="D4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="50"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="50"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
+      <c r="A6" s="51"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="50"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
+      <c r="A7" s="51"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
       <c r="D7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="50"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
       <c r="D8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="50"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
       <c r="D9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="50"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
       <c r="D10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="50"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
+      <c r="A11" s="51"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
       <c r="D11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="50"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51">
+      <c r="A12" s="51"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45">
         <v>1.2</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="48" cm="1">
+      <c r="F12" s="49" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="50"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="51"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
       <c r="D13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="50"/>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
+      <c r="A14" s="51"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
       <c r="D14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="50"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="51">
+      <c r="A15" s="51"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45">
         <v>1.3</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="48" t="s">
+      <c r="E15" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="48"/>
+      <c r="F15" s="49"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="50"/>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="45"/>
       <c r="D16" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="50"/>
-      <c r="B17" s="51"/>
-      <c r="C17" s="51"/>
+      <c r="A17" s="51"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
       <c r="D17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="50"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="51">
+      <c r="A18" s="51"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45">
         <v>1.4</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="48" t="s">
+      <c r="E18" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="48"/>
+      <c r="F18" s="49"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="50"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="51"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="45"/>
       <c r="D19" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="50"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
+      <c r="A20" s="51"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
       <c r="D20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="50"/>
-      <c r="B21" s="51"/>
-      <c r="C21" s="51"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
       <c r="D21" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="50"/>
-      <c r="B22" s="51"/>
-      <c r="C22" s="51"/>
+      <c r="A22" s="51"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
       <c r="D22" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="50"/>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
+      <c r="A23" s="51"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
       <c r="D23" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="50"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="51"/>
+      <c r="A24" s="51"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
       <c r="D24" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="50"/>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
+      <c r="A25" s="51"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
       <c r="D25" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="50"/>
+      <c r="A26" s="51"/>
       <c r="B26" s="52">
         <v>2</v>
       </c>
-      <c r="C26" s="51">
+      <c r="C26" s="45">
         <v>2.1</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E26" s="49" t="s">
+      <c r="E26" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="48"/>
+      <c r="F26" s="49"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="50"/>
+      <c r="A27" s="51"/>
       <c r="B27" s="52"/>
-      <c r="C27" s="51"/>
+      <c r="C27" s="45"/>
       <c r="D27" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="49"/>
-      <c r="F27" s="48"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="49"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="50"/>
+      <c r="A28" s="51"/>
       <c r="B28" s="52"/>
-      <c r="C28" s="51"/>
+      <c r="C28" s="45"/>
       <c r="D28" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E28" s="49"/>
-      <c r="F28" s="48"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="49"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="50"/>
+      <c r="A29" s="51"/>
       <c r="B29" s="52"/>
-      <c r="C29" s="53">
+      <c r="C29" s="47">
         <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="48" t="s">
+      <c r="E29" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="48"/>
+      <c r="F29" s="49"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="50"/>
+      <c r="A30" s="51"/>
       <c r="B30" s="52"/>
-      <c r="C30" s="53"/>
+      <c r="C30" s="47"/>
       <c r="D30" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="49"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="50"/>
+      <c r="A31" s="51"/>
       <c r="B31" s="52"/>
-      <c r="C31" s="51">
+      <c r="C31" s="45">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="48" t="s">
+      <c r="E31" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48" t="s">
+      <c r="F31" s="49"/>
+      <c r="G31" s="49" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="50"/>
+      <c r="A32" s="51"/>
       <c r="B32" s="52"/>
-      <c r="C32" s="51"/>
+      <c r="C32" s="45"/>
       <c r="D32" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="49"/>
+      <c r="G32" s="49"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="50"/>
+      <c r="A33" s="51"/>
       <c r="B33" s="52"/>
-      <c r="C33" s="51"/>
+      <c r="C33" s="45"/>
       <c r="D33" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="50"/>
+      <c r="A34" s="51"/>
       <c r="B34" s="52"/>
-      <c r="C34" s="51"/>
+      <c r="C34" s="45"/>
       <c r="D34" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="50"/>
+      <c r="A35" s="51"/>
       <c r="B35" s="52"/>
-      <c r="C35" s="51"/>
+      <c r="C35" s="45"/>
       <c r="D35" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="50"/>
+      <c r="A36" s="51"/>
       <c r="B36" s="52"/>
-      <c r="C36" s="51"/>
+      <c r="C36" s="45"/>
       <c r="D36" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="49"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="50"/>
+      <c r="A37" s="51"/>
       <c r="B37" s="52"/>
-      <c r="C37" s="51"/>
+      <c r="C37" s="45"/>
       <c r="D37" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="50"/>
+      <c r="A38" s="51"/>
       <c r="B38" s="52"/>
-      <c r="C38" s="51">
+      <c r="C38" s="45">
         <v>2.4</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E38" s="48" t="s">
+      <c r="E38" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="48"/>
+      <c r="F38" s="49"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="50"/>
+      <c r="A39" s="51"/>
       <c r="B39" s="52"/>
-      <c r="C39" s="51"/>
+      <c r="C39" s="45"/>
       <c r="D39" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="49"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="50"/>
+      <c r="A40" s="51"/>
       <c r="B40" s="52"/>
-      <c r="C40" s="51"/>
+      <c r="C40" s="45"/>
       <c r="D40" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="49"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="50"/>
+      <c r="A41" s="51"/>
       <c r="B41" s="52"/>
-      <c r="C41" s="51"/>
+      <c r="C41" s="45"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="50"/>
+      <c r="A42" s="51"/>
       <c r="B42" s="52"/>
-      <c r="C42" s="51"/>
+      <c r="C42" s="45"/>
       <c r="D42" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="50"/>
+      <c r="A43" s="51"/>
       <c r="B43" s="52"/>
-      <c r="C43" s="51"/>
+      <c r="C43" s="45"/>
       <c r="D43" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="50"/>
+      <c r="A44" s="51"/>
       <c r="B44" s="52"/>
-      <c r="C44" s="51"/>
+      <c r="C44" s="45"/>
       <c r="D44" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="50"/>
+      <c r="A45" s="51"/>
       <c r="B45" s="52"/>
-      <c r="C45" s="51"/>
+      <c r="C45" s="45"/>
       <c r="D45" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="50"/>
+      <c r="A46" s="51"/>
       <c r="B46" s="52"/>
-      <c r="C46" s="51">
+      <c r="C46" s="45">
         <v>2.5</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="E46" s="49" t="s">
+      <c r="E46" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="48"/>
+      <c r="F46" s="49"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="50"/>
+      <c r="A47" s="51"/>
       <c r="B47" s="52"/>
-      <c r="C47" s="51"/>
+      <c r="C47" s="45"/>
       <c r="D47" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E47" s="49"/>
-      <c r="F47" s="48"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="49"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="50"/>
+      <c r="A48" s="51"/>
       <c r="B48" s="52"/>
-      <c r="C48" s="51"/>
+      <c r="C48" s="45"/>
       <c r="D48" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E48" s="49"/>
-      <c r="F48" s="48"/>
+      <c r="E48" s="50"/>
+      <c r="F48" s="49"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="50"/>
+      <c r="A49" s="51"/>
       <c r="B49" s="52"/>
-      <c r="C49" s="51"/>
+      <c r="C49" s="45"/>
       <c r="D49" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E49" s="49"/>
-      <c r="F49" s="48"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="49"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="50"/>
+      <c r="A50" s="51"/>
       <c r="B50" s="52"/>
-      <c r="C50" s="51">
+      <c r="C50" s="45">
         <v>2.7</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E50" s="48" t="s">
+      <c r="E50" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="F50" s="48"/>
+      <c r="F50" s="49"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="50"/>
+      <c r="A51" s="51"/>
       <c r="B51" s="52"/>
-      <c r="C51" s="51"/>
+      <c r="C51" s="45"/>
       <c r="D51" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="50"/>
+      <c r="A52" s="51"/>
       <c r="B52" s="52"/>
-      <c r="C52" s="51"/>
+      <c r="C52" s="45"/>
       <c r="D52" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E52" s="48"/>
-      <c r="F52" s="48"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="49"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="50"/>
+      <c r="A53" s="51"/>
       <c r="B53" s="52"/>
-      <c r="C53" s="51"/>
+      <c r="C53" s="45"/>
       <c r="D53" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E53" s="48"/>
-      <c r="F53" s="48"/>
+      <c r="E53" s="49"/>
+      <c r="F53" s="49"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="50"/>
+      <c r="A54" s="51"/>
       <c r="B54" s="52"/>
-      <c r="C54" s="51"/>
+      <c r="C54" s="45"/>
       <c r="D54" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E54" s="48"/>
-      <c r="F54" s="48"/>
+      <c r="E54" s="49"/>
+      <c r="F54" s="49"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="50"/>
+      <c r="A55" s="51"/>
       <c r="B55" s="52"/>
-      <c r="C55" s="51"/>
+      <c r="C55" s="45"/>
       <c r="D55" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="49"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="50"/>
+      <c r="A56" s="51"/>
       <c r="B56" s="52"/>
-      <c r="C56" s="51"/>
+      <c r="C56" s="45"/>
       <c r="D56" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
+      <c r="E56" s="49"/>
+      <c r="F56" s="49"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="50"/>
+      <c r="A57" s="51"/>
       <c r="B57" s="52"/>
-      <c r="C57" s="51"/>
+      <c r="C57" s="45"/>
       <c r="D57" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E57" s="48"/>
-      <c r="F57" s="48"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="50"/>
+      <c r="A58" s="51"/>
       <c r="B58" s="52"/>
-      <c r="C58" s="51"/>
+      <c r="C58" s="45"/>
       <c r="D58" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E58" s="48"/>
-      <c r="F58" s="48"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
-      <c r="B59" s="51">
+      <c r="B59" s="45">
         <v>3</v>
       </c>
-      <c r="C59" s="51">
+      <c r="C59" s="45">
         <v>3.1</v>
       </c>
       <c r="D59" s="7" t="s">
@@ -5236,48 +5243,48 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="19"/>
-      <c r="B60" s="51"/>
-      <c r="C60" s="51"/>
+      <c r="B60" s="45"/>
+      <c r="C60" s="45"/>
       <c r="D60" s="7" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="19"/>
-      <c r="B61" s="51"/>
-      <c r="C61" s="51"/>
+      <c r="B61" s="45"/>
+      <c r="C61" s="45"/>
       <c r="D61" s="7" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="19"/>
-      <c r="B62" s="51"/>
-      <c r="C62" s="51"/>
+      <c r="B62" s="45"/>
+      <c r="C62" s="45"/>
       <c r="D62" s="7" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="19"/>
-      <c r="B63" s="51"/>
-      <c r="C63" s="51"/>
+      <c r="B63" s="45"/>
+      <c r="C63" s="45"/>
       <c r="D63" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="19"/>
-      <c r="B64" s="51"/>
-      <c r="C64" s="51"/>
+      <c r="B64" s="45"/>
+      <c r="C64" s="45"/>
       <c r="D64" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="19"/>
-      <c r="B65" s="51"/>
-      <c r="C65" s="51">
+      <c r="B65" s="45"/>
+      <c r="C65" s="45">
         <v>3.2</v>
       </c>
       <c r="D65" s="7" t="s">
@@ -5286,96 +5293,96 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="19"/>
-      <c r="B66" s="51"/>
-      <c r="C66" s="51"/>
+      <c r="B66" s="45"/>
+      <c r="C66" s="45"/>
       <c r="D66" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="19"/>
-      <c r="B67" s="51"/>
-      <c r="C67" s="51"/>
+      <c r="B67" s="45"/>
+      <c r="C67" s="45"/>
       <c r="D67" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="19"/>
-      <c r="B68" s="51"/>
-      <c r="C68" s="51"/>
+      <c r="B68" s="45"/>
+      <c r="C68" s="45"/>
       <c r="D68" s="7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="19"/>
-      <c r="B69" s="51"/>
-      <c r="C69" s="51"/>
+      <c r="B69" s="45"/>
+      <c r="C69" s="45"/>
       <c r="D69" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="19"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
+      <c r="B70" s="45"/>
+      <c r="C70" s="45"/>
       <c r="D70" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="19"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="45"/>
       <c r="D71" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="19"/>
-      <c r="B72" s="51"/>
-      <c r="C72" s="51"/>
+      <c r="B72" s="45"/>
+      <c r="C72" s="45"/>
       <c r="D72" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="19"/>
-      <c r="B73" s="51"/>
-      <c r="C73" s="51"/>
+      <c r="B73" s="45"/>
+      <c r="C73" s="45"/>
       <c r="D73" s="7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="19"/>
-      <c r="B74" s="51"/>
-      <c r="C74" s="51"/>
+      <c r="B74" s="45"/>
+      <c r="C74" s="45"/>
       <c r="D74" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="19"/>
-      <c r="B75" s="51"/>
-      <c r="C75" s="51"/>
+      <c r="B75" s="45"/>
+      <c r="C75" s="45"/>
       <c r="D75" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="19"/>
-      <c r="B76" s="51"/>
-      <c r="C76" s="51"/>
+      <c r="B76" s="45"/>
+      <c r="C76" s="45"/>
       <c r="D76" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="19"/>
-      <c r="B77" s="51"/>
-      <c r="C77" s="51">
+      <c r="B77" s="45"/>
+      <c r="C77" s="45">
         <v>3.3</v>
       </c>
       <c r="D77" s="7" t="s">
@@ -5384,88 +5391,88 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="19"/>
-      <c r="B78" s="51"/>
-      <c r="C78" s="51"/>
+      <c r="B78" s="45"/>
+      <c r="C78" s="45"/>
       <c r="D78" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="19"/>
-      <c r="B79" s="51"/>
-      <c r="C79" s="51"/>
+      <c r="B79" s="45"/>
+      <c r="C79" s="45"/>
       <c r="D79" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="19"/>
-      <c r="B80" s="51"/>
-      <c r="C80" s="51"/>
+      <c r="B80" s="45"/>
+      <c r="C80" s="45"/>
       <c r="D80" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="19"/>
-      <c r="B81" s="51"/>
-      <c r="C81" s="51"/>
+      <c r="B81" s="45"/>
+      <c r="C81" s="45"/>
       <c r="D81" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="19"/>
-      <c r="B82" s="51"/>
-      <c r="C82" s="51"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="45"/>
       <c r="D82" s="7" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="19"/>
-      <c r="B83" s="51"/>
-      <c r="C83" s="51"/>
+      <c r="B83" s="45"/>
+      <c r="C83" s="45"/>
       <c r="D83" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="19"/>
-      <c r="B84" s="51"/>
-      <c r="C84" s="51"/>
+      <c r="B84" s="45"/>
+      <c r="C84" s="45"/>
       <c r="D84" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="19"/>
-      <c r="B85" s="51"/>
-      <c r="C85" s="51"/>
+      <c r="B85" s="45"/>
+      <c r="C85" s="45"/>
       <c r="D85" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="19"/>
-      <c r="B86" s="51"/>
-      <c r="C86" s="51"/>
+      <c r="B86" s="45"/>
+      <c r="C86" s="45"/>
       <c r="D86" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="19"/>
-      <c r="B87" s="51"/>
-      <c r="C87" s="51"/>
+      <c r="B87" s="45"/>
+      <c r="C87" s="45"/>
       <c r="D87" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="19"/>
-      <c r="B88" s="51"/>
-      <c r="C88" s="51">
+      <c r="B88" s="45"/>
+      <c r="C88" s="45">
         <v>3.4</v>
       </c>
       <c r="D88" s="15" t="s">
@@ -5474,104 +5481,104 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="19"/>
-      <c r="B89" s="51"/>
-      <c r="C89" s="51"/>
+      <c r="B89" s="45"/>
+      <c r="C89" s="45"/>
       <c r="D89" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="19"/>
-      <c r="B90" s="51"/>
-      <c r="C90" s="51"/>
+      <c r="B90" s="45"/>
+      <c r="C90" s="45"/>
       <c r="D90" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="19"/>
-      <c r="B91" s="51"/>
-      <c r="C91" s="51"/>
+      <c r="B91" s="45"/>
+      <c r="C91" s="45"/>
       <c r="D91" s="7" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="19"/>
-      <c r="B92" s="51"/>
-      <c r="C92" s="51"/>
+      <c r="B92" s="45"/>
+      <c r="C92" s="45"/>
       <c r="D92" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="19"/>
-      <c r="B93" s="51"/>
-      <c r="C93" s="51"/>
+      <c r="B93" s="45"/>
+      <c r="C93" s="45"/>
       <c r="D93" s="7" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="19"/>
-      <c r="B94" s="51"/>
-      <c r="C94" s="51"/>
+      <c r="B94" s="45"/>
+      <c r="C94" s="45"/>
       <c r="D94" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="19"/>
-      <c r="B95" s="51"/>
-      <c r="C95" s="51"/>
+      <c r="B95" s="45"/>
+      <c r="C95" s="45"/>
       <c r="D95" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="19"/>
-      <c r="B96" s="51"/>
-      <c r="C96" s="51"/>
+      <c r="B96" s="45"/>
+      <c r="C96" s="45"/>
       <c r="D96" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="19"/>
-      <c r="B97" s="51"/>
-      <c r="C97" s="51"/>
+      <c r="B97" s="45"/>
+      <c r="C97" s="45"/>
       <c r="D97" s="7" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="19"/>
-      <c r="B98" s="51"/>
-      <c r="C98" s="51"/>
+      <c r="B98" s="45"/>
+      <c r="C98" s="45"/>
       <c r="D98" s="7" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="19"/>
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
+      <c r="B99" s="45"/>
+      <c r="C99" s="45"/>
       <c r="D99" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="19"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
+      <c r="B100" s="45"/>
+      <c r="C100" s="45"/>
       <c r="D100" s="7" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="19"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51">
+      <c r="B101" s="45"/>
+      <c r="C101" s="45">
         <v>3.5</v>
       </c>
       <c r="D101" s="11" t="s">
@@ -5580,72 +5587,72 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="19"/>
-      <c r="B102" s="51"/>
-      <c r="C102" s="51"/>
+      <c r="B102" s="45"/>
+      <c r="C102" s="45"/>
       <c r="D102" s="7" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="19"/>
-      <c r="B103" s="51"/>
-      <c r="C103" s="51"/>
+      <c r="B103" s="45"/>
+      <c r="C103" s="45"/>
       <c r="D103" s="7" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="19"/>
-      <c r="B104" s="51"/>
-      <c r="C104" s="51"/>
+      <c r="B104" s="45"/>
+      <c r="C104" s="45"/>
       <c r="D104" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="19"/>
-      <c r="B105" s="51"/>
-      <c r="C105" s="51"/>
+      <c r="B105" s="45"/>
+      <c r="C105" s="45"/>
       <c r="D105" s="7" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="19"/>
-      <c r="B106" s="51"/>
-      <c r="C106" s="51"/>
+      <c r="B106" s="45"/>
+      <c r="C106" s="45"/>
       <c r="D106" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="19"/>
-      <c r="B107" s="51"/>
-      <c r="C107" s="51"/>
+      <c r="B107" s="45"/>
+      <c r="C107" s="45"/>
       <c r="D107" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="19"/>
-      <c r="B108" s="51"/>
-      <c r="C108" s="51"/>
+      <c r="B108" s="45"/>
+      <c r="C108" s="45"/>
       <c r="D108" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="19"/>
-      <c r="B109" s="51"/>
-      <c r="C109" s="51"/>
+      <c r="B109" s="45"/>
+      <c r="C109" s="45"/>
       <c r="D109" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="19"/>
-      <c r="B110" s="51"/>
-      <c r="C110" s="51">
+      <c r="B110" s="45"/>
+      <c r="C110" s="45">
         <v>3.6</v>
       </c>
       <c r="D110" s="7" t="s">
@@ -5654,48 +5661,48 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19"/>
-      <c r="B111" s="51"/>
-      <c r="C111" s="51"/>
+      <c r="B111" s="45"/>
+      <c r="C111" s="45"/>
       <c r="D111" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19"/>
-      <c r="B112" s="51"/>
-      <c r="C112" s="51"/>
+      <c r="B112" s="45"/>
+      <c r="C112" s="45"/>
       <c r="D112" s="7" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="19"/>
-      <c r="B113" s="51"/>
-      <c r="C113" s="51"/>
+      <c r="B113" s="45"/>
+      <c r="C113" s="45"/>
       <c r="D113" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="19"/>
-      <c r="B114" s="51"/>
-      <c r="C114" s="51"/>
+      <c r="B114" s="45"/>
+      <c r="C114" s="45"/>
       <c r="D114" s="7" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="19"/>
-      <c r="B115" s="51"/>
-      <c r="C115" s="51"/>
+      <c r="B115" s="45"/>
+      <c r="C115" s="45"/>
       <c r="D115" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="19"/>
-      <c r="B116" s="51"/>
-      <c r="C116" s="51">
+      <c r="B116" s="45"/>
+      <c r="C116" s="45">
         <v>3.7</v>
       </c>
       <c r="D116" s="7" t="s">
@@ -5704,88 +5711,88 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="19"/>
-      <c r="B117" s="51"/>
-      <c r="C117" s="51"/>
+      <c r="B117" s="45"/>
+      <c r="C117" s="45"/>
       <c r="D117" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="19"/>
-      <c r="B118" s="51"/>
-      <c r="C118" s="51"/>
+      <c r="B118" s="45"/>
+      <c r="C118" s="45"/>
       <c r="D118" s="7" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="19"/>
-      <c r="B119" s="51"/>
-      <c r="C119" s="51"/>
+      <c r="B119" s="45"/>
+      <c r="C119" s="45"/>
       <c r="D119" s="7" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="19"/>
-      <c r="B120" s="51"/>
-      <c r="C120" s="51"/>
+      <c r="B120" s="45"/>
+      <c r="C120" s="45"/>
       <c r="D120" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="19"/>
-      <c r="B121" s="51"/>
-      <c r="C121" s="51"/>
+      <c r="B121" s="45"/>
+      <c r="C121" s="45"/>
       <c r="D121" s="7" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="19"/>
-      <c r="B122" s="51"/>
-      <c r="C122" s="51"/>
+      <c r="B122" s="45"/>
+      <c r="C122" s="45"/>
       <c r="D122" s="7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="19"/>
-      <c r="B123" s="51"/>
-      <c r="C123" s="51"/>
+      <c r="B123" s="45"/>
+      <c r="C123" s="45"/>
       <c r="D123" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="19"/>
-      <c r="B124" s="51"/>
-      <c r="C124" s="51"/>
+      <c r="B124" s="45"/>
+      <c r="C124" s="45"/>
       <c r="D124" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="19"/>
-      <c r="B125" s="51"/>
-      <c r="C125" s="51"/>
+      <c r="B125" s="45"/>
+      <c r="C125" s="45"/>
       <c r="D125" s="7" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="19"/>
-      <c r="B126" s="51"/>
-      <c r="C126" s="51"/>
+      <c r="B126" s="45"/>
+      <c r="C126" s="45"/>
       <c r="D126" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="19"/>
-      <c r="B127" s="51"/>
-      <c r="C127" s="51">
+      <c r="B127" s="45"/>
+      <c r="C127" s="45">
         <v>3.8</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -5794,80 +5801,80 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="19"/>
-      <c r="B128" s="51"/>
-      <c r="C128" s="51"/>
+      <c r="B128" s="45"/>
+      <c r="C128" s="45"/>
       <c r="D128" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="19"/>
-      <c r="B129" s="51"/>
-      <c r="C129" s="51"/>
+      <c r="B129" s="45"/>
+      <c r="C129" s="45"/>
       <c r="D129" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="19"/>
-      <c r="B130" s="51"/>
-      <c r="C130" s="51"/>
+      <c r="B130" s="45"/>
+      <c r="C130" s="45"/>
       <c r="D130" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="19"/>
-      <c r="B131" s="51"/>
-      <c r="C131" s="51"/>
+      <c r="B131" s="45"/>
+      <c r="C131" s="45"/>
       <c r="D131" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="19"/>
-      <c r="B132" s="51"/>
-      <c r="C132" s="51"/>
+      <c r="B132" s="45"/>
+      <c r="C132" s="45"/>
       <c r="D132" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="19"/>
-      <c r="B133" s="51"/>
-      <c r="C133" s="51"/>
+      <c r="B133" s="45"/>
+      <c r="C133" s="45"/>
       <c r="D133" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="19"/>
-      <c r="B134" s="51"/>
-      <c r="C134" s="51"/>
+      <c r="B134" s="45"/>
+      <c r="C134" s="45"/>
       <c r="D134" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="19"/>
-      <c r="B135" s="51"/>
-      <c r="C135" s="51"/>
+      <c r="B135" s="45"/>
+      <c r="C135" s="45"/>
       <c r="D135" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="19"/>
-      <c r="B136" s="51"/>
-      <c r="C136" s="51"/>
+      <c r="B136" s="45"/>
+      <c r="C136" s="45"/>
       <c r="D136" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="19"/>
-      <c r="B137" s="51"/>
-      <c r="C137" s="51">
+      <c r="B137" s="45"/>
+      <c r="C137" s="45">
         <v>3.9</v>
       </c>
       <c r="D137" s="7" t="s">
@@ -5876,40 +5883,40 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="19"/>
-      <c r="B138" s="51"/>
-      <c r="C138" s="51"/>
+      <c r="B138" s="45"/>
+      <c r="C138" s="45"/>
       <c r="D138" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="19"/>
-      <c r="B139" s="51"/>
-      <c r="C139" s="51"/>
+      <c r="B139" s="45"/>
+      <c r="C139" s="45"/>
       <c r="D139" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="19"/>
-      <c r="B140" s="51"/>
-      <c r="C140" s="51"/>
+      <c r="B140" s="45"/>
+      <c r="C140" s="45"/>
       <c r="D140" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="19"/>
-      <c r="B141" s="51"/>
-      <c r="C141" s="51"/>
+      <c r="B141" s="45"/>
+      <c r="C141" s="45"/>
       <c r="D141" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
-      <c r="B142" s="51"/>
-      <c r="C142" s="54">
+      <c r="B142" s="45"/>
+      <c r="C142" s="46">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -5918,122 +5925,122 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
-      <c r="B143" s="51"/>
-      <c r="C143" s="54"/>
+      <c r="B143" s="45"/>
+      <c r="C143" s="46"/>
       <c r="D143" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
-      <c r="B144" s="51"/>
-      <c r="C144" s="54"/>
+      <c r="B144" s="45"/>
+      <c r="C144" s="46"/>
       <c r="D144" s="7" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
-      <c r="B145" s="51"/>
-      <c r="C145" s="54"/>
+      <c r="B145" s="45"/>
+      <c r="C145" s="46"/>
       <c r="D145" s="7" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
-      <c r="B146" s="51"/>
-      <c r="C146" s="54"/>
+      <c r="B146" s="45"/>
+      <c r="C146" s="46"/>
       <c r="D146" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
-      <c r="B147" s="51"/>
-      <c r="C147" s="54"/>
+      <c r="B147" s="45"/>
+      <c r="C147" s="46"/>
       <c r="D147" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
-      <c r="B148" s="51"/>
-      <c r="C148" s="54"/>
+      <c r="B148" s="45"/>
+      <c r="C148" s="46"/>
       <c r="D148" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
-      <c r="B149" s="51"/>
-      <c r="C149" s="54"/>
+      <c r="B149" s="45"/>
+      <c r="C149" s="46"/>
       <c r="D149" s="7" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
-      <c r="B150" s="51"/>
-      <c r="C150" s="54"/>
+      <c r="B150" s="45"/>
+      <c r="C150" s="46"/>
       <c r="D150" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
-      <c r="B151" s="51"/>
-      <c r="C151" s="54"/>
+      <c r="B151" s="45"/>
+      <c r="C151" s="46"/>
       <c r="D151" s="7" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
-      <c r="B152" s="51"/>
-      <c r="C152" s="54"/>
+      <c r="B152" s="45"/>
+      <c r="C152" s="46"/>
       <c r="D152" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
-      <c r="B153" s="51"/>
-      <c r="C153" s="54"/>
+      <c r="B153" s="45"/>
+      <c r="C153" s="46"/>
       <c r="D153" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
-      <c r="B154" s="51"/>
-      <c r="C154" s="54"/>
+      <c r="B154" s="45"/>
+      <c r="C154" s="46"/>
       <c r="D154" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
-      <c r="B155" s="51"/>
-      <c r="C155" s="54"/>
+      <c r="B155" s="45"/>
+      <c r="C155" s="46"/>
       <c r="D155" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
-      <c r="B156" s="51"/>
-      <c r="C156" s="54"/>
+      <c r="B156" s="45"/>
+      <c r="C156" s="46"/>
       <c r="D156" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="20"/>
-      <c r="B157" s="51">
+      <c r="B157" s="45">
         <v>4</v>
       </c>
-      <c r="C157" s="51">
+      <c r="C157" s="45">
         <v>4.0999999999999996</v>
       </c>
       <c r="D157" s="7" t="s">
@@ -6042,32 +6049,32 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="19"/>
-      <c r="B158" s="51"/>
-      <c r="C158" s="51"/>
+      <c r="B158" s="45"/>
+      <c r="C158" s="45"/>
       <c r="D158" s="7" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="19"/>
-      <c r="B159" s="51"/>
-      <c r="C159" s="51"/>
+      <c r="B159" s="45"/>
+      <c r="C159" s="45"/>
       <c r="D159" s="7" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="19"/>
-      <c r="B160" s="51"/>
-      <c r="C160" s="51"/>
+      <c r="B160" s="45"/>
+      <c r="C160" s="45"/>
       <c r="D160" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="19"/>
-      <c r="B161" s="51"/>
-      <c r="C161" s="51">
+      <c r="B161" s="45"/>
+      <c r="C161" s="45">
         <v>4.2</v>
       </c>
       <c r="D161" s="7" t="s">
@@ -6076,56 +6083,56 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="19"/>
-      <c r="B162" s="51"/>
-      <c r="C162" s="51"/>
+      <c r="B162" s="45"/>
+      <c r="C162" s="45"/>
       <c r="D162" s="7" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="19"/>
-      <c r="B163" s="51"/>
-      <c r="C163" s="51"/>
+      <c r="B163" s="45"/>
+      <c r="C163" s="45"/>
       <c r="D163" s="7" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="19"/>
-      <c r="B164" s="51"/>
-      <c r="C164" s="51"/>
+      <c r="B164" s="45"/>
+      <c r="C164" s="45"/>
       <c r="D164" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="19"/>
-      <c r="B165" s="51"/>
-      <c r="C165" s="51"/>
+      <c r="B165" s="45"/>
+      <c r="C165" s="45"/>
       <c r="D165" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="19"/>
-      <c r="B166" s="51"/>
-      <c r="C166" s="51"/>
+      <c r="B166" s="45"/>
+      <c r="C166" s="45"/>
       <c r="D166" s="7" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="19"/>
-      <c r="B167" s="51"/>
-      <c r="C167" s="51"/>
+      <c r="B167" s="45"/>
+      <c r="C167" s="45"/>
       <c r="D167" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="19"/>
-      <c r="B168" s="51"/>
-      <c r="C168" s="51">
+      <c r="B168" s="45"/>
+      <c r="C168" s="45">
         <v>4.3</v>
       </c>
       <c r="D168" s="7" t="s">
@@ -6134,48 +6141,48 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="19"/>
-      <c r="B169" s="51"/>
-      <c r="C169" s="51"/>
+      <c r="B169" s="45"/>
+      <c r="C169" s="45"/>
       <c r="D169" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="19"/>
-      <c r="B170" s="51"/>
-      <c r="C170" s="51"/>
+      <c r="B170" s="45"/>
+      <c r="C170" s="45"/>
       <c r="D170" s="7" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="19"/>
-      <c r="B171" s="51"/>
-      <c r="C171" s="51"/>
+      <c r="B171" s="45"/>
+      <c r="C171" s="45"/>
       <c r="D171" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="19"/>
-      <c r="B172" s="51"/>
-      <c r="C172" s="51"/>
+      <c r="B172" s="45"/>
+      <c r="C172" s="45"/>
       <c r="D172" s="7" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="19"/>
-      <c r="B173" s="51"/>
-      <c r="C173" s="51"/>
+      <c r="B173" s="45"/>
+      <c r="C173" s="45"/>
       <c r="D173" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="19"/>
-      <c r="B174" s="51"/>
-      <c r="C174" s="51">
+      <c r="B174" s="45"/>
+      <c r="C174" s="45">
         <v>4.4000000000000004</v>
       </c>
       <c r="D174" s="7" t="s">
@@ -6184,63 +6191,98 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="19"/>
-      <c r="B175" s="51"/>
-      <c r="C175" s="51"/>
+      <c r="B175" s="45"/>
+      <c r="C175" s="45"/>
       <c r="D175" s="7" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="19"/>
-      <c r="B176" s="51"/>
-      <c r="C176" s="51"/>
+      <c r="B176" s="45"/>
+      <c r="C176" s="45"/>
       <c r="D176" s="7" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="19"/>
-      <c r="B177" s="51"/>
-      <c r="C177" s="51"/>
+      <c r="B177" s="45"/>
+      <c r="C177" s="45"/>
       <c r="D177" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="19"/>
-      <c r="B178" s="51"/>
-      <c r="C178" s="51"/>
+      <c r="B178" s="45"/>
+      <c r="C178" s="45"/>
       <c r="D178" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="19"/>
-      <c r="B179" s="51"/>
-      <c r="C179" s="51"/>
+      <c r="B179" s="45"/>
+      <c r="C179" s="45"/>
       <c r="D179" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="19"/>
-      <c r="B180" s="51"/>
-      <c r="C180" s="51"/>
+      <c r="B180" s="45"/>
+      <c r="C180" s="45"/>
       <c r="D180" s="7" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="19"/>
-      <c r="B181" s="51"/>
-      <c r="C181" s="51"/>
+      <c r="B181" s="45"/>
+      <c r="C181" s="45"/>
       <c r="D181" s="7" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J181" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A2:J181"/>
   <mergeCells count="51">
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -6257,41 +6299,6 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6300,32 +6307,32 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
     </row>
     <row r="2" spans="1:12" s="4" customFormat="1">
       <c r="A2" s="32" t="s">
@@ -6363,11 +6370,11 @@
       </c>
       <c r="L2" s="40"/>
     </row>
-    <row r="3" spans="1:12" ht="129.6">
-      <c r="A3" s="44">
+    <row r="3" spans="1:12" ht="135">
+      <c r="A3" s="53">
         <v>1</v>
       </c>
-      <c r="B3" s="44">
+      <c r="B3" s="53">
         <v>1</v>
       </c>
       <c r="C3" s="15">
@@ -6390,9 +6397,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="57.6">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44"/>
+    <row r="4" spans="1:12" ht="60">
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
       <c r="C4" s="15">
         <v>1.2</v>
       </c>
@@ -6413,9 +6420,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="43.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
+    <row r="5" spans="1:12" ht="45">
+      <c r="A5" s="53"/>
+      <c r="B5" s="53"/>
       <c r="C5" s="15">
         <v>1.3</v>
       </c>
@@ -6436,9 +6443,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="115.2">
-      <c r="A6" s="44"/>
-      <c r="B6" s="44"/>
+    <row r="6" spans="1:12" ht="120">
+      <c r="A6" s="53"/>
+      <c r="B6" s="53"/>
       <c r="C6" s="36">
         <v>1.4</v>
       </c>
@@ -6461,9 +6468,9 @@
       <c r="I6" s="38"/>
       <c r="J6" s="38"/>
     </row>
-    <row r="7" spans="1:12" ht="72">
-      <c r="A7" s="44"/>
-      <c r="B7" s="44">
+    <row r="7" spans="1:12" ht="90">
+      <c r="A7" s="53"/>
+      <c r="B7" s="53">
         <v>2</v>
       </c>
       <c r="C7" s="15">
@@ -6486,9 +6493,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="57.6">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
+    <row r="8" spans="1:12" ht="60">
+      <c r="A8" s="53"/>
+      <c r="B8" s="53"/>
       <c r="C8" s="15">
         <v>2.2000000000000002</v>
       </c>
@@ -6509,9 +6516,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="100.8">
-      <c r="A9" s="44"/>
-      <c r="B9" s="44"/>
+    <row r="9" spans="1:12" ht="105">
+      <c r="A9" s="53"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="15">
         <v>2.2999999999999998</v>
       </c>
@@ -6526,15 +6533,15 @@
         <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="H9" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="115.2">
-      <c r="A10" s="44"/>
-      <c r="B10" s="44"/>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="120">
+      <c r="A10" s="53"/>
+      <c r="B10" s="53"/>
       <c r="C10" s="15">
         <v>2.4</v>
       </c>
@@ -6555,9 +6562,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="100.8">
-      <c r="A11" s="44"/>
-      <c r="B11" s="44"/>
+    <row r="11" spans="1:12" ht="120">
+      <c r="A11" s="53"/>
+      <c r="B11" s="53"/>
       <c r="C11" s="15">
         <v>2.5</v>
       </c>
@@ -6575,12 +6582,12 @@
         <v>245</v>
       </c>
       <c r="H11" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="115.2">
-      <c r="A12" s="44"/>
-      <c r="B12" s="44"/>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="120">
+      <c r="A12" s="53"/>
+      <c r="B12" s="53"/>
       <c r="C12" s="15">
         <v>2.6</v>
       </c>
@@ -6601,9 +6608,9 @@
         <v>261</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="158.4">
-      <c r="A13" s="44"/>
-      <c r="B13" s="44"/>
+    <row r="13" spans="1:12" ht="165">
+      <c r="A13" s="53"/>
+      <c r="B13" s="53"/>
       <c r="C13" s="36">
         <v>2.7</v>
       </c>
@@ -6626,7 +6633,7 @@
       <c r="I13" s="38"/>
       <c r="J13" s="38"/>
     </row>
-    <row r="14" spans="1:12" ht="144">
+    <row r="14" spans="1:12" ht="165">
       <c r="C14" s="41">
         <v>2.8</v>
       </c>
@@ -6666,11 +6673,11 @@
       <c r="I15" s="29"/>
       <c r="J15" s="31"/>
     </row>
-    <row r="16" spans="1:12" ht="86.4">
-      <c r="A16" s="45">
+    <row r="16" spans="1:12" ht="90">
+      <c r="A16" s="54">
         <v>2</v>
       </c>
-      <c r="B16" s="45">
+      <c r="B16" s="54">
         <v>3</v>
       </c>
       <c r="C16" s="15">
@@ -6680,9 +6687,9 @@
         <v>234</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="86.4">
-      <c r="A17" s="44"/>
-      <c r="B17" s="44"/>
+    <row r="17" spans="1:4" ht="90">
+      <c r="A17" s="53"/>
+      <c r="B17" s="53"/>
       <c r="C17" s="15">
         <v>3.2</v>
       </c>
@@ -6690,9 +6697,9 @@
         <v>266</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="86.4">
-      <c r="A18" s="44"/>
-      <c r="B18" s="44"/>
+    <row r="18" spans="1:4" ht="90">
+      <c r="A18" s="53"/>
+      <c r="B18" s="53"/>
       <c r="C18" s="15">
         <v>3.3</v>
       </c>
@@ -6700,9 +6707,9 @@
         <v>265</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="158.4">
-      <c r="A19" s="44"/>
-      <c r="B19" s="44"/>
+    <row r="19" spans="1:4" ht="165">
+      <c r="A19" s="53"/>
+      <c r="B19" s="53"/>
       <c r="C19" s="15">
         <v>3.4</v>
       </c>
@@ -6710,9 +6717,9 @@
         <v>235</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="100.8">
-      <c r="A20" s="44"/>
-      <c r="B20" s="44"/>
+    <row r="20" spans="1:4" ht="105">
+      <c r="A20" s="53"/>
+      <c r="B20" s="53"/>
       <c r="C20" s="15">
         <v>3.5</v>
       </c>
@@ -6720,9 +6727,9 @@
         <v>267</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="115.2">
-      <c r="A21" s="44"/>
-      <c r="B21" s="44"/>
+    <row r="21" spans="1:4" ht="120">
+      <c r="A21" s="53"/>
+      <c r="B21" s="53"/>
       <c r="C21" s="15">
         <v>3.6</v>
       </c>
@@ -6731,8 +6738,8 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="44"/>
-      <c r="B22" s="44"/>
+      <c r="A22" s="53"/>
+      <c r="B22" s="53"/>
       <c r="C22" s="15">
         <v>3.7</v>
       </c>
@@ -6740,9 +6747,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="86.4">
-      <c r="A23" s="44"/>
-      <c r="B23" s="44"/>
+    <row r="23" spans="1:4" ht="90">
+      <c r="A23" s="53"/>
+      <c r="B23" s="53"/>
       <c r="C23" s="15">
         <v>3.8</v>
       </c>
@@ -6750,9 +6757,9 @@
         <v>236</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="158.4">
-      <c r="A24" s="44"/>
-      <c r="B24" s="44"/>
+    <row r="24" spans="1:4" ht="165">
+      <c r="A24" s="53"/>
+      <c r="B24" s="53"/>
       <c r="C24" s="15">
         <v>3.9</v>
       </c>
@@ -6760,9 +6767,9 @@
         <v>237</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="144">
-      <c r="A25" s="44"/>
-      <c r="B25" s="44"/>
+    <row r="25" spans="1:4" ht="150">
+      <c r="A25" s="53"/>
+      <c r="B25" s="53"/>
       <c r="C25" s="35">
         <v>3.1</v>
       </c>
@@ -6770,9 +6777,9 @@
         <v>238</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="72">
-      <c r="A26" s="44"/>
-      <c r="B26" s="44"/>
+    <row r="26" spans="1:4" ht="75">
+      <c r="A26" s="53"/>
+      <c r="B26" s="53"/>
       <c r="C26" s="15">
         <v>3.11</v>
       </c>
@@ -6780,9 +6787,9 @@
         <v>239</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="216">
-      <c r="A27" s="44"/>
-      <c r="B27" s="44"/>
+    <row r="27" spans="1:4" ht="225">
+      <c r="A27" s="53"/>
+      <c r="B27" s="53"/>
       <c r="C27" s="35">
         <v>3.12</v>
       </c>
@@ -6790,9 +6797,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="57.6">
-      <c r="A28" s="44"/>
-      <c r="B28" s="44">
+    <row r="28" spans="1:4" ht="60">
+      <c r="A28" s="53"/>
+      <c r="B28" s="53">
         <v>4</v>
       </c>
       <c r="C28" s="15">
@@ -6802,9 +6809,9 @@
         <v>241</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="100.8">
-      <c r="A29" s="44"/>
-      <c r="B29" s="44"/>
+    <row r="29" spans="1:4" ht="105">
+      <c r="A29" s="53"/>
+      <c r="B29" s="53"/>
       <c r="C29" s="15">
         <v>4.2</v>
       </c>
@@ -6812,9 +6819,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="86.4">
-      <c r="A30" s="44"/>
-      <c r="B30" s="44"/>
+    <row r="30" spans="1:4" ht="90">
+      <c r="A30" s="53"/>
+      <c r="B30" s="53"/>
       <c r="C30" s="15">
         <v>4.3</v>
       </c>
@@ -6822,9 +6829,9 @@
         <v>243</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="115.2">
-      <c r="A31" s="44"/>
-      <c r="B31" s="44"/>
+    <row r="31" spans="1:4" ht="120">
+      <c r="A31" s="53"/>
+      <c r="B31" s="53"/>
       <c r="C31" s="15">
         <v>4.4000000000000004</v>
       </c>
@@ -6849,17 +6856,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57.6">
+    <row r="1" spans="1:5" ht="60">
       <c r="A1" s="22" t="s">
         <v>214</v>
       </c>
@@ -7057,9 +7064,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="55" t="s">

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -6628,7 +6628,7 @@
         <v>247</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I13" s="38"/>
       <c r="J13" s="38"/>

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -2899,18 +2899,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2918,7 +2906,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4563,18 +4563,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1">
       <c r="A2" s="10" t="s">
@@ -4609,632 +4609,632 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="51">
+      <c r="A3" s="47">
         <v>1</v>
       </c>
-      <c r="B3" s="45">
+      <c r="B3" s="48">
         <v>1</v>
       </c>
-      <c r="C3" s="45">
+      <c r="C3" s="48">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="49" t="s">
+      <c r="E3" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="49" cm="1">
+      <c r="F3" s="45" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="51"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
       <c r="D4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="51"/>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
+      <c r="A5" s="47"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="51"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
+      <c r="A6" s="47"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="51"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
+      <c r="A7" s="47"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="51"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
+      <c r="A8" s="47"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="51"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
+      <c r="A9" s="47"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
       <c r="D9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="51"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="51"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
+      <c r="A11" s="47"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="51"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45">
+      <c r="A12" s="47"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48">
         <v>1.2</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="49" t="s">
+      <c r="E12" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="49" cm="1">
+      <c r="F12" s="45" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="51"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="51"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
+      <c r="A14" s="47"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="51"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45">
+      <c r="A15" s="47"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48">
         <v>1.3</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="49" t="s">
+      <c r="E15" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="49"/>
+      <c r="F15" s="45"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="51"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
+      <c r="A16" s="47"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="51"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
       <c r="D17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="51"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45">
+      <c r="A18" s="47"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48">
         <v>1.4</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="49" t="s">
+      <c r="E18" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="49"/>
+      <c r="F18" s="45"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="51"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
       <c r="D19" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="51"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="48"/>
       <c r="D20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="51"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
       <c r="D21" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="51"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
       <c r="D22" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="51"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
       <c r="D23" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="51"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
+      <c r="A24" s="47"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
       <c r="D24" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="51"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
+      <c r="A25" s="47"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
       <c r="D25" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="51"/>
-      <c r="B26" s="52">
+      <c r="A26" s="47"/>
+      <c r="B26" s="49">
         <v>2</v>
       </c>
-      <c r="C26" s="45">
+      <c r="C26" s="48">
         <v>2.1</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E26" s="50" t="s">
+      <c r="E26" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="49"/>
+      <c r="F26" s="45"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="51"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="45"/>
+      <c r="A27" s="47"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="48"/>
       <c r="D27" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="50"/>
-      <c r="F27" s="49"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="45"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="51"/>
-      <c r="B28" s="52"/>
-      <c r="C28" s="45"/>
+      <c r="A28" s="47"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="48"/>
       <c r="D28" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E28" s="50"/>
-      <c r="F28" s="49"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="45"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="51"/>
-      <c r="B29" s="52"/>
-      <c r="C29" s="47">
+      <c r="A29" s="47"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="51">
         <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="49" t="s">
+      <c r="E29" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="49"/>
+      <c r="F29" s="45"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="51"/>
-      <c r="B30" s="52"/>
-      <c r="C30" s="47"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="51"/>
       <c r="D30" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="51"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="45">
+      <c r="A31" s="47"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="48">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="49" t="s">
+      <c r="E31" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49" t="s">
+      <c r="F31" s="45"/>
+      <c r="G31" s="45" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="51"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="45"/>
+      <c r="A32" s="47"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="48"/>
       <c r="D32" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="51"/>
-      <c r="B33" s="52"/>
-      <c r="C33" s="45"/>
+      <c r="A33" s="47"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="48"/>
       <c r="D33" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="49"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="49"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="51"/>
-      <c r="B34" s="52"/>
-      <c r="C34" s="45"/>
+      <c r="A34" s="47"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="48"/>
       <c r="D34" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="51"/>
-      <c r="B35" s="52"/>
-      <c r="C35" s="45"/>
+      <c r="A35" s="47"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="48"/>
       <c r="D35" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="49"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="51"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="45"/>
+      <c r="A36" s="47"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="48"/>
       <c r="D36" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="51"/>
-      <c r="B37" s="52"/>
-      <c r="C37" s="45"/>
+      <c r="A37" s="47"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="48"/>
       <c r="D37" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E37" s="49"/>
-      <c r="F37" s="49"/>
-      <c r="G37" s="49"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="51"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="45">
+      <c r="A38" s="47"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="48">
         <v>2.4</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E38" s="49" t="s">
+      <c r="E38" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="49"/>
+      <c r="F38" s="45"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="51"/>
-      <c r="B39" s="52"/>
-      <c r="C39" s="45"/>
+      <c r="A39" s="47"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="48"/>
       <c r="D39" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E39" s="49"/>
-      <c r="F39" s="49"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="51"/>
-      <c r="B40" s="52"/>
-      <c r="C40" s="45"/>
+      <c r="A40" s="47"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="48"/>
       <c r="D40" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E40" s="49"/>
-      <c r="F40" s="49"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="51"/>
-      <c r="B41" s="52"/>
-      <c r="C41" s="45"/>
+      <c r="A41" s="47"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="48"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="49"/>
-      <c r="F41" s="49"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="51"/>
-      <c r="B42" s="52"/>
-      <c r="C42" s="45"/>
+      <c r="A42" s="47"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="48"/>
       <c r="D42" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="49"/>
-      <c r="F42" s="49"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="51"/>
-      <c r="B43" s="52"/>
-      <c r="C43" s="45"/>
+      <c r="A43" s="47"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="48"/>
       <c r="D43" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="45"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="51"/>
-      <c r="B44" s="52"/>
-      <c r="C44" s="45"/>
+      <c r="A44" s="47"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="48"/>
       <c r="D44" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E44" s="49"/>
-      <c r="F44" s="49"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="45"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="51"/>
-      <c r="B45" s="52"/>
-      <c r="C45" s="45"/>
+      <c r="A45" s="47"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="48"/>
       <c r="D45" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="45"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="51"/>
-      <c r="B46" s="52"/>
-      <c r="C46" s="45">
+      <c r="A46" s="47"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="48">
         <v>2.5</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="E46" s="50" t="s">
+      <c r="E46" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="49"/>
+      <c r="F46" s="45"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="51"/>
-      <c r="B47" s="52"/>
-      <c r="C47" s="45"/>
+      <c r="A47" s="47"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="48"/>
       <c r="D47" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E47" s="50"/>
-      <c r="F47" s="49"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="45"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="51"/>
-      <c r="B48" s="52"/>
-      <c r="C48" s="45"/>
+      <c r="A48" s="47"/>
+      <c r="B48" s="49"/>
+      <c r="C48" s="48"/>
       <c r="D48" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E48" s="50"/>
-      <c r="F48" s="49"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="45"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="51"/>
-      <c r="B49" s="52"/>
-      <c r="C49" s="45"/>
+      <c r="A49" s="47"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="48"/>
       <c r="D49" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E49" s="50"/>
-      <c r="F49" s="49"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="45"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="51"/>
-      <c r="B50" s="52"/>
-      <c r="C50" s="45">
+      <c r="A50" s="47"/>
+      <c r="B50" s="49"/>
+      <c r="C50" s="48">
         <v>2.7</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E50" s="49" t="s">
+      <c r="E50" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F50" s="49"/>
+      <c r="F50" s="45"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="51"/>
-      <c r="B51" s="52"/>
-      <c r="C51" s="45"/>
+      <c r="A51" s="47"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="48"/>
       <c r="D51" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E51" s="49"/>
-      <c r="F51" s="49"/>
+      <c r="E51" s="45"/>
+      <c r="F51" s="45"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="51"/>
-      <c r="B52" s="52"/>
-      <c r="C52" s="45"/>
+      <c r="A52" s="47"/>
+      <c r="B52" s="49"/>
+      <c r="C52" s="48"/>
       <c r="D52" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E52" s="49"/>
-      <c r="F52" s="49"/>
+      <c r="E52" s="45"/>
+      <c r="F52" s="45"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="51"/>
-      <c r="B53" s="52"/>
-      <c r="C53" s="45"/>
+      <c r="A53" s="47"/>
+      <c r="B53" s="49"/>
+      <c r="C53" s="48"/>
       <c r="D53" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E53" s="49"/>
-      <c r="F53" s="49"/>
+      <c r="E53" s="45"/>
+      <c r="F53" s="45"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="51"/>
-      <c r="B54" s="52"/>
-      <c r="C54" s="45"/>
+      <c r="A54" s="47"/>
+      <c r="B54" s="49"/>
+      <c r="C54" s="48"/>
       <c r="D54" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E54" s="49"/>
-      <c r="F54" s="49"/>
+      <c r="E54" s="45"/>
+      <c r="F54" s="45"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="51"/>
-      <c r="B55" s="52"/>
-      <c r="C55" s="45"/>
+      <c r="A55" s="47"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="48"/>
       <c r="D55" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E55" s="49"/>
-      <c r="F55" s="49"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="45"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="51"/>
-      <c r="B56" s="52"/>
-      <c r="C56" s="45"/>
+      <c r="A56" s="47"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="48"/>
       <c r="D56" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="49"/>
-      <c r="F56" s="49"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="45"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="51"/>
-      <c r="B57" s="52"/>
-      <c r="C57" s="45"/>
+      <c r="A57" s="47"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="48"/>
       <c r="D57" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E57" s="49"/>
-      <c r="F57" s="49"/>
+      <c r="E57" s="45"/>
+      <c r="F57" s="45"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="51"/>
-      <c r="B58" s="52"/>
-      <c r="C58" s="45"/>
+      <c r="A58" s="47"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="48"/>
       <c r="D58" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E58" s="49"/>
-      <c r="F58" s="49"/>
+      <c r="E58" s="45"/>
+      <c r="F58" s="45"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
-      <c r="B59" s="45">
+      <c r="B59" s="48">
         <v>3</v>
       </c>
-      <c r="C59" s="45">
+      <c r="C59" s="48">
         <v>3.1</v>
       </c>
       <c r="D59" s="7" t="s">
@@ -5243,48 +5243,48 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="19"/>
-      <c r="B60" s="45"/>
-      <c r="C60" s="45"/>
+      <c r="B60" s="48"/>
+      <c r="C60" s="48"/>
       <c r="D60" s="7" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="19"/>
-      <c r="B61" s="45"/>
-      <c r="C61" s="45"/>
+      <c r="B61" s="48"/>
+      <c r="C61" s="48"/>
       <c r="D61" s="7" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="19"/>
-      <c r="B62" s="45"/>
-      <c r="C62" s="45"/>
+      <c r="B62" s="48"/>
+      <c r="C62" s="48"/>
       <c r="D62" s="7" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="19"/>
-      <c r="B63" s="45"/>
-      <c r="C63" s="45"/>
+      <c r="B63" s="48"/>
+      <c r="C63" s="48"/>
       <c r="D63" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="19"/>
-      <c r="B64" s="45"/>
-      <c r="C64" s="45"/>
+      <c r="B64" s="48"/>
+      <c r="C64" s="48"/>
       <c r="D64" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="19"/>
-      <c r="B65" s="45"/>
-      <c r="C65" s="45">
+      <c r="B65" s="48"/>
+      <c r="C65" s="48">
         <v>3.2</v>
       </c>
       <c r="D65" s="7" t="s">
@@ -5293,96 +5293,96 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="19"/>
-      <c r="B66" s="45"/>
-      <c r="C66" s="45"/>
+      <c r="B66" s="48"/>
+      <c r="C66" s="48"/>
       <c r="D66" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="19"/>
-      <c r="B67" s="45"/>
-      <c r="C67" s="45"/>
+      <c r="B67" s="48"/>
+      <c r="C67" s="48"/>
       <c r="D67" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="19"/>
-      <c r="B68" s="45"/>
-      <c r="C68" s="45"/>
+      <c r="B68" s="48"/>
+      <c r="C68" s="48"/>
       <c r="D68" s="7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="19"/>
-      <c r="B69" s="45"/>
-      <c r="C69" s="45"/>
+      <c r="B69" s="48"/>
+      <c r="C69" s="48"/>
       <c r="D69" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="19"/>
-      <c r="B70" s="45"/>
-      <c r="C70" s="45"/>
+      <c r="B70" s="48"/>
+      <c r="C70" s="48"/>
       <c r="D70" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="19"/>
-      <c r="B71" s="45"/>
-      <c r="C71" s="45"/>
+      <c r="B71" s="48"/>
+      <c r="C71" s="48"/>
       <c r="D71" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="19"/>
-      <c r="B72" s="45"/>
-      <c r="C72" s="45"/>
+      <c r="B72" s="48"/>
+      <c r="C72" s="48"/>
       <c r="D72" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="19"/>
-      <c r="B73" s="45"/>
-      <c r="C73" s="45"/>
+      <c r="B73" s="48"/>
+      <c r="C73" s="48"/>
       <c r="D73" s="7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="19"/>
-      <c r="B74" s="45"/>
-      <c r="C74" s="45"/>
+      <c r="B74" s="48"/>
+      <c r="C74" s="48"/>
       <c r="D74" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="19"/>
-      <c r="B75" s="45"/>
-      <c r="C75" s="45"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
       <c r="D75" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="19"/>
-      <c r="B76" s="45"/>
-      <c r="C76" s="45"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
       <c r="D76" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="19"/>
-      <c r="B77" s="45"/>
-      <c r="C77" s="45">
+      <c r="B77" s="48"/>
+      <c r="C77" s="48">
         <v>3.3</v>
       </c>
       <c r="D77" s="7" t="s">
@@ -5391,88 +5391,88 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="19"/>
-      <c r="B78" s="45"/>
-      <c r="C78" s="45"/>
+      <c r="B78" s="48"/>
+      <c r="C78" s="48"/>
       <c r="D78" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="19"/>
-      <c r="B79" s="45"/>
-      <c r="C79" s="45"/>
+      <c r="B79" s="48"/>
+      <c r="C79" s="48"/>
       <c r="D79" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="19"/>
-      <c r="B80" s="45"/>
-      <c r="C80" s="45"/>
+      <c r="B80" s="48"/>
+      <c r="C80" s="48"/>
       <c r="D80" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="19"/>
-      <c r="B81" s="45"/>
-      <c r="C81" s="45"/>
+      <c r="B81" s="48"/>
+      <c r="C81" s="48"/>
       <c r="D81" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="19"/>
-      <c r="B82" s="45"/>
-      <c r="C82" s="45"/>
+      <c r="B82" s="48"/>
+      <c r="C82" s="48"/>
       <c r="D82" s="7" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="19"/>
-      <c r="B83" s="45"/>
-      <c r="C83" s="45"/>
+      <c r="B83" s="48"/>
+      <c r="C83" s="48"/>
       <c r="D83" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="19"/>
-      <c r="B84" s="45"/>
-      <c r="C84" s="45"/>
+      <c r="B84" s="48"/>
+      <c r="C84" s="48"/>
       <c r="D84" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="19"/>
-      <c r="B85" s="45"/>
-      <c r="C85" s="45"/>
+      <c r="B85" s="48"/>
+      <c r="C85" s="48"/>
       <c r="D85" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="19"/>
-      <c r="B86" s="45"/>
-      <c r="C86" s="45"/>
+      <c r="B86" s="48"/>
+      <c r="C86" s="48"/>
       <c r="D86" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="19"/>
-      <c r="B87" s="45"/>
-      <c r="C87" s="45"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
       <c r="D87" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="19"/>
-      <c r="B88" s="45"/>
-      <c r="C88" s="45">
+      <c r="B88" s="48"/>
+      <c r="C88" s="48">
         <v>3.4</v>
       </c>
       <c r="D88" s="15" t="s">
@@ -5481,104 +5481,104 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="19"/>
-      <c r="B89" s="45"/>
-      <c r="C89" s="45"/>
+      <c r="B89" s="48"/>
+      <c r="C89" s="48"/>
       <c r="D89" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="19"/>
-      <c r="B90" s="45"/>
-      <c r="C90" s="45"/>
+      <c r="B90" s="48"/>
+      <c r="C90" s="48"/>
       <c r="D90" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="19"/>
-      <c r="B91" s="45"/>
-      <c r="C91" s="45"/>
+      <c r="B91" s="48"/>
+      <c r="C91" s="48"/>
       <c r="D91" s="7" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="19"/>
-      <c r="B92" s="45"/>
-      <c r="C92" s="45"/>
+      <c r="B92" s="48"/>
+      <c r="C92" s="48"/>
       <c r="D92" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="19"/>
-      <c r="B93" s="45"/>
-      <c r="C93" s="45"/>
+      <c r="B93" s="48"/>
+      <c r="C93" s="48"/>
       <c r="D93" s="7" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="19"/>
-      <c r="B94" s="45"/>
-      <c r="C94" s="45"/>
+      <c r="B94" s="48"/>
+      <c r="C94" s="48"/>
       <c r="D94" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="19"/>
-      <c r="B95" s="45"/>
-      <c r="C95" s="45"/>
+      <c r="B95" s="48"/>
+      <c r="C95" s="48"/>
       <c r="D95" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="19"/>
-      <c r="B96" s="45"/>
-      <c r="C96" s="45"/>
+      <c r="B96" s="48"/>
+      <c r="C96" s="48"/>
       <c r="D96" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="19"/>
-      <c r="B97" s="45"/>
-      <c r="C97" s="45"/>
+      <c r="B97" s="48"/>
+      <c r="C97" s="48"/>
       <c r="D97" s="7" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="19"/>
-      <c r="B98" s="45"/>
-      <c r="C98" s="45"/>
+      <c r="B98" s="48"/>
+      <c r="C98" s="48"/>
       <c r="D98" s="7" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="19"/>
-      <c r="B99" s="45"/>
-      <c r="C99" s="45"/>
+      <c r="B99" s="48"/>
+      <c r="C99" s="48"/>
       <c r="D99" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="19"/>
-      <c r="B100" s="45"/>
-      <c r="C100" s="45"/>
+      <c r="B100" s="48"/>
+      <c r="C100" s="48"/>
       <c r="D100" s="7" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="19"/>
-      <c r="B101" s="45"/>
-      <c r="C101" s="45">
+      <c r="B101" s="48"/>
+      <c r="C101" s="48">
         <v>3.5</v>
       </c>
       <c r="D101" s="11" t="s">
@@ -5587,72 +5587,72 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="19"/>
-      <c r="B102" s="45"/>
-      <c r="C102" s="45"/>
+      <c r="B102" s="48"/>
+      <c r="C102" s="48"/>
       <c r="D102" s="7" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="19"/>
-      <c r="B103" s="45"/>
-      <c r="C103" s="45"/>
+      <c r="B103" s="48"/>
+      <c r="C103" s="48"/>
       <c r="D103" s="7" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="19"/>
-      <c r="B104" s="45"/>
-      <c r="C104" s="45"/>
+      <c r="B104" s="48"/>
+      <c r="C104" s="48"/>
       <c r="D104" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="19"/>
-      <c r="B105" s="45"/>
-      <c r="C105" s="45"/>
+      <c r="B105" s="48"/>
+      <c r="C105" s="48"/>
       <c r="D105" s="7" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="19"/>
-      <c r="B106" s="45"/>
-      <c r="C106" s="45"/>
+      <c r="B106" s="48"/>
+      <c r="C106" s="48"/>
       <c r="D106" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="19"/>
-      <c r="B107" s="45"/>
-      <c r="C107" s="45"/>
+      <c r="B107" s="48"/>
+      <c r="C107" s="48"/>
       <c r="D107" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="19"/>
-      <c r="B108" s="45"/>
-      <c r="C108" s="45"/>
+      <c r="B108" s="48"/>
+      <c r="C108" s="48"/>
       <c r="D108" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="19"/>
-      <c r="B109" s="45"/>
-      <c r="C109" s="45"/>
+      <c r="B109" s="48"/>
+      <c r="C109" s="48"/>
       <c r="D109" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="19"/>
-      <c r="B110" s="45"/>
-      <c r="C110" s="45">
+      <c r="B110" s="48"/>
+      <c r="C110" s="48">
         <v>3.6</v>
       </c>
       <c r="D110" s="7" t="s">
@@ -5661,48 +5661,48 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19"/>
-      <c r="B111" s="45"/>
-      <c r="C111" s="45"/>
+      <c r="B111" s="48"/>
+      <c r="C111" s="48"/>
       <c r="D111" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19"/>
-      <c r="B112" s="45"/>
-      <c r="C112" s="45"/>
+      <c r="B112" s="48"/>
+      <c r="C112" s="48"/>
       <c r="D112" s="7" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="19"/>
-      <c r="B113" s="45"/>
-      <c r="C113" s="45"/>
+      <c r="B113" s="48"/>
+      <c r="C113" s="48"/>
       <c r="D113" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="19"/>
-      <c r="B114" s="45"/>
-      <c r="C114" s="45"/>
+      <c r="B114" s="48"/>
+      <c r="C114" s="48"/>
       <c r="D114" s="7" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="19"/>
-      <c r="B115" s="45"/>
-      <c r="C115" s="45"/>
+      <c r="B115" s="48"/>
+      <c r="C115" s="48"/>
       <c r="D115" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="19"/>
-      <c r="B116" s="45"/>
-      <c r="C116" s="45">
+      <c r="B116" s="48"/>
+      <c r="C116" s="48">
         <v>3.7</v>
       </c>
       <c r="D116" s="7" t="s">
@@ -5711,88 +5711,88 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="19"/>
-      <c r="B117" s="45"/>
-      <c r="C117" s="45"/>
+      <c r="B117" s="48"/>
+      <c r="C117" s="48"/>
       <c r="D117" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="19"/>
-      <c r="B118" s="45"/>
-      <c r="C118" s="45"/>
+      <c r="B118" s="48"/>
+      <c r="C118" s="48"/>
       <c r="D118" s="7" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="19"/>
-      <c r="B119" s="45"/>
-      <c r="C119" s="45"/>
+      <c r="B119" s="48"/>
+      <c r="C119" s="48"/>
       <c r="D119" s="7" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="19"/>
-      <c r="B120" s="45"/>
-      <c r="C120" s="45"/>
+      <c r="B120" s="48"/>
+      <c r="C120" s="48"/>
       <c r="D120" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="19"/>
-      <c r="B121" s="45"/>
-      <c r="C121" s="45"/>
+      <c r="B121" s="48"/>
+      <c r="C121" s="48"/>
       <c r="D121" s="7" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="19"/>
-      <c r="B122" s="45"/>
-      <c r="C122" s="45"/>
+      <c r="B122" s="48"/>
+      <c r="C122" s="48"/>
       <c r="D122" s="7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="19"/>
-      <c r="B123" s="45"/>
-      <c r="C123" s="45"/>
+      <c r="B123" s="48"/>
+      <c r="C123" s="48"/>
       <c r="D123" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="19"/>
-      <c r="B124" s="45"/>
-      <c r="C124" s="45"/>
+      <c r="B124" s="48"/>
+      <c r="C124" s="48"/>
       <c r="D124" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="19"/>
-      <c r="B125" s="45"/>
-      <c r="C125" s="45"/>
+      <c r="B125" s="48"/>
+      <c r="C125" s="48"/>
       <c r="D125" s="7" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="19"/>
-      <c r="B126" s="45"/>
-      <c r="C126" s="45"/>
+      <c r="B126" s="48"/>
+      <c r="C126" s="48"/>
       <c r="D126" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="19"/>
-      <c r="B127" s="45"/>
-      <c r="C127" s="45">
+      <c r="B127" s="48"/>
+      <c r="C127" s="48">
         <v>3.8</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -5801,80 +5801,80 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="19"/>
-      <c r="B128" s="45"/>
-      <c r="C128" s="45"/>
+      <c r="B128" s="48"/>
+      <c r="C128" s="48"/>
       <c r="D128" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="19"/>
-      <c r="B129" s="45"/>
-      <c r="C129" s="45"/>
+      <c r="B129" s="48"/>
+      <c r="C129" s="48"/>
       <c r="D129" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="19"/>
-      <c r="B130" s="45"/>
-      <c r="C130" s="45"/>
+      <c r="B130" s="48"/>
+      <c r="C130" s="48"/>
       <c r="D130" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="19"/>
-      <c r="B131" s="45"/>
-      <c r="C131" s="45"/>
+      <c r="B131" s="48"/>
+      <c r="C131" s="48"/>
       <c r="D131" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="19"/>
-      <c r="B132" s="45"/>
-      <c r="C132" s="45"/>
+      <c r="B132" s="48"/>
+      <c r="C132" s="48"/>
       <c r="D132" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="19"/>
-      <c r="B133" s="45"/>
-      <c r="C133" s="45"/>
+      <c r="B133" s="48"/>
+      <c r="C133" s="48"/>
       <c r="D133" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="19"/>
-      <c r="B134" s="45"/>
-      <c r="C134" s="45"/>
+      <c r="B134" s="48"/>
+      <c r="C134" s="48"/>
       <c r="D134" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="19"/>
-      <c r="B135" s="45"/>
-      <c r="C135" s="45"/>
+      <c r="B135" s="48"/>
+      <c r="C135" s="48"/>
       <c r="D135" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="19"/>
-      <c r="B136" s="45"/>
-      <c r="C136" s="45"/>
+      <c r="B136" s="48"/>
+      <c r="C136" s="48"/>
       <c r="D136" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="19"/>
-      <c r="B137" s="45"/>
-      <c r="C137" s="45">
+      <c r="B137" s="48"/>
+      <c r="C137" s="48">
         <v>3.9</v>
       </c>
       <c r="D137" s="7" t="s">
@@ -5883,40 +5883,40 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="19"/>
-      <c r="B138" s="45"/>
-      <c r="C138" s="45"/>
+      <c r="B138" s="48"/>
+      <c r="C138" s="48"/>
       <c r="D138" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="19"/>
-      <c r="B139" s="45"/>
-      <c r="C139" s="45"/>
+      <c r="B139" s="48"/>
+      <c r="C139" s="48"/>
       <c r="D139" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="19"/>
-      <c r="B140" s="45"/>
-      <c r="C140" s="45"/>
+      <c r="B140" s="48"/>
+      <c r="C140" s="48"/>
       <c r="D140" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="19"/>
-      <c r="B141" s="45"/>
-      <c r="C141" s="45"/>
+      <c r="B141" s="48"/>
+      <c r="C141" s="48"/>
       <c r="D141" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
-      <c r="B142" s="45"/>
-      <c r="C142" s="46">
+      <c r="B142" s="48"/>
+      <c r="C142" s="52">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -5925,122 +5925,122 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
-      <c r="B143" s="45"/>
-      <c r="C143" s="46"/>
+      <c r="B143" s="48"/>
+      <c r="C143" s="52"/>
       <c r="D143" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
-      <c r="B144" s="45"/>
-      <c r="C144" s="46"/>
+      <c r="B144" s="48"/>
+      <c r="C144" s="52"/>
       <c r="D144" s="7" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
-      <c r="B145" s="45"/>
-      <c r="C145" s="46"/>
+      <c r="B145" s="48"/>
+      <c r="C145" s="52"/>
       <c r="D145" s="7" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
-      <c r="B146" s="45"/>
-      <c r="C146" s="46"/>
+      <c r="B146" s="48"/>
+      <c r="C146" s="52"/>
       <c r="D146" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
-      <c r="B147" s="45"/>
-      <c r="C147" s="46"/>
+      <c r="B147" s="48"/>
+      <c r="C147" s="52"/>
       <c r="D147" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
-      <c r="B148" s="45"/>
-      <c r="C148" s="46"/>
+      <c r="B148" s="48"/>
+      <c r="C148" s="52"/>
       <c r="D148" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
-      <c r="B149" s="45"/>
-      <c r="C149" s="46"/>
+      <c r="B149" s="48"/>
+      <c r="C149" s="52"/>
       <c r="D149" s="7" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
-      <c r="B150" s="45"/>
-      <c r="C150" s="46"/>
+      <c r="B150" s="48"/>
+      <c r="C150" s="52"/>
       <c r="D150" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
-      <c r="B151" s="45"/>
-      <c r="C151" s="46"/>
+      <c r="B151" s="48"/>
+      <c r="C151" s="52"/>
       <c r="D151" s="7" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
-      <c r="B152" s="45"/>
-      <c r="C152" s="46"/>
+      <c r="B152" s="48"/>
+      <c r="C152" s="52"/>
       <c r="D152" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
-      <c r="B153" s="45"/>
-      <c r="C153" s="46"/>
+      <c r="B153" s="48"/>
+      <c r="C153" s="52"/>
       <c r="D153" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
-      <c r="B154" s="45"/>
-      <c r="C154" s="46"/>
+      <c r="B154" s="48"/>
+      <c r="C154" s="52"/>
       <c r="D154" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
-      <c r="B155" s="45"/>
-      <c r="C155" s="46"/>
+      <c r="B155" s="48"/>
+      <c r="C155" s="52"/>
       <c r="D155" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
-      <c r="B156" s="45"/>
-      <c r="C156" s="46"/>
+      <c r="B156" s="48"/>
+      <c r="C156" s="52"/>
       <c r="D156" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="20"/>
-      <c r="B157" s="45">
+      <c r="B157" s="48">
         <v>4</v>
       </c>
-      <c r="C157" s="45">
+      <c r="C157" s="48">
         <v>4.0999999999999996</v>
       </c>
       <c r="D157" s="7" t="s">
@@ -6049,32 +6049,32 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="19"/>
-      <c r="B158" s="45"/>
-      <c r="C158" s="45"/>
+      <c r="B158" s="48"/>
+      <c r="C158" s="48"/>
       <c r="D158" s="7" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="19"/>
-      <c r="B159" s="45"/>
-      <c r="C159" s="45"/>
+      <c r="B159" s="48"/>
+      <c r="C159" s="48"/>
       <c r="D159" s="7" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="19"/>
-      <c r="B160" s="45"/>
-      <c r="C160" s="45"/>
+      <c r="B160" s="48"/>
+      <c r="C160" s="48"/>
       <c r="D160" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="19"/>
-      <c r="B161" s="45"/>
-      <c r="C161" s="45">
+      <c r="B161" s="48"/>
+      <c r="C161" s="48">
         <v>4.2</v>
       </c>
       <c r="D161" s="7" t="s">
@@ -6083,56 +6083,56 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="19"/>
-      <c r="B162" s="45"/>
-      <c r="C162" s="45"/>
+      <c r="B162" s="48"/>
+      <c r="C162" s="48"/>
       <c r="D162" s="7" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="19"/>
-      <c r="B163" s="45"/>
-      <c r="C163" s="45"/>
+      <c r="B163" s="48"/>
+      <c r="C163" s="48"/>
       <c r="D163" s="7" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="19"/>
-      <c r="B164" s="45"/>
-      <c r="C164" s="45"/>
+      <c r="B164" s="48"/>
+      <c r="C164" s="48"/>
       <c r="D164" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="19"/>
-      <c r="B165" s="45"/>
-      <c r="C165" s="45"/>
+      <c r="B165" s="48"/>
+      <c r="C165" s="48"/>
       <c r="D165" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="19"/>
-      <c r="B166" s="45"/>
-      <c r="C166" s="45"/>
+      <c r="B166" s="48"/>
+      <c r="C166" s="48"/>
       <c r="D166" s="7" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="19"/>
-      <c r="B167" s="45"/>
-      <c r="C167" s="45"/>
+      <c r="B167" s="48"/>
+      <c r="C167" s="48"/>
       <c r="D167" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="19"/>
-      <c r="B168" s="45"/>
-      <c r="C168" s="45">
+      <c r="B168" s="48"/>
+      <c r="C168" s="48">
         <v>4.3</v>
       </c>
       <c r="D168" s="7" t="s">
@@ -6141,48 +6141,48 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="19"/>
-      <c r="B169" s="45"/>
-      <c r="C169" s="45"/>
+      <c r="B169" s="48"/>
+      <c r="C169" s="48"/>
       <c r="D169" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="19"/>
-      <c r="B170" s="45"/>
-      <c r="C170" s="45"/>
+      <c r="B170" s="48"/>
+      <c r="C170" s="48"/>
       <c r="D170" s="7" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="19"/>
-      <c r="B171" s="45"/>
-      <c r="C171" s="45"/>
+      <c r="B171" s="48"/>
+      <c r="C171" s="48"/>
       <c r="D171" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="19"/>
-      <c r="B172" s="45"/>
-      <c r="C172" s="45"/>
+      <c r="B172" s="48"/>
+      <c r="C172" s="48"/>
       <c r="D172" s="7" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="19"/>
-      <c r="B173" s="45"/>
-      <c r="C173" s="45"/>
+      <c r="B173" s="48"/>
+      <c r="C173" s="48"/>
       <c r="D173" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="19"/>
-      <c r="B174" s="45"/>
-      <c r="C174" s="45">
+      <c r="B174" s="48"/>
+      <c r="C174" s="48">
         <v>4.4000000000000004</v>
       </c>
       <c r="D174" s="7" t="s">
@@ -6191,56 +6191,56 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="19"/>
-      <c r="B175" s="45"/>
-      <c r="C175" s="45"/>
+      <c r="B175" s="48"/>
+      <c r="C175" s="48"/>
       <c r="D175" s="7" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="19"/>
-      <c r="B176" s="45"/>
-      <c r="C176" s="45"/>
+      <c r="B176" s="48"/>
+      <c r="C176" s="48"/>
       <c r="D176" s="7" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="19"/>
-      <c r="B177" s="45"/>
-      <c r="C177" s="45"/>
+      <c r="B177" s="48"/>
+      <c r="C177" s="48"/>
       <c r="D177" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="19"/>
-      <c r="B178" s="45"/>
-      <c r="C178" s="45"/>
+      <c r="B178" s="48"/>
+      <c r="C178" s="48"/>
       <c r="D178" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="19"/>
-      <c r="B179" s="45"/>
-      <c r="C179" s="45"/>
+      <c r="B179" s="48"/>
+      <c r="C179" s="48"/>
       <c r="D179" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="19"/>
-      <c r="B180" s="45"/>
-      <c r="C180" s="45"/>
+      <c r="B180" s="48"/>
+      <c r="C180" s="48"/>
       <c r="D180" s="7" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="19"/>
-      <c r="B181" s="45"/>
-      <c r="C181" s="45"/>
+      <c r="B181" s="48"/>
+      <c r="C181" s="48"/>
       <c r="D181" s="7" t="s">
         <v>57</v>
       </c>
@@ -6248,41 +6248,6 @@
   </sheetData>
   <autoFilter ref="A2:J181"/>
   <mergeCells count="51">
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -6299,6 +6264,41 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6321,18 +6321,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
     </row>
     <row r="2" spans="1:12" s="4" customFormat="1">
       <c r="A2" s="32" t="s">

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B3398E-200A-452E-81A1-E9A31A4AA09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="13170" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="4" r:id="rId1"/>
@@ -16,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sprint Backlog'!$A$2:$J$181</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,12 +35,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="E5" authorId="0" shapeId="0">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -56,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -78,12 +79,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -109,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -133,7 +134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -157,7 +158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C15" authorId="0" shapeId="0">
+    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
@@ -181,7 +182,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C18" authorId="0" shapeId="0">
+    <comment ref="C18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
@@ -205,7 +206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C26" authorId="0" shapeId="0">
+    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
@@ -230,7 +231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C29" authorId="0" shapeId="0">
+    <comment ref="C29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
@@ -254,7 +255,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C31" authorId="0" shapeId="0">
+    <comment ref="C31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
@@ -278,7 +279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C38" authorId="0" shapeId="0">
+    <comment ref="C38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
         <r>
           <rPr>
@@ -302,7 +303,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C46" authorId="0" shapeId="0">
+    <comment ref="C46" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -326,7 +327,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C50" authorId="0" shapeId="0">
+    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -350,7 +351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C59" authorId="0" shapeId="0">
+    <comment ref="C59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -374,7 +375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C65" authorId="0" shapeId="0">
+    <comment ref="C65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -398,7 +399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C77" authorId="0" shapeId="0">
+    <comment ref="C77" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -422,7 +423,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C88" authorId="0" shapeId="0">
+    <comment ref="C88" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -446,7 +447,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C101" authorId="0" shapeId="0">
+    <comment ref="C101" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000010000000}">
       <text>
         <r>
           <rPr>
@@ -470,7 +471,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C110" authorId="0" shapeId="0">
+    <comment ref="C110" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000011000000}">
       <text>
         <r>
           <rPr>
@@ -494,7 +495,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C116" authorId="0" shapeId="0">
+    <comment ref="C116" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000012000000}">
       <text>
         <r>
           <rPr>
@@ -518,7 +519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C127" authorId="0" shapeId="0">
+    <comment ref="C127" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000013000000}">
       <text>
         <r>
           <rPr>
@@ -542,7 +543,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C137" authorId="0" shapeId="0">
+    <comment ref="C137" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000014000000}">
       <text>
         <r>
           <rPr>
@@ -566,7 +567,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C142" authorId="0" shapeId="0">
+    <comment ref="C142" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000015000000}">
       <text>
         <r>
           <rPr>
@@ -590,7 +591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C157" authorId="0" shapeId="0">
+    <comment ref="C157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000016000000}">
       <text>
         <r>
           <rPr>
@@ -614,7 +615,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C161" authorId="0" shapeId="0">
+    <comment ref="C161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000017000000}">
       <text>
         <r>
           <rPr>
@@ -638,7 +639,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C168" authorId="0" shapeId="0">
+    <comment ref="C168" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000018000000}">
       <text>
         <r>
           <rPr>
@@ -662,7 +663,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C174" authorId="0" shapeId="0">
+    <comment ref="C174" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000019000000}">
       <text>
         <r>
           <rPr>
@@ -691,12 +692,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -727,14 +728,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -749,7 +750,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="274">
   <si>
     <t>Work Item</t>
   </si>
@@ -2596,11 +2597,51 @@
 Ensure selected actives are compatible with selected base
 Generate formulation information</t>
   </si>
+  <si>
+    <t>Add POST API to create session in backend - /create_session
+Link POST /create_session with BEGIN ASSESMENT button in frontend</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Add in confidence values in skin_concerns.json 
+Rank skin concerns based on confidence scores ; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>threshold_value = ??</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Return top 6 ranked skin concerns to frontend </t>
+    </r>
+  </si>
+  <si>
+    <t>Rename skin concerns to a more user friendly option ( it should not look like a diagnosis)
+Modify the vision AI system prompt to ensure the returned explanations for skin concerns are more user friendly and less clinical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create database migrations
+while restoring (going back to async) image_intake_service.py ,do we have to decouple image-validation from image-analysis api or not
+Make db enums for processing error and completed </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11">
     <font>
       <sz val="11"/>
@@ -2797,7 +2838,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2896,8 +2937,26 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2906,29 +2965,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4112,9 +4166,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4152,9 +4206,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4189,7 +4243,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4224,7 +4278,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4396,34 +4450,26 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="E6" dT="2026-09-10T10:13:35.35" personId="{00000000-0000-0000-0000-000000000000}" id="{148E080D-CE22-4CE0-8311-B67C30FEF121}">
-    <text>Get client verification</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="35.7109375" customWidth="1"/>
-    <col min="5" max="5" width="51.140625" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" customWidth="1"/>
+    <col min="5" max="5" width="51.109375" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="10"/>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
     </row>
@@ -4447,7 +4493,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="105">
+    <row r="3" spans="1:6" ht="100.8">
       <c r="A3" s="16">
         <v>1</v>
       </c>
@@ -4498,7 +4544,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="90">
+    <row r="6" spans="1:6" ht="86.4">
       <c r="A6" s="15">
         <v>4</v>
       </c>
@@ -4549,32 +4595,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J181"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1">
       <c r="A2" s="10" t="s">
@@ -4609,7 +4655,7 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="47">
+      <c r="A3" s="53">
         <v>1</v>
       </c>
       <c r="B3" s="48">
@@ -4621,96 +4667,96 @@
       <c r="D3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="E3" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="45" cm="1">
+      <c r="F3" s="51" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="47"/>
+      <c r="A4" s="53"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="47"/>
+      <c r="A5" s="53"/>
       <c r="B5" s="48"/>
       <c r="C5" s="48"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="47"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="48"/>
       <c r="C6" s="48"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="47"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
       <c r="D7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="47"/>
+      <c r="A8" s="53"/>
       <c r="B8" s="48"/>
       <c r="C8" s="48"/>
       <c r="D8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="47"/>
+      <c r="A9" s="53"/>
       <c r="B9" s="48"/>
       <c r="C9" s="48"/>
       <c r="D9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="47"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="48"/>
       <c r="C10" s="48"/>
       <c r="D10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="47"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="47"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48">
         <v>1.2</v>
@@ -4718,36 +4764,36 @@
       <c r="D12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="45" t="s">
+      <c r="E12" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="45" cm="1">
+      <c r="F12" s="51" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="47"/>
+      <c r="A13" s="53"/>
       <c r="B13" s="48"/>
       <c r="C13" s="48"/>
       <c r="D13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="47"/>
+      <c r="A14" s="53"/>
       <c r="B14" s="48"/>
       <c r="C14" s="48"/>
       <c r="D14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="47"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="48"/>
       <c r="C15" s="48">
         <v>1.3</v>
@@ -4755,33 +4801,33 @@
       <c r="D15" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="45" t="s">
+      <c r="E15" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="45"/>
+      <c r="F15" s="51"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="47"/>
+      <c r="A16" s="53"/>
       <c r="B16" s="48"/>
       <c r="C16" s="48"/>
       <c r="D16" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="47"/>
+      <c r="A17" s="53"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
       <c r="D17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="47"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48">
         <v>1.4</v>
@@ -4789,84 +4835,84 @@
       <c r="D18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="45" t="s">
+      <c r="E18" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="45"/>
+      <c r="F18" s="51"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="47"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="47"/>
+      <c r="A20" s="53"/>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
       <c r="D20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="47"/>
+      <c r="A21" s="53"/>
       <c r="B21" s="48"/>
       <c r="C21" s="48"/>
       <c r="D21" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="47"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="48"/>
       <c r="C22" s="48"/>
       <c r="D22" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="47"/>
+      <c r="A23" s="53"/>
       <c r="B23" s="48"/>
       <c r="C23" s="48"/>
       <c r="D23" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="47"/>
+      <c r="A24" s="53"/>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
       <c r="D24" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="47"/>
+      <c r="A25" s="53"/>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
       <c r="D25" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="47"/>
-      <c r="B26" s="49">
+      <c r="A26" s="53"/>
+      <c r="B26" s="54">
         <v>2</v>
       </c>
       <c r="C26" s="48">
@@ -4875,359 +4921,359 @@
       <c r="D26" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E26" s="46" t="s">
+      <c r="E26" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="45"/>
+      <c r="F26" s="51"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="47"/>
-      <c r="B27" s="49"/>
+      <c r="A27" s="53"/>
+      <c r="B27" s="54"/>
       <c r="C27" s="48"/>
       <c r="D27" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="46"/>
-      <c r="F27" s="45"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="51"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="47"/>
-      <c r="B28" s="49"/>
+      <c r="A28" s="53"/>
+      <c r="B28" s="54"/>
       <c r="C28" s="48"/>
       <c r="D28" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E28" s="46"/>
-      <c r="F28" s="45"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="51"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="47"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="51">
+      <c r="A29" s="53"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="50">
         <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="45" t="s">
+      <c r="E29" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="45"/>
+      <c r="F29" s="51"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="47"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="51"/>
+      <c r="A30" s="53"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="50"/>
       <c r="D30" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="47"/>
-      <c r="B31" s="49"/>
+      <c r="A31" s="53"/>
+      <c r="B31" s="54"/>
       <c r="C31" s="48">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="45" t="s">
+      <c r="E31" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45" t="s">
+      <c r="F31" s="51"/>
+      <c r="G31" s="51" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="47"/>
-      <c r="B32" s="49"/>
+      <c r="A32" s="53"/>
+      <c r="B32" s="54"/>
       <c r="C32" s="48"/>
       <c r="D32" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="47"/>
-      <c r="B33" s="49"/>
+      <c r="A33" s="53"/>
+      <c r="B33" s="54"/>
       <c r="C33" s="48"/>
       <c r="D33" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="47"/>
-      <c r="B34" s="49"/>
+      <c r="A34" s="53"/>
+      <c r="B34" s="54"/>
       <c r="C34" s="48"/>
       <c r="D34" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="47"/>
-      <c r="B35" s="49"/>
+      <c r="A35" s="53"/>
+      <c r="B35" s="54"/>
       <c r="C35" s="48"/>
       <c r="D35" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="47"/>
-      <c r="B36" s="49"/>
+      <c r="A36" s="53"/>
+      <c r="B36" s="54"/>
       <c r="C36" s="48"/>
       <c r="D36" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="47"/>
-      <c r="B37" s="49"/>
+      <c r="A37" s="53"/>
+      <c r="B37" s="54"/>
       <c r="C37" s="48"/>
       <c r="D37" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="47"/>
-      <c r="B38" s="49"/>
+      <c r="A38" s="53"/>
+      <c r="B38" s="54"/>
       <c r="C38" s="48">
         <v>2.4</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E38" s="45" t="s">
+      <c r="E38" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="45"/>
+      <c r="F38" s="51"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="47"/>
-      <c r="B39" s="49"/>
+      <c r="A39" s="53"/>
+      <c r="B39" s="54"/>
       <c r="C39" s="48"/>
       <c r="D39" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="47"/>
-      <c r="B40" s="49"/>
+      <c r="A40" s="53"/>
+      <c r="B40" s="54"/>
       <c r="C40" s="48"/>
       <c r="D40" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="47"/>
-      <c r="B41" s="49"/>
+      <c r="A41" s="53"/>
+      <c r="B41" s="54"/>
       <c r="C41" s="48"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="45"/>
-      <c r="F41" s="45"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="47"/>
-      <c r="B42" s="49"/>
+      <c r="A42" s="53"/>
+      <c r="B42" s="54"/>
       <c r="C42" s="48"/>
       <c r="D42" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="51"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="47"/>
-      <c r="B43" s="49"/>
+      <c r="A43" s="53"/>
+      <c r="B43" s="54"/>
       <c r="C43" s="48"/>
       <c r="D43" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E43" s="45"/>
-      <c r="F43" s="45"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="51"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="47"/>
-      <c r="B44" s="49"/>
+      <c r="A44" s="53"/>
+      <c r="B44" s="54"/>
       <c r="C44" s="48"/>
       <c r="D44" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="51"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="47"/>
-      <c r="B45" s="49"/>
+      <c r="A45" s="53"/>
+      <c r="B45" s="54"/>
       <c r="C45" s="48"/>
       <c r="D45" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E45" s="45"/>
-      <c r="F45" s="45"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="47"/>
-      <c r="B46" s="49"/>
+      <c r="A46" s="53"/>
+      <c r="B46" s="54"/>
       <c r="C46" s="48">
         <v>2.5</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="E46" s="46" t="s">
+      <c r="E46" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="45"/>
+      <c r="F46" s="51"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="47"/>
-      <c r="B47" s="49"/>
+      <c r="A47" s="53"/>
+      <c r="B47" s="54"/>
       <c r="C47" s="48"/>
       <c r="D47" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E47" s="46"/>
-      <c r="F47" s="45"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="51"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="47"/>
-      <c r="B48" s="49"/>
+      <c r="A48" s="53"/>
+      <c r="B48" s="54"/>
       <c r="C48" s="48"/>
       <c r="D48" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E48" s="46"/>
-      <c r="F48" s="45"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="51"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="47"/>
-      <c r="B49" s="49"/>
+      <c r="A49" s="53"/>
+      <c r="B49" s="54"/>
       <c r="C49" s="48"/>
       <c r="D49" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E49" s="46"/>
-      <c r="F49" s="45"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="51"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="47"/>
-      <c r="B50" s="49"/>
+      <c r="A50" s="53"/>
+      <c r="B50" s="54"/>
       <c r="C50" s="48">
         <v>2.7</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E50" s="45" t="s">
+      <c r="E50" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F50" s="45"/>
+      <c r="F50" s="51"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="47"/>
-      <c r="B51" s="49"/>
+      <c r="A51" s="53"/>
+      <c r="B51" s="54"/>
       <c r="C51" s="48"/>
       <c r="D51" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="51"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="47"/>
-      <c r="B52" s="49"/>
+      <c r="A52" s="53"/>
+      <c r="B52" s="54"/>
       <c r="C52" s="48"/>
       <c r="D52" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E52" s="45"/>
-      <c r="F52" s="45"/>
+      <c r="E52" s="51"/>
+      <c r="F52" s="51"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="47"/>
-      <c r="B53" s="49"/>
+      <c r="A53" s="53"/>
+      <c r="B53" s="54"/>
       <c r="C53" s="48"/>
       <c r="D53" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E53" s="45"/>
-      <c r="F53" s="45"/>
+      <c r="E53" s="51"/>
+      <c r="F53" s="51"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="47"/>
-      <c r="B54" s="49"/>
+      <c r="A54" s="53"/>
+      <c r="B54" s="54"/>
       <c r="C54" s="48"/>
       <c r="D54" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E54" s="45"/>
-      <c r="F54" s="45"/>
+      <c r="E54" s="51"/>
+      <c r="F54" s="51"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="47"/>
-      <c r="B55" s="49"/>
+      <c r="A55" s="53"/>
+      <c r="B55" s="54"/>
       <c r="C55" s="48"/>
       <c r="D55" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E55" s="45"/>
-      <c r="F55" s="45"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="51"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="47"/>
-      <c r="B56" s="49"/>
+      <c r="A56" s="53"/>
+      <c r="B56" s="54"/>
       <c r="C56" s="48"/>
       <c r="D56" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="45"/>
-      <c r="F56" s="45"/>
+      <c r="E56" s="51"/>
+      <c r="F56" s="51"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="47"/>
-      <c r="B57" s="49"/>
+      <c r="A57" s="53"/>
+      <c r="B57" s="54"/>
       <c r="C57" s="48"/>
       <c r="D57" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E57" s="45"/>
-      <c r="F57" s="45"/>
+      <c r="E57" s="51"/>
+      <c r="F57" s="51"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="47"/>
-      <c r="B58" s="49"/>
+      <c r="A58" s="53"/>
+      <c r="B58" s="54"/>
       <c r="C58" s="48"/>
       <c r="D58" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E58" s="45"/>
-      <c r="F58" s="45"/>
+      <c r="E58" s="51"/>
+      <c r="F58" s="51"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
@@ -5916,7 +5962,7 @@
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
       <c r="B142" s="48"/>
-      <c r="C142" s="52">
+      <c r="C142" s="49">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -5926,7 +5972,7 @@
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
       <c r="B143" s="48"/>
-      <c r="C143" s="52"/>
+      <c r="C143" s="49"/>
       <c r="D143" s="7" t="s">
         <v>168</v>
       </c>
@@ -5934,7 +5980,7 @@
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
       <c r="B144" s="48"/>
-      <c r="C144" s="52"/>
+      <c r="C144" s="49"/>
       <c r="D144" s="7" t="s">
         <v>169</v>
       </c>
@@ -5942,7 +5988,7 @@
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
       <c r="B145" s="48"/>
-      <c r="C145" s="52"/>
+      <c r="C145" s="49"/>
       <c r="D145" s="7" t="s">
         <v>170</v>
       </c>
@@ -5950,7 +5996,7 @@
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
       <c r="B146" s="48"/>
-      <c r="C146" s="52"/>
+      <c r="C146" s="49"/>
       <c r="D146" s="7" t="s">
         <v>171</v>
       </c>
@@ -5958,7 +6004,7 @@
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
       <c r="B147" s="48"/>
-      <c r="C147" s="52"/>
+      <c r="C147" s="49"/>
       <c r="D147" s="7" t="s">
         <v>172</v>
       </c>
@@ -5966,7 +6012,7 @@
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
       <c r="B148" s="48"/>
-      <c r="C148" s="52"/>
+      <c r="C148" s="49"/>
       <c r="D148" s="7" t="s">
         <v>173</v>
       </c>
@@ -5974,7 +6020,7 @@
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
       <c r="B149" s="48"/>
-      <c r="C149" s="52"/>
+      <c r="C149" s="49"/>
       <c r="D149" s="7" t="s">
         <v>174</v>
       </c>
@@ -5982,7 +6028,7 @@
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
       <c r="B150" s="48"/>
-      <c r="C150" s="52"/>
+      <c r="C150" s="49"/>
       <c r="D150" s="7" t="s">
         <v>175</v>
       </c>
@@ -5990,7 +6036,7 @@
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
       <c r="B151" s="48"/>
-      <c r="C151" s="52"/>
+      <c r="C151" s="49"/>
       <c r="D151" s="7" t="s">
         <v>176</v>
       </c>
@@ -5998,7 +6044,7 @@
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
       <c r="B152" s="48"/>
-      <c r="C152" s="52"/>
+      <c r="C152" s="49"/>
       <c r="D152" s="7" t="s">
         <v>177</v>
       </c>
@@ -6006,7 +6052,7 @@
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
       <c r="B153" s="48"/>
-      <c r="C153" s="52"/>
+      <c r="C153" s="49"/>
       <c r="D153" s="7" t="s">
         <v>178</v>
       </c>
@@ -6014,7 +6060,7 @@
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
       <c r="B154" s="48"/>
-      <c r="C154" s="52"/>
+      <c r="C154" s="49"/>
       <c r="D154" s="7" t="s">
         <v>179</v>
       </c>
@@ -6022,7 +6068,7 @@
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
       <c r="B155" s="48"/>
-      <c r="C155" s="52"/>
+      <c r="C155" s="49"/>
       <c r="D155" s="7" t="s">
         <v>180</v>
       </c>
@@ -6030,7 +6076,7 @@
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
       <c r="B156" s="48"/>
-      <c r="C156" s="52"/>
+      <c r="C156" s="49"/>
       <c r="D156" s="7" t="s">
         <v>56</v>
       </c>
@@ -6246,8 +6292,43 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J181"/>
+  <autoFilter ref="A2:J181" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="51">
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -6264,41 +6345,6 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6307,32 +6353,32 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:L35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:12" s="4" customFormat="1">
       <c r="A2" s="32" t="s">
@@ -6370,11 +6416,11 @@
       </c>
       <c r="L2" s="40"/>
     </row>
-    <row r="3" spans="1:12" ht="135">
-      <c r="A3" s="53">
+    <row r="3" spans="1:12" ht="129.6">
+      <c r="A3" s="44">
         <v>1</v>
       </c>
-      <c r="B3" s="53">
+      <c r="B3" s="44">
         <v>1</v>
       </c>
       <c r="C3" s="15">
@@ -6397,9 +6443,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="60">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
+    <row r="4" spans="1:12" ht="57.6">
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
       <c r="C4" s="15">
         <v>1.2</v>
       </c>
@@ -6420,9 +6466,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="45">
-      <c r="A5" s="53"/>
-      <c r="B5" s="53"/>
+    <row r="5" spans="1:12" ht="43.2">
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
       <c r="C5" s="15">
         <v>1.3</v>
       </c>
@@ -6443,9 +6489,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="120">
-      <c r="A6" s="53"/>
-      <c r="B6" s="53"/>
+    <row r="6" spans="1:12" ht="115.2">
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
       <c r="C6" s="36">
         <v>1.4</v>
       </c>
@@ -6468,9 +6514,9 @@
       <c r="I6" s="38"/>
       <c r="J6" s="38"/>
     </row>
-    <row r="7" spans="1:12" ht="90">
-      <c r="A7" s="53"/>
-      <c r="B7" s="53">
+    <row r="7" spans="1:12" ht="72">
+      <c r="A7" s="44"/>
+      <c r="B7" s="44">
         <v>2</v>
       </c>
       <c r="C7" s="15">
@@ -6493,9 +6539,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="60">
-      <c r="A8" s="53"/>
-      <c r="B8" s="53"/>
+    <row r="8" spans="1:12" ht="57.6">
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
       <c r="C8" s="15">
         <v>2.2000000000000002</v>
       </c>
@@ -6516,9 +6562,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="105">
-      <c r="A9" s="53"/>
-      <c r="B9" s="53"/>
+    <row r="9" spans="1:12" ht="100.8">
+      <c r="A9" s="44"/>
+      <c r="B9" s="44"/>
       <c r="C9" s="15">
         <v>2.2999999999999998</v>
       </c>
@@ -6539,9 +6585,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="120">
-      <c r="A10" s="53"/>
-      <c r="B10" s="53"/>
+    <row r="10" spans="1:12" ht="115.2">
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
       <c r="C10" s="15">
         <v>2.4</v>
       </c>
@@ -6562,9 +6608,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="120">
-      <c r="A11" s="53"/>
-      <c r="B11" s="53"/>
+    <row r="11" spans="1:12" ht="100.8">
+      <c r="A11" s="44"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="15">
         <v>2.5</v>
       </c>
@@ -6585,9 +6631,9 @@
         <v>260</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="120">
-      <c r="A12" s="53"/>
-      <c r="B12" s="53"/>
+    <row r="12" spans="1:12" ht="115.2">
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
       <c r="C12" s="15">
         <v>2.6</v>
       </c>
@@ -6608,9 +6654,9 @@
         <v>261</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="165">
-      <c r="A13" s="53"/>
-      <c r="B13" s="53"/>
+    <row r="13" spans="1:12" ht="158.4">
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
       <c r="C13" s="36">
         <v>2.7</v>
       </c>
@@ -6633,7 +6679,7 @@
       <c r="I13" s="38"/>
       <c r="J13" s="38"/>
     </row>
-    <row r="14" spans="1:12" ht="165">
+    <row r="14" spans="1:12" ht="144">
       <c r="C14" s="41">
         <v>2.8</v>
       </c>
@@ -6673,181 +6719,245 @@
       <c r="I15" s="29"/>
       <c r="J15" s="31"/>
     </row>
-    <row r="16" spans="1:12" ht="90">
-      <c r="A16" s="54">
+    <row r="16" spans="1:12" ht="28.8">
+      <c r="A16" s="56"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="57">
+        <v>2.9</v>
+      </c>
+      <c r="D16" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="59"/>
+    </row>
+    <row r="17" spans="1:10" ht="57.6">
+      <c r="A17" s="56"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="60">
+        <v>2.1</v>
+      </c>
+      <c r="D17" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="59"/>
+    </row>
+    <row r="18" spans="1:10" ht="43.2">
+      <c r="A18" s="56"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="60">
+        <v>2.11</v>
+      </c>
+      <c r="D18" s="58" t="s">
+        <v>271</v>
+      </c>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="59"/>
+    </row>
+    <row r="19" spans="1:10" ht="43.2">
+      <c r="A19" s="56"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="60">
+        <v>2.12</v>
+      </c>
+      <c r="D19" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
+    </row>
+    <row r="20" spans="1:10" ht="86.4">
+      <c r="A20" s="45">
         <v>2</v>
       </c>
-      <c r="B16" s="54">
+      <c r="B20" s="45">
         <v>3</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C20" s="15">
         <v>3.1</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="90">
-      <c r="A17" s="53"/>
-      <c r="B17" s="53"/>
-      <c r="C17" s="15">
+    <row r="21" spans="1:10" ht="86.4">
+      <c r="A21" s="44"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="15">
         <v>3.2</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="90">
-      <c r="A18" s="53"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="15">
+    <row r="22" spans="1:10" ht="86.4">
+      <c r="A22" s="44"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="15">
         <v>3.3</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="165">
-      <c r="A19" s="53"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="15">
+    <row r="23" spans="1:10" ht="158.4">
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="15">
         <v>3.4</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="105">
-      <c r="A20" s="53"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="15">
+    <row r="24" spans="1:10" ht="100.8">
+      <c r="A24" s="44"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="15">
         <v>3.5</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="120">
-      <c r="A21" s="53"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="15">
+    <row r="25" spans="1:10" ht="115.2">
+      <c r="A25" s="44"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="15">
         <v>3.6</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="53"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="15">
+    <row r="26" spans="1:10">
+      <c r="A26" s="44"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="15">
         <v>3.7</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="90">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="15">
+    <row r="27" spans="1:10" ht="86.4">
+      <c r="A27" s="44"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="15">
         <v>3.8</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="165">
-      <c r="A24" s="53"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="15">
+    <row r="28" spans="1:10" ht="158.4">
+      <c r="A28" s="44"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="15">
         <v>3.9</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="150">
-      <c r="A25" s="53"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="35">
+    <row r="29" spans="1:10" ht="144">
+      <c r="A29" s="44"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="35">
         <v>3.1</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="75">
-      <c r="A26" s="53"/>
-      <c r="B26" s="53"/>
-      <c r="C26" s="15">
+    <row r="30" spans="1:10" ht="72">
+      <c r="A30" s="44"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="15">
         <v>3.11</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="225">
-      <c r="A27" s="53"/>
-      <c r="B27" s="53"/>
-      <c r="C27" s="35">
+    <row r="31" spans="1:10" ht="216">
+      <c r="A31" s="44"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="35">
         <v>3.12</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="60">
-      <c r="A28" s="53"/>
-      <c r="B28" s="53">
+    <row r="32" spans="1:10" ht="57.6">
+      <c r="A32" s="44"/>
+      <c r="B32" s="44">
         <v>4</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C32" s="15">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="105">
-      <c r="A29" s="53"/>
-      <c r="B29" s="53"/>
-      <c r="C29" s="15">
+    <row r="33" spans="1:4" ht="100.8">
+      <c r="A33" s="44"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="15">
         <v>4.2</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="90">
-      <c r="A30" s="53"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="15">
+    <row r="34" spans="1:4" ht="86.4">
+      <c r="A34" s="44"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="15">
         <v>4.3</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="120">
-      <c r="A31" s="53"/>
-      <c r="B31" s="53"/>
-      <c r="C31" s="15">
+    <row r="35" spans="1:4" ht="115.2">
+      <c r="A35" s="44"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="15">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>244</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="A16:A31"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="A20:A35"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="B7:B13"/>
-    <mergeCell ref="B16:B27"/>
+    <mergeCell ref="B20:B31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6856,17 +6966,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="60">
+    <row r="1" spans="1:5" ht="57.6">
       <c r="A1" s="22" t="s">
         <v>214</v>
       </c>
@@ -7064,9 +7174,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="55" t="s">

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B3398E-200A-452E-81A1-E9A31A4AA09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="13170" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="4" r:id="rId1"/>
@@ -17,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sprint Backlog'!$A$2:$J$181</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,12 +34,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -57,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="E6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -79,12 +78,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="H2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -110,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -134,7 +133,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+    <comment ref="C12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -158,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
+    <comment ref="C15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -182,7 +181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
+    <comment ref="C18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -206,7 +205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
+    <comment ref="C26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -231,7 +230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
+    <comment ref="C29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -255,7 +254,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
+    <comment ref="C31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -279,7 +278,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
+    <comment ref="C38" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -303,7 +302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C46" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
+    <comment ref="C46" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -327,7 +326,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
+    <comment ref="C50" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -351,7 +350,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
+    <comment ref="C59" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -375,7 +374,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000D000000}">
+    <comment ref="C65" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -399,7 +398,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C77" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
+    <comment ref="C77" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -423,7 +422,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C88" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000F000000}">
+    <comment ref="C88" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -447,7 +446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C101" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000010000000}">
+    <comment ref="C101" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -471,7 +470,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C110" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000011000000}">
+    <comment ref="C110" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -495,7 +494,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C116" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000012000000}">
+    <comment ref="C116" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -519,7 +518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C127" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000013000000}">
+    <comment ref="C127" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -543,7 +542,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C137" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000014000000}">
+    <comment ref="C137" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -567,7 +566,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C142" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000015000000}">
+    <comment ref="C142" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -591,7 +590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000016000000}">
+    <comment ref="C157" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -615,7 +614,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000017000000}">
+    <comment ref="C161" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -639,7 +638,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C168" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000018000000}">
+    <comment ref="C168" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -663,7 +662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C174" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000019000000}">
+    <comment ref="C174" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -692,12 +691,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="H2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -728,14 +727,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -750,7 +749,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="279">
   <si>
     <t>Work Item</t>
   </si>
@@ -1903,14 +1902,6 @@
   </si>
   <si>
     <t>Total Sprint Story Points</t>
-  </si>
-  <si>
-    <t>Display questionnaire to user
-Collect questionnaire answers
-Validate required questionnaire fields
-Store questionnaire answers in questionnaire_response
-Associate questionnaire response with current customer_session
-Submit questionnaire for LLM analysis</t>
   </si>
   <si>
     <t>Retrieve image-based detection results
@@ -2598,12 +2589,32 @@
 Generate formulation information</t>
   </si>
   <si>
-    <t>Add POST API to create session in backend - /create_session
-Link POST /create_session with BEGIN ASSESMENT button in frontend</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Add in confidence values in skin_concerns.json 
+    <t>Rename skin concerns to a more user friendly option ( it should not look like a diagnosis)
+Modify the vision AI system prompt to ensure the returned explanations for skin concerns are more user friendly and less clinical</t>
+  </si>
+  <si>
+    <t>Create database migrations</t>
+  </si>
+  <si>
+    <t>{=_xlfn.SWITCH(E11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")}</t>
+  </si>
+  <si>
+    <t>Revise db tables and model contracts (DML)</t>
+  </si>
+  <si>
+    <t>Azad, Vidit</t>
+  </si>
+  <si>
+    <t>restore codebase to async
+while restoring (going back to async) image_intake_service.py 
+decouple image-validation from image-analysis api or not
+Make db enums for processing error and completed 
+db enums for workers : "analysis_status" : PENDING ; PROCESSING; COMPLETED; ERROR; DEFAULT:PENDING (NOT NULL CONSTRAINT) 
+STARTED AT ; COMPLETED AT</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Add in confidence values in skin_concerns.json and define in system prompt
 Rank skin concerns based on confidence scores ; </t>
     </r>
     <r>
@@ -2629,19 +2640,28 @@
     </r>
   </si>
   <si>
-    <t>Rename skin concerns to a more user friendly option ( it should not look like a diagnosis)
-Modify the vision AI system prompt to ensure the returned explanations for skin concerns are more user friendly and less clinical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create database migrations
-while restoring (going back to async) image_intake_service.py ,do we have to decouple image-validation from image-analysis api or not
-Make db enums for processing error and completed </t>
+    <t>Create a consent checkbox : "I agree to share my image for AI analysis"
+Add POST API to create session in backend  /create-session
+Construct incoming and outgoing payload for the api
+Link POST /create-session with BEGIN ASSESMENT button in frontend
+Make a SessionStorage in frontend and store session_id from create-session API response in this storage.</t>
+  </si>
+  <si>
+    <t>session id required for every API</t>
+  </si>
+  <si>
+    <t>Display questionnaire to user
+Collect questionnaire answers
+Validate required questionnaire fields (frontend only)
+Store questionnaire answers in questionnaire_response
+Associate questionnaire response with current customer_session
+Call questionnaire LLM analysis API</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="11">
     <font>
       <sz val="11"/>
@@ -2838,7 +2858,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2940,23 +2960,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2965,25 +2971,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3123,28 +3135,28 @@
                   <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>39</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>39</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>36</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>31</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>30</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>30</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3225,28 +3237,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>45</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>39.375</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>33.75</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28.125</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>22.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>16.875</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11.25</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.625</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -4166,9 +4178,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4206,9 +4218,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4243,7 +4255,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4278,7 +4290,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4451,25 +4463,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="35.6640625" customWidth="1"/>
-    <col min="5" max="5" width="51.109375" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" customWidth="1"/>
+    <col min="5" max="5" width="51.140625" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="10"/>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
     </row>
@@ -4493,7 +4505,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="100.8">
+    <row r="3" spans="1:6" ht="105">
       <c r="A3" s="16">
         <v>1</v>
       </c>
@@ -4538,13 +4550,13 @@
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="86.4">
+    </row>
+    <row r="6" spans="1:6" ht="90">
       <c r="A6" s="15">
         <v>4</v>
       </c>
@@ -4595,32 +4607,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J181"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1">
       <c r="A2" s="10" t="s">
@@ -4655,632 +4667,632 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="53">
+      <c r="A3" s="49">
         <v>1</v>
       </c>
-      <c r="B3" s="48">
+      <c r="B3" s="50">
         <v>1</v>
       </c>
-      <c r="C3" s="48">
+      <c r="C3" s="50">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="51" cm="1">
+      <c r="F3" s="47" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="53"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
       <c r="D4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="53"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
+      <c r="A5" s="49"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="53"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="53"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
       <c r="D7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="53"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
       <c r="D8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="53"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="50"/>
       <c r="D9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="53"/>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
+      <c r="A10" s="49"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="50"/>
       <c r="D10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="53"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="53"/>
-      <c r="B12" s="48"/>
-      <c r="C12" s="48">
+      <c r="A12" s="49"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50">
         <v>1.2</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="E12" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="51" cm="1">
+      <c r="F12" s="47" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="53"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="53"/>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
+      <c r="A14" s="49"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="53"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48">
+      <c r="A15" s="49"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="50">
         <v>1.3</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="51" t="s">
+      <c r="E15" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="51"/>
+      <c r="F15" s="47"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="53"/>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
+      <c r="A16" s="49"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
       <c r="D16" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="53"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
+      <c r="A17" s="49"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="53"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48">
+      <c r="A18" s="49"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50">
         <v>1.4</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="51"/>
+      <c r="F18" s="47"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="53"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
+      <c r="A19" s="49"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
       <c r="D19" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="53"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="48"/>
+      <c r="A20" s="49"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="50"/>
       <c r="D20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="53"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="48"/>
+      <c r="A21" s="49"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="50"/>
       <c r="D21" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="53"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
+      <c r="A22" s="49"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50"/>
       <c r="D22" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="53"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="48"/>
+      <c r="A23" s="49"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
       <c r="D23" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="53"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
+      <c r="A24" s="49"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="50"/>
       <c r="D24" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="53"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
+      <c r="A25" s="49"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
       <c r="D25" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="53"/>
-      <c r="B26" s="54">
+      <c r="A26" s="49"/>
+      <c r="B26" s="51">
         <v>2</v>
       </c>
-      <c r="C26" s="48">
+      <c r="C26" s="50">
         <v>2.1</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E26" s="52" t="s">
+      <c r="E26" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="51"/>
+      <c r="F26" s="47"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="53"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="48"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="50"/>
       <c r="D27" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="52"/>
-      <c r="F27" s="51"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="47"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="53"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="48"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="50"/>
       <c r="D28" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E28" s="52"/>
-      <c r="F28" s="51"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="47"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="53"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="50">
+      <c r="A29" s="49"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="53">
         <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="51" t="s">
+      <c r="E29" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="51"/>
+      <c r="F29" s="47"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="53"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="50"/>
+      <c r="A30" s="49"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="53"/>
       <c r="D30" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="53"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="48">
+      <c r="A31" s="49"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="50">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="51" t="s">
+      <c r="E31" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51" t="s">
+      <c r="F31" s="47"/>
+      <c r="G31" s="47" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="53"/>
-      <c r="B32" s="54"/>
-      <c r="C32" s="48"/>
+      <c r="A32" s="49"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="50"/>
       <c r="D32" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="53"/>
-      <c r="B33" s="54"/>
-      <c r="C33" s="48"/>
+      <c r="A33" s="49"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="50"/>
       <c r="D33" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="53"/>
-      <c r="B34" s="54"/>
-      <c r="C34" s="48"/>
+      <c r="A34" s="49"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="50"/>
       <c r="D34" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E34" s="51"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="53"/>
-      <c r="B35" s="54"/>
-      <c r="C35" s="48"/>
+      <c r="A35" s="49"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="50"/>
       <c r="D35" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="53"/>
-      <c r="B36" s="54"/>
-      <c r="C36" s="48"/>
+      <c r="A36" s="49"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="50"/>
       <c r="D36" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="53"/>
-      <c r="B37" s="54"/>
-      <c r="C37" s="48"/>
+      <c r="A37" s="49"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="50"/>
       <c r="D37" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
+      <c r="E37" s="47"/>
+      <c r="F37" s="47"/>
+      <c r="G37" s="47"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="53"/>
-      <c r="B38" s="54"/>
-      <c r="C38" s="48">
+      <c r="A38" s="49"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="50">
         <v>2.4</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E38" s="51" t="s">
+      <c r="E38" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="51"/>
+      <c r="F38" s="47"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="53"/>
-      <c r="B39" s="54"/>
-      <c r="C39" s="48"/>
+      <c r="A39" s="49"/>
+      <c r="B39" s="51"/>
+      <c r="C39" s="50"/>
       <c r="D39" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="53"/>
-      <c r="B40" s="54"/>
-      <c r="C40" s="48"/>
+      <c r="A40" s="49"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="50"/>
       <c r="D40" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="53"/>
-      <c r="B41" s="54"/>
-      <c r="C41" s="48"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="51"/>
+      <c r="C41" s="50"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="53"/>
-      <c r="B42" s="54"/>
-      <c r="C42" s="48"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="50"/>
       <c r="D42" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="53"/>
-      <c r="B43" s="54"/>
-      <c r="C43" s="48"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="50"/>
       <c r="D43" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E43" s="51"/>
-      <c r="F43" s="51"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="47"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="53"/>
-      <c r="B44" s="54"/>
-      <c r="C44" s="48"/>
+      <c r="A44" s="49"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="50"/>
       <c r="D44" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E44" s="51"/>
-      <c r="F44" s="51"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="53"/>
-      <c r="B45" s="54"/>
-      <c r="C45" s="48"/>
+      <c r="A45" s="49"/>
+      <c r="B45" s="51"/>
+      <c r="C45" s="50"/>
       <c r="D45" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="53"/>
-      <c r="B46" s="54"/>
-      <c r="C46" s="48">
+      <c r="A46" s="49"/>
+      <c r="B46" s="51"/>
+      <c r="C46" s="50">
         <v>2.5</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="E46" s="52" t="s">
+      <c r="E46" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="51"/>
+      <c r="F46" s="47"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="53"/>
-      <c r="B47" s="54"/>
-      <c r="C47" s="48"/>
+      <c r="A47" s="49"/>
+      <c r="B47" s="51"/>
+      <c r="C47" s="50"/>
       <c r="D47" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E47" s="52"/>
-      <c r="F47" s="51"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="47"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="53"/>
-      <c r="B48" s="54"/>
-      <c r="C48" s="48"/>
+      <c r="A48" s="49"/>
+      <c r="B48" s="51"/>
+      <c r="C48" s="50"/>
       <c r="D48" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E48" s="52"/>
-      <c r="F48" s="51"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="47"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="53"/>
-      <c r="B49" s="54"/>
-      <c r="C49" s="48"/>
+      <c r="A49" s="49"/>
+      <c r="B49" s="51"/>
+      <c r="C49" s="50"/>
       <c r="D49" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E49" s="52"/>
-      <c r="F49" s="51"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="47"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="53"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="48">
+      <c r="A50" s="49"/>
+      <c r="B50" s="51"/>
+      <c r="C50" s="50">
         <v>2.7</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E50" s="51" t="s">
+      <c r="E50" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="F50" s="51"/>
+      <c r="F50" s="47"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="53"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="48"/>
+      <c r="A51" s="49"/>
+      <c r="B51" s="51"/>
+      <c r="C51" s="50"/>
       <c r="D51" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E51" s="51"/>
-      <c r="F51" s="51"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="47"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="53"/>
-      <c r="B52" s="54"/>
-      <c r="C52" s="48"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="51"/>
+      <c r="C52" s="50"/>
       <c r="D52" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E52" s="51"/>
-      <c r="F52" s="51"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="47"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="53"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="48"/>
+      <c r="A53" s="49"/>
+      <c r="B53" s="51"/>
+      <c r="C53" s="50"/>
       <c r="D53" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E53" s="51"/>
-      <c r="F53" s="51"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="47"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="53"/>
-      <c r="B54" s="54"/>
-      <c r="C54" s="48"/>
+      <c r="A54" s="49"/>
+      <c r="B54" s="51"/>
+      <c r="C54" s="50"/>
       <c r="D54" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E54" s="51"/>
-      <c r="F54" s="51"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="47"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="53"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="48"/>
+      <c r="A55" s="49"/>
+      <c r="B55" s="51"/>
+      <c r="C55" s="50"/>
       <c r="D55" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E55" s="51"/>
-      <c r="F55" s="51"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="47"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="53"/>
-      <c r="B56" s="54"/>
-      <c r="C56" s="48"/>
+      <c r="A56" s="49"/>
+      <c r="B56" s="51"/>
+      <c r="C56" s="50"/>
       <c r="D56" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="51"/>
-      <c r="F56" s="51"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="47"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="53"/>
-      <c r="B57" s="54"/>
-      <c r="C57" s="48"/>
+      <c r="A57" s="49"/>
+      <c r="B57" s="51"/>
+      <c r="C57" s="50"/>
       <c r="D57" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E57" s="51"/>
-      <c r="F57" s="51"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="47"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="53"/>
-      <c r="B58" s="54"/>
-      <c r="C58" s="48"/>
+      <c r="A58" s="49"/>
+      <c r="B58" s="51"/>
+      <c r="C58" s="50"/>
       <c r="D58" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E58" s="51"/>
-      <c r="F58" s="51"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="47"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
-      <c r="B59" s="48">
+      <c r="B59" s="50">
         <v>3</v>
       </c>
-      <c r="C59" s="48">
+      <c r="C59" s="50">
         <v>3.1</v>
       </c>
       <c r="D59" s="7" t="s">
@@ -5289,48 +5301,48 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="19"/>
-      <c r="B60" s="48"/>
-      <c r="C60" s="48"/>
+      <c r="B60" s="50"/>
+      <c r="C60" s="50"/>
       <c r="D60" s="7" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="19"/>
-      <c r="B61" s="48"/>
-      <c r="C61" s="48"/>
+      <c r="B61" s="50"/>
+      <c r="C61" s="50"/>
       <c r="D61" s="7" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="19"/>
-      <c r="B62" s="48"/>
-      <c r="C62" s="48"/>
+      <c r="B62" s="50"/>
+      <c r="C62" s="50"/>
       <c r="D62" s="7" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="19"/>
-      <c r="B63" s="48"/>
-      <c r="C63" s="48"/>
+      <c r="B63" s="50"/>
+      <c r="C63" s="50"/>
       <c r="D63" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="19"/>
-      <c r="B64" s="48"/>
-      <c r="C64" s="48"/>
+      <c r="B64" s="50"/>
+      <c r="C64" s="50"/>
       <c r="D64" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="19"/>
-      <c r="B65" s="48"/>
-      <c r="C65" s="48">
+      <c r="B65" s="50"/>
+      <c r="C65" s="50">
         <v>3.2</v>
       </c>
       <c r="D65" s="7" t="s">
@@ -5339,96 +5351,96 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="19"/>
-      <c r="B66" s="48"/>
-      <c r="C66" s="48"/>
+      <c r="B66" s="50"/>
+      <c r="C66" s="50"/>
       <c r="D66" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="19"/>
-      <c r="B67" s="48"/>
-      <c r="C67" s="48"/>
+      <c r="B67" s="50"/>
+      <c r="C67" s="50"/>
       <c r="D67" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="19"/>
-      <c r="B68" s="48"/>
-      <c r="C68" s="48"/>
+      <c r="B68" s="50"/>
+      <c r="C68" s="50"/>
       <c r="D68" s="7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="19"/>
-      <c r="B69" s="48"/>
-      <c r="C69" s="48"/>
+      <c r="B69" s="50"/>
+      <c r="C69" s="50"/>
       <c r="D69" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="19"/>
-      <c r="B70" s="48"/>
-      <c r="C70" s="48"/>
+      <c r="B70" s="50"/>
+      <c r="C70" s="50"/>
       <c r="D70" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="19"/>
-      <c r="B71" s="48"/>
-      <c r="C71" s="48"/>
+      <c r="B71" s="50"/>
+      <c r="C71" s="50"/>
       <c r="D71" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="19"/>
-      <c r="B72" s="48"/>
-      <c r="C72" s="48"/>
+      <c r="B72" s="50"/>
+      <c r="C72" s="50"/>
       <c r="D72" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="19"/>
-      <c r="B73" s="48"/>
-      <c r="C73" s="48"/>
+      <c r="B73" s="50"/>
+      <c r="C73" s="50"/>
       <c r="D73" s="7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="19"/>
-      <c r="B74" s="48"/>
-      <c r="C74" s="48"/>
+      <c r="B74" s="50"/>
+      <c r="C74" s="50"/>
       <c r="D74" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="19"/>
-      <c r="B75" s="48"/>
-      <c r="C75" s="48"/>
+      <c r="B75" s="50"/>
+      <c r="C75" s="50"/>
       <c r="D75" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="19"/>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
+      <c r="B76" s="50"/>
+      <c r="C76" s="50"/>
       <c r="D76" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="19"/>
-      <c r="B77" s="48"/>
-      <c r="C77" s="48">
+      <c r="B77" s="50"/>
+      <c r="C77" s="50">
         <v>3.3</v>
       </c>
       <c r="D77" s="7" t="s">
@@ -5437,88 +5449,88 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="19"/>
-      <c r="B78" s="48"/>
-      <c r="C78" s="48"/>
+      <c r="B78" s="50"/>
+      <c r="C78" s="50"/>
       <c r="D78" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="19"/>
-      <c r="B79" s="48"/>
-      <c r="C79" s="48"/>
+      <c r="B79" s="50"/>
+      <c r="C79" s="50"/>
       <c r="D79" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="19"/>
-      <c r="B80" s="48"/>
-      <c r="C80" s="48"/>
+      <c r="B80" s="50"/>
+      <c r="C80" s="50"/>
       <c r="D80" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="19"/>
-      <c r="B81" s="48"/>
-      <c r="C81" s="48"/>
+      <c r="B81" s="50"/>
+      <c r="C81" s="50"/>
       <c r="D81" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="19"/>
-      <c r="B82" s="48"/>
-      <c r="C82" s="48"/>
+      <c r="B82" s="50"/>
+      <c r="C82" s="50"/>
       <c r="D82" s="7" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="19"/>
-      <c r="B83" s="48"/>
-      <c r="C83" s="48"/>
+      <c r="B83" s="50"/>
+      <c r="C83" s="50"/>
       <c r="D83" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="19"/>
-      <c r="B84" s="48"/>
-      <c r="C84" s="48"/>
+      <c r="B84" s="50"/>
+      <c r="C84" s="50"/>
       <c r="D84" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="19"/>
-      <c r="B85" s="48"/>
-      <c r="C85" s="48"/>
+      <c r="B85" s="50"/>
+      <c r="C85" s="50"/>
       <c r="D85" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="19"/>
-      <c r="B86" s="48"/>
-      <c r="C86" s="48"/>
+      <c r="B86" s="50"/>
+      <c r="C86" s="50"/>
       <c r="D86" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="19"/>
-      <c r="B87" s="48"/>
-      <c r="C87" s="48"/>
+      <c r="B87" s="50"/>
+      <c r="C87" s="50"/>
       <c r="D87" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="19"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="48">
+      <c r="B88" s="50"/>
+      <c r="C88" s="50">
         <v>3.4</v>
       </c>
       <c r="D88" s="15" t="s">
@@ -5527,104 +5539,104 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="19"/>
-      <c r="B89" s="48"/>
-      <c r="C89" s="48"/>
+      <c r="B89" s="50"/>
+      <c r="C89" s="50"/>
       <c r="D89" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="19"/>
-      <c r="B90" s="48"/>
-      <c r="C90" s="48"/>
+      <c r="B90" s="50"/>
+      <c r="C90" s="50"/>
       <c r="D90" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="19"/>
-      <c r="B91" s="48"/>
-      <c r="C91" s="48"/>
+      <c r="B91" s="50"/>
+      <c r="C91" s="50"/>
       <c r="D91" s="7" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="19"/>
-      <c r="B92" s="48"/>
-      <c r="C92" s="48"/>
+      <c r="B92" s="50"/>
+      <c r="C92" s="50"/>
       <c r="D92" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="19"/>
-      <c r="B93" s="48"/>
-      <c r="C93" s="48"/>
+      <c r="B93" s="50"/>
+      <c r="C93" s="50"/>
       <c r="D93" s="7" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="19"/>
-      <c r="B94" s="48"/>
-      <c r="C94" s="48"/>
+      <c r="B94" s="50"/>
+      <c r="C94" s="50"/>
       <c r="D94" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="19"/>
-      <c r="B95" s="48"/>
-      <c r="C95" s="48"/>
+      <c r="B95" s="50"/>
+      <c r="C95" s="50"/>
       <c r="D95" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="19"/>
-      <c r="B96" s="48"/>
-      <c r="C96" s="48"/>
+      <c r="B96" s="50"/>
+      <c r="C96" s="50"/>
       <c r="D96" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="19"/>
-      <c r="B97" s="48"/>
-      <c r="C97" s="48"/>
+      <c r="B97" s="50"/>
+      <c r="C97" s="50"/>
       <c r="D97" s="7" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="19"/>
-      <c r="B98" s="48"/>
-      <c r="C98" s="48"/>
+      <c r="B98" s="50"/>
+      <c r="C98" s="50"/>
       <c r="D98" s="7" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="19"/>
-      <c r="B99" s="48"/>
-      <c r="C99" s="48"/>
+      <c r="B99" s="50"/>
+      <c r="C99" s="50"/>
       <c r="D99" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="19"/>
-      <c r="B100" s="48"/>
-      <c r="C100" s="48"/>
+      <c r="B100" s="50"/>
+      <c r="C100" s="50"/>
       <c r="D100" s="7" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="19"/>
-      <c r="B101" s="48"/>
-      <c r="C101" s="48">
+      <c r="B101" s="50"/>
+      <c r="C101" s="50">
         <v>3.5</v>
       </c>
       <c r="D101" s="11" t="s">
@@ -5633,72 +5645,72 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="19"/>
-      <c r="B102" s="48"/>
-      <c r="C102" s="48"/>
+      <c r="B102" s="50"/>
+      <c r="C102" s="50"/>
       <c r="D102" s="7" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="19"/>
-      <c r="B103" s="48"/>
-      <c r="C103" s="48"/>
+      <c r="B103" s="50"/>
+      <c r="C103" s="50"/>
       <c r="D103" s="7" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="19"/>
-      <c r="B104" s="48"/>
-      <c r="C104" s="48"/>
+      <c r="B104" s="50"/>
+      <c r="C104" s="50"/>
       <c r="D104" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="19"/>
-      <c r="B105" s="48"/>
-      <c r="C105" s="48"/>
+      <c r="B105" s="50"/>
+      <c r="C105" s="50"/>
       <c r="D105" s="7" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="19"/>
-      <c r="B106" s="48"/>
-      <c r="C106" s="48"/>
+      <c r="B106" s="50"/>
+      <c r="C106" s="50"/>
       <c r="D106" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="19"/>
-      <c r="B107" s="48"/>
-      <c r="C107" s="48"/>
+      <c r="B107" s="50"/>
+      <c r="C107" s="50"/>
       <c r="D107" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="19"/>
-      <c r="B108" s="48"/>
-      <c r="C108" s="48"/>
+      <c r="B108" s="50"/>
+      <c r="C108" s="50"/>
       <c r="D108" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="19"/>
-      <c r="B109" s="48"/>
-      <c r="C109" s="48"/>
+      <c r="B109" s="50"/>
+      <c r="C109" s="50"/>
       <c r="D109" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="19"/>
-      <c r="B110" s="48"/>
-      <c r="C110" s="48">
+      <c r="B110" s="50"/>
+      <c r="C110" s="50">
         <v>3.6</v>
       </c>
       <c r="D110" s="7" t="s">
@@ -5707,48 +5719,48 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19"/>
-      <c r="B111" s="48"/>
-      <c r="C111" s="48"/>
+      <c r="B111" s="50"/>
+      <c r="C111" s="50"/>
       <c r="D111" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19"/>
-      <c r="B112" s="48"/>
-      <c r="C112" s="48"/>
+      <c r="B112" s="50"/>
+      <c r="C112" s="50"/>
       <c r="D112" s="7" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="19"/>
-      <c r="B113" s="48"/>
-      <c r="C113" s="48"/>
+      <c r="B113" s="50"/>
+      <c r="C113" s="50"/>
       <c r="D113" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="19"/>
-      <c r="B114" s="48"/>
-      <c r="C114" s="48"/>
+      <c r="B114" s="50"/>
+      <c r="C114" s="50"/>
       <c r="D114" s="7" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="19"/>
-      <c r="B115" s="48"/>
-      <c r="C115" s="48"/>
+      <c r="B115" s="50"/>
+      <c r="C115" s="50"/>
       <c r="D115" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="19"/>
-      <c r="B116" s="48"/>
-      <c r="C116" s="48">
+      <c r="B116" s="50"/>
+      <c r="C116" s="50">
         <v>3.7</v>
       </c>
       <c r="D116" s="7" t="s">
@@ -5757,88 +5769,88 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="19"/>
-      <c r="B117" s="48"/>
-      <c r="C117" s="48"/>
+      <c r="B117" s="50"/>
+      <c r="C117" s="50"/>
       <c r="D117" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="19"/>
-      <c r="B118" s="48"/>
-      <c r="C118" s="48"/>
+      <c r="B118" s="50"/>
+      <c r="C118" s="50"/>
       <c r="D118" s="7" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="19"/>
-      <c r="B119" s="48"/>
-      <c r="C119" s="48"/>
+      <c r="B119" s="50"/>
+      <c r="C119" s="50"/>
       <c r="D119" s="7" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="19"/>
-      <c r="B120" s="48"/>
-      <c r="C120" s="48"/>
+      <c r="B120" s="50"/>
+      <c r="C120" s="50"/>
       <c r="D120" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="19"/>
-      <c r="B121" s="48"/>
-      <c r="C121" s="48"/>
+      <c r="B121" s="50"/>
+      <c r="C121" s="50"/>
       <c r="D121" s="7" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="19"/>
-      <c r="B122" s="48"/>
-      <c r="C122" s="48"/>
+      <c r="B122" s="50"/>
+      <c r="C122" s="50"/>
       <c r="D122" s="7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="19"/>
-      <c r="B123" s="48"/>
-      <c r="C123" s="48"/>
+      <c r="B123" s="50"/>
+      <c r="C123" s="50"/>
       <c r="D123" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="19"/>
-      <c r="B124" s="48"/>
-      <c r="C124" s="48"/>
+      <c r="B124" s="50"/>
+      <c r="C124" s="50"/>
       <c r="D124" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="19"/>
-      <c r="B125" s="48"/>
-      <c r="C125" s="48"/>
+      <c r="B125" s="50"/>
+      <c r="C125" s="50"/>
       <c r="D125" s="7" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="19"/>
-      <c r="B126" s="48"/>
-      <c r="C126" s="48"/>
+      <c r="B126" s="50"/>
+      <c r="C126" s="50"/>
       <c r="D126" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="19"/>
-      <c r="B127" s="48"/>
-      <c r="C127" s="48">
+      <c r="B127" s="50"/>
+      <c r="C127" s="50">
         <v>3.8</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -5847,80 +5859,80 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="19"/>
-      <c r="B128" s="48"/>
-      <c r="C128" s="48"/>
+      <c r="B128" s="50"/>
+      <c r="C128" s="50"/>
       <c r="D128" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="19"/>
-      <c r="B129" s="48"/>
-      <c r="C129" s="48"/>
+      <c r="B129" s="50"/>
+      <c r="C129" s="50"/>
       <c r="D129" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="19"/>
-      <c r="B130" s="48"/>
-      <c r="C130" s="48"/>
+      <c r="B130" s="50"/>
+      <c r="C130" s="50"/>
       <c r="D130" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="19"/>
-      <c r="B131" s="48"/>
-      <c r="C131" s="48"/>
+      <c r="B131" s="50"/>
+      <c r="C131" s="50"/>
       <c r="D131" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="19"/>
-      <c r="B132" s="48"/>
-      <c r="C132" s="48"/>
+      <c r="B132" s="50"/>
+      <c r="C132" s="50"/>
       <c r="D132" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="19"/>
-      <c r="B133" s="48"/>
-      <c r="C133" s="48"/>
+      <c r="B133" s="50"/>
+      <c r="C133" s="50"/>
       <c r="D133" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="19"/>
-      <c r="B134" s="48"/>
-      <c r="C134" s="48"/>
+      <c r="B134" s="50"/>
+      <c r="C134" s="50"/>
       <c r="D134" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="19"/>
-      <c r="B135" s="48"/>
-      <c r="C135" s="48"/>
+      <c r="B135" s="50"/>
+      <c r="C135" s="50"/>
       <c r="D135" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="19"/>
-      <c r="B136" s="48"/>
-      <c r="C136" s="48"/>
+      <c r="B136" s="50"/>
+      <c r="C136" s="50"/>
       <c r="D136" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="19"/>
-      <c r="B137" s="48"/>
-      <c r="C137" s="48">
+      <c r="B137" s="50"/>
+      <c r="C137" s="50">
         <v>3.9</v>
       </c>
       <c r="D137" s="7" t="s">
@@ -5929,40 +5941,40 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="19"/>
-      <c r="B138" s="48"/>
-      <c r="C138" s="48"/>
+      <c r="B138" s="50"/>
+      <c r="C138" s="50"/>
       <c r="D138" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="19"/>
-      <c r="B139" s="48"/>
-      <c r="C139" s="48"/>
+      <c r="B139" s="50"/>
+      <c r="C139" s="50"/>
       <c r="D139" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="19"/>
-      <c r="B140" s="48"/>
-      <c r="C140" s="48"/>
+      <c r="B140" s="50"/>
+      <c r="C140" s="50"/>
       <c r="D140" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="19"/>
-      <c r="B141" s="48"/>
-      <c r="C141" s="48"/>
+      <c r="B141" s="50"/>
+      <c r="C141" s="50"/>
       <c r="D141" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
-      <c r="B142" s="48"/>
-      <c r="C142" s="49">
+      <c r="B142" s="50"/>
+      <c r="C142" s="54">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -5971,122 +5983,122 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
-      <c r="B143" s="48"/>
-      <c r="C143" s="49"/>
+      <c r="B143" s="50"/>
+      <c r="C143" s="54"/>
       <c r="D143" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
-      <c r="B144" s="48"/>
-      <c r="C144" s="49"/>
+      <c r="B144" s="50"/>
+      <c r="C144" s="54"/>
       <c r="D144" s="7" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
-      <c r="B145" s="48"/>
-      <c r="C145" s="49"/>
+      <c r="B145" s="50"/>
+      <c r="C145" s="54"/>
       <c r="D145" s="7" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
-      <c r="B146" s="48"/>
-      <c r="C146" s="49"/>
+      <c r="B146" s="50"/>
+      <c r="C146" s="54"/>
       <c r="D146" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
-      <c r="B147" s="48"/>
-      <c r="C147" s="49"/>
+      <c r="B147" s="50"/>
+      <c r="C147" s="54"/>
       <c r="D147" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
-      <c r="B148" s="48"/>
-      <c r="C148" s="49"/>
+      <c r="B148" s="50"/>
+      <c r="C148" s="54"/>
       <c r="D148" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
-      <c r="B149" s="48"/>
-      <c r="C149" s="49"/>
+      <c r="B149" s="50"/>
+      <c r="C149" s="54"/>
       <c r="D149" s="7" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
-      <c r="B150" s="48"/>
-      <c r="C150" s="49"/>
+      <c r="B150" s="50"/>
+      <c r="C150" s="54"/>
       <c r="D150" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
-      <c r="B151" s="48"/>
-      <c r="C151" s="49"/>
+      <c r="B151" s="50"/>
+      <c r="C151" s="54"/>
       <c r="D151" s="7" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
-      <c r="B152" s="48"/>
-      <c r="C152" s="49"/>
+      <c r="B152" s="50"/>
+      <c r="C152" s="54"/>
       <c r="D152" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
-      <c r="B153" s="48"/>
-      <c r="C153" s="49"/>
+      <c r="B153" s="50"/>
+      <c r="C153" s="54"/>
       <c r="D153" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
-      <c r="B154" s="48"/>
-      <c r="C154" s="49"/>
+      <c r="B154" s="50"/>
+      <c r="C154" s="54"/>
       <c r="D154" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
-      <c r="B155" s="48"/>
-      <c r="C155" s="49"/>
+      <c r="B155" s="50"/>
+      <c r="C155" s="54"/>
       <c r="D155" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
-      <c r="B156" s="48"/>
-      <c r="C156" s="49"/>
+      <c r="B156" s="50"/>
+      <c r="C156" s="54"/>
       <c r="D156" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="20"/>
-      <c r="B157" s="48">
+      <c r="B157" s="50">
         <v>4</v>
       </c>
-      <c r="C157" s="48">
+      <c r="C157" s="50">
         <v>4.0999999999999996</v>
       </c>
       <c r="D157" s="7" t="s">
@@ -6095,32 +6107,32 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="19"/>
-      <c r="B158" s="48"/>
-      <c r="C158" s="48"/>
+      <c r="B158" s="50"/>
+      <c r="C158" s="50"/>
       <c r="D158" s="7" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="19"/>
-      <c r="B159" s="48"/>
-      <c r="C159" s="48"/>
+      <c r="B159" s="50"/>
+      <c r="C159" s="50"/>
       <c r="D159" s="7" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="19"/>
-      <c r="B160" s="48"/>
-      <c r="C160" s="48"/>
+      <c r="B160" s="50"/>
+      <c r="C160" s="50"/>
       <c r="D160" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="19"/>
-      <c r="B161" s="48"/>
-      <c r="C161" s="48">
+      <c r="B161" s="50"/>
+      <c r="C161" s="50">
         <v>4.2</v>
       </c>
       <c r="D161" s="7" t="s">
@@ -6129,56 +6141,56 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="19"/>
-      <c r="B162" s="48"/>
-      <c r="C162" s="48"/>
+      <c r="B162" s="50"/>
+      <c r="C162" s="50"/>
       <c r="D162" s="7" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="19"/>
-      <c r="B163" s="48"/>
-      <c r="C163" s="48"/>
+      <c r="B163" s="50"/>
+      <c r="C163" s="50"/>
       <c r="D163" s="7" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="19"/>
-      <c r="B164" s="48"/>
-      <c r="C164" s="48"/>
+      <c r="B164" s="50"/>
+      <c r="C164" s="50"/>
       <c r="D164" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="19"/>
-      <c r="B165" s="48"/>
-      <c r="C165" s="48"/>
+      <c r="B165" s="50"/>
+      <c r="C165" s="50"/>
       <c r="D165" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="19"/>
-      <c r="B166" s="48"/>
-      <c r="C166" s="48"/>
+      <c r="B166" s="50"/>
+      <c r="C166" s="50"/>
       <c r="D166" s="7" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="19"/>
-      <c r="B167" s="48"/>
-      <c r="C167" s="48"/>
+      <c r="B167" s="50"/>
+      <c r="C167" s="50"/>
       <c r="D167" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="19"/>
-      <c r="B168" s="48"/>
-      <c r="C168" s="48">
+      <c r="B168" s="50"/>
+      <c r="C168" s="50">
         <v>4.3</v>
       </c>
       <c r="D168" s="7" t="s">
@@ -6187,48 +6199,48 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="19"/>
-      <c r="B169" s="48"/>
-      <c r="C169" s="48"/>
+      <c r="B169" s="50"/>
+      <c r="C169" s="50"/>
       <c r="D169" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="19"/>
-      <c r="B170" s="48"/>
-      <c r="C170" s="48"/>
+      <c r="B170" s="50"/>
+      <c r="C170" s="50"/>
       <c r="D170" s="7" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="19"/>
-      <c r="B171" s="48"/>
-      <c r="C171" s="48"/>
+      <c r="B171" s="50"/>
+      <c r="C171" s="50"/>
       <c r="D171" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="19"/>
-      <c r="B172" s="48"/>
-      <c r="C172" s="48"/>
+      <c r="B172" s="50"/>
+      <c r="C172" s="50"/>
       <c r="D172" s="7" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="19"/>
-      <c r="B173" s="48"/>
-      <c r="C173" s="48"/>
+      <c r="B173" s="50"/>
+      <c r="C173" s="50"/>
       <c r="D173" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="19"/>
-      <c r="B174" s="48"/>
-      <c r="C174" s="48">
+      <c r="B174" s="50"/>
+      <c r="C174" s="50">
         <v>4.4000000000000004</v>
       </c>
       <c r="D174" s="7" t="s">
@@ -6237,98 +6249,63 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="19"/>
-      <c r="B175" s="48"/>
-      <c r="C175" s="48"/>
+      <c r="B175" s="50"/>
+      <c r="C175" s="50"/>
       <c r="D175" s="7" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="19"/>
-      <c r="B176" s="48"/>
-      <c r="C176" s="48"/>
+      <c r="B176" s="50"/>
+      <c r="C176" s="50"/>
       <c r="D176" s="7" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="19"/>
-      <c r="B177" s="48"/>
-      <c r="C177" s="48"/>
+      <c r="B177" s="50"/>
+      <c r="C177" s="50"/>
       <c r="D177" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="19"/>
-      <c r="B178" s="48"/>
-      <c r="C178" s="48"/>
+      <c r="B178" s="50"/>
+      <c r="C178" s="50"/>
       <c r="D178" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="19"/>
-      <c r="B179" s="48"/>
-      <c r="C179" s="48"/>
+      <c r="B179" s="50"/>
+      <c r="C179" s="50"/>
       <c r="D179" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="19"/>
-      <c r="B180" s="48"/>
-      <c r="C180" s="48"/>
+      <c r="B180" s="50"/>
+      <c r="C180" s="50"/>
       <c r="D180" s="7" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="19"/>
-      <c r="B181" s="48"/>
-      <c r="C181" s="48"/>
+      <c r="B181" s="50"/>
+      <c r="C181" s="50"/>
       <c r="D181" s="7" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J181" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A2:J181"/>
   <mergeCells count="51">
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -6345,6 +6322,41 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6353,32 +6365,32 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
     </row>
     <row r="2" spans="1:12" s="4" customFormat="1">
       <c r="A2" s="32" t="s">
@@ -6412,63 +6424,63 @@
         <v>2</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L2" s="40"/>
     </row>
-    <row r="3" spans="1:12" ht="129.6">
-      <c r="A3" s="44">
+    <row r="3" spans="1:12" ht="135">
+      <c r="A3" s="55">
         <v>1</v>
       </c>
-      <c r="B3" s="44">
+      <c r="B3" s="55">
         <v>1</v>
       </c>
       <c r="C3" s="15">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" cm="1">
-        <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+      <c r="F3" t="e" cm="1">
+        <f t="array" aca="1" ref="F3" ca="1">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>#NAME?</v>
       </c>
       <c r="G3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="57.6">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44"/>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="60">
+      <c r="A4" s="55"/>
+      <c r="B4" s="55"/>
       <c r="C4" s="15">
         <v>1.2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" cm="1">
-        <f t="array" ref="F4">_xlfn.SWITCH(E4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+      <c r="F4" t="e" cm="1">
+        <f t="array" aca="1" ref="F4" ca="1">_xlfn.SWITCH(E4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>#NAME?</v>
       </c>
       <c r="G4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H4" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="43.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="45">
+      <c r="A5" s="55"/>
+      <c r="B5" s="55"/>
       <c r="C5" s="15">
         <v>1.3</v>
       </c>
@@ -6478,20 +6490,20 @@
       <c r="E5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" cm="1">
-        <f t="array" ref="F5">_xlfn.SWITCH(E5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+      <c r="F5" t="e" cm="1">
+        <f t="array" aca="1" ref="F5" ca="1">_xlfn.SWITCH(E5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>#NAME?</v>
       </c>
       <c r="G5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="115.2">
-      <c r="A6" s="44"/>
-      <c r="B6" s="44"/>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="120">
+      <c r="A6" s="55"/>
+      <c r="B6" s="55"/>
       <c r="C6" s="36">
         <v>1.4</v>
       </c>
@@ -6501,162 +6513,161 @@
       <c r="E6" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="38" cm="1">
-        <f t="array" ref="F6">_xlfn.SWITCH(E6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+      <c r="F6" s="38" t="e" cm="1">
+        <f t="array" aca="1" ref="F6" ca="1">_xlfn.SWITCH(E6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>#NAME?</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I6" s="38"/>
       <c r="J6" s="38"/>
     </row>
-    <row r="7" spans="1:12" ht="72">
-      <c r="A7" s="44"/>
-      <c r="B7" s="44">
+    <row r="7" spans="1:12" ht="90">
+      <c r="A7" s="55"/>
+      <c r="B7" s="55">
         <v>2</v>
       </c>
       <c r="C7" s="15">
         <v>2.1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
       </c>
-      <c r="F7" cm="1">
-        <f t="array" ref="F7">_xlfn.SWITCH(E7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+      <c r="F7" t="e" cm="1">
+        <f t="array" aca="1" ref="F7" ca="1">_xlfn.SWITCH(E7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>#NAME?</v>
       </c>
       <c r="G7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="57.6">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="60">
+      <c r="A8" s="55"/>
+      <c r="B8" s="55"/>
       <c r="C8" s="15">
         <v>2.2000000000000002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
       </c>
-      <c r="F8" cm="1">
-        <f t="array" ref="F8">_xlfn.SWITCH(E8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+      <c r="F8" t="e" cm="1">
+        <f t="array" aca="1" ref="F8" ca="1">_xlfn.SWITCH(E8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>#NAME?</v>
       </c>
       <c r="G8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H8" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="100.8">
-      <c r="A9" s="44"/>
-      <c r="B9" s="44"/>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="105">
+      <c r="A9" s="55"/>
+      <c r="B9" s="55"/>
       <c r="C9" s="15">
         <v>2.2999999999999998</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
       </c>
-      <c r="F9" cm="1">
-        <f t="array" ref="F9">_xlfn.SWITCH(E9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
+      <c r="F9" t="e" cm="1">
+        <f t="array" aca="1" ref="F9" ca="1">_xlfn.SWITCH(E9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>#NAME?</v>
       </c>
       <c r="G9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H9" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="115.2">
-      <c r="A10" s="44"/>
-      <c r="B10" s="44"/>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="120">
+      <c r="A10" s="55"/>
+      <c r="B10" s="55"/>
       <c r="C10" s="15">
         <v>2.4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
       </c>
-      <c r="F10" cm="1">
-        <f t="array" ref="F10">_xlfn.SWITCH(E10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+      <c r="F10" t="e" cm="1">
+        <f t="array" aca="1" ref="F10" ca="1">_xlfn.SWITCH(E10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>#NAME?</v>
       </c>
       <c r="G10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H10" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="100.8">
-      <c r="A11" s="44"/>
-      <c r="B11" s="44"/>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="120">
+      <c r="A11" s="55"/>
+      <c r="B11" s="55"/>
       <c r="C11" s="15">
         <v>2.5</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
       </c>
-      <c r="F11" cm="1">
-        <f t="array" ref="F11">_xlfn.SWITCH(E11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+      <c r="F11" t="s">
+        <v>271</v>
       </c>
       <c r="G11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H11" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="115.2">
-      <c r="A12" s="44"/>
-      <c r="B12" s="44"/>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="120">
+      <c r="A12" s="55"/>
+      <c r="B12" s="55"/>
       <c r="C12" s="15">
         <v>2.6</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
-      <c r="F12" cm="1">
-        <f t="array" ref="F12">_xlfn.SWITCH(E12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+      <c r="F12" t="e">
+        <f ca="1">_xlfn.SWITCH(E12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>#NAME?</v>
       </c>
       <c r="G12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H12" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="158.4">
-      <c r="A13" s="44"/>
-      <c r="B13" s="44"/>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="165">
+      <c r="A13" s="55"/>
+      <c r="B13" s="55"/>
       <c r="C13" s="36">
         <v>2.7</v>
       </c>
@@ -6666,38 +6677,38 @@
       <c r="E13" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="38" cm="1">
-        <f t="array" ref="F13">_xlfn.SWITCH(E13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+      <c r="F13" s="38" t="e" cm="1">
+        <f t="array" aca="1" ref="F13" ca="1">_xlfn.SWITCH(E13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>#NAME?</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I13" s="38"/>
       <c r="J13" s="38"/>
     </row>
-    <row r="14" spans="1:12" ht="144">
+    <row r="14" spans="1:12" ht="165">
       <c r="C14" s="41">
         <v>2.8</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E14" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="43" cm="1">
-        <f t="array" ref="F14">_xlfn.SWITCH(E14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+      <c r="F14" s="43" t="e" cm="1">
+        <f t="array" aca="1" ref="F14" ca="1">_xlfn.SWITCH(E14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>#NAME?</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H14" s="43" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I14" s="43"/>
       <c r="J14" s="43"/>
@@ -6710,254 +6721,320 @@
         <v>233</v>
       </c>
       <c r="E15" s="29"/>
-      <c r="F15" s="29">
-        <f>SUM(F3:F14)</f>
-        <v>45</v>
+      <c r="F15" s="29" t="e">
+        <f ca="1">SUM(F3:F14)</f>
+        <v>#NAME?</v>
       </c>
       <c r="G15" s="29"/>
       <c r="H15" s="29"/>
       <c r="I15" s="29"/>
       <c r="J15" s="31"/>
     </row>
-    <row r="16" spans="1:12" ht="28.8">
-      <c r="A16" s="56"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="57">
+    <row r="16" spans="1:12" s="45" customFormat="1">
+      <c r="A16" s="44"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44">
         <v>2.9</v>
       </c>
-      <c r="D16" s="58" t="s">
-        <v>270</v>
-      </c>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="59"/>
-      <c r="I16" s="59"/>
-      <c r="J16" s="59"/>
-    </row>
-    <row r="17" spans="1:10" ht="57.6">
-      <c r="A17" s="56"/>
-      <c r="B17" s="56"/>
-      <c r="C17" s="60">
+      <c r="D16" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="45" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="45" customFormat="1" ht="90">
+      <c r="A17" s="44"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="35">
         <v>2.1</v>
       </c>
-      <c r="D17" s="58" t="s">
+      <c r="D17" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="45" t="s">
         <v>273</v>
       </c>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="59"/>
-      <c r="J17" s="59"/>
-    </row>
-    <row r="18" spans="1:10" ht="43.2">
-      <c r="A18" s="56"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="60">
+      <c r="J17" s="58" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="45" customFormat="1" ht="105">
+      <c r="A18" s="44"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44">
         <v>2.11</v>
       </c>
-      <c r="D18" s="58" t="s">
-        <v>271</v>
-      </c>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="59"/>
-      <c r="J18" s="59"/>
-    </row>
-    <row r="19" spans="1:10" ht="43.2">
-      <c r="A19" s="56"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="60">
+      <c r="D18" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E18" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="45" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="45">
+      <c r="A19" s="44"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44">
         <v>2.12</v>
       </c>
-      <c r="D19" s="58" t="s">
-        <v>272</v>
-      </c>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="59"/>
-      <c r="J19" s="59"/>
-    </row>
-    <row r="20" spans="1:10" ht="86.4">
-      <c r="A20" s="45">
-        <v>2</v>
-      </c>
-      <c r="B20" s="45">
-        <v>3</v>
-      </c>
-      <c r="C20" s="15">
-        <v>3.1</v>
+      <c r="D19" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E19" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="H19" s="45"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+    </row>
+    <row r="20" spans="1:10" ht="60">
+      <c r="A20" s="44"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44">
+        <v>2.13</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="86.4">
+        <v>269</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45" t="s">
+        <v>247</v>
+      </c>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+    </row>
+    <row r="21" spans="1:10" s="45" customFormat="1">
       <c r="A21" s="44"/>
       <c r="B21" s="44"/>
-      <c r="C21" s="15">
+      <c r="C21" s="44">
+        <v>2.14</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E21" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="45" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="90">
+      <c r="A22" s="44">
+        <v>2</v>
+      </c>
+      <c r="B22" s="56">
+        <v>3</v>
+      </c>
+      <c r="C22" s="15">
+        <v>3.1</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="90">
+      <c r="A23" s="44"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="15">
         <v>3.2</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="90">
+      <c r="A24" s="44"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="15">
+        <v>3.3</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="165">
+      <c r="A25" s="44"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="15">
+        <v>3.4</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="105">
+      <c r="A26" s="44"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="15">
+        <v>3.5</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="86.4">
-      <c r="A22" s="44"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="15">
-        <v>3.3</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="158.4">
-      <c r="A23" s="44"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="15">
-        <v>3.4</v>
-      </c>
-      <c r="D23" s="2" t="s">
+    <row r="27" spans="1:10" ht="120">
+      <c r="A27" s="44"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="15">
+        <v>3.6</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="44"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="15">
+        <v>3.7</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="90">
+      <c r="A29" s="44"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="15">
+        <v>3.8</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="100.8">
-      <c r="A24" s="44"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="15">
-        <v>3.5</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="115.2">
-      <c r="A25" s="44"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="15">
-        <v>3.6</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="44"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="15">
-        <v>3.7</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="86.4">
-      <c r="A27" s="44"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="15">
-        <v>3.8</v>
-      </c>
-      <c r="D27" s="2" t="s">
+    <row r="30" spans="1:10" ht="165">
+      <c r="A30" s="44"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="15">
+        <v>3.9</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="158.4">
-      <c r="A28" s="44"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="15">
-        <v>3.9</v>
-      </c>
-      <c r="D28" s="2" t="s">
+    <row r="31" spans="1:10" ht="150">
+      <c r="A31" s="44"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="35">
+        <v>3.1</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="144">
-      <c r="A29" s="44"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="35">
-        <v>3.1</v>
-      </c>
-      <c r="D29" s="2" t="s">
+    <row r="32" spans="1:10" ht="75">
+      <c r="A32" s="44"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="15">
+        <v>3.11</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="72">
-      <c r="A30" s="44"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="15">
-        <v>3.11</v>
-      </c>
-      <c r="D30" s="2" t="s">
+    <row r="33" spans="1:4" ht="225">
+      <c r="A33" s="44"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="35">
+        <v>3.12</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="216">
-      <c r="A31" s="44"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="35">
-        <v>3.12</v>
-      </c>
-      <c r="D31" s="2" t="s">
+    <row r="34" spans="1:4" ht="60">
+      <c r="A34" s="44"/>
+      <c r="B34" s="55">
+        <v>4</v>
+      </c>
+      <c r="C34" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="57.6">
-      <c r="A32" s="44"/>
-      <c r="B32" s="44">
-        <v>4</v>
-      </c>
-      <c r="C32" s="15">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="D32" s="2" t="s">
+    <row r="35" spans="1:4" ht="105">
+      <c r="A35" s="44"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="15">
+        <v>4.2</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="100.8">
-      <c r="A33" s="44"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="15">
-        <v>4.2</v>
-      </c>
-      <c r="D33" s="2" t="s">
+    <row r="36" spans="1:4" ht="90">
+      <c r="A36" s="44"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="15">
+        <v>4.3</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="86.4">
-      <c r="A34" s="44"/>
-      <c r="B34" s="44"/>
-      <c r="C34" s="15">
-        <v>4.3</v>
-      </c>
-      <c r="D34" s="2" t="s">
+    <row r="37" spans="1:4" ht="120">
+      <c r="A37" s="44"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="15">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="115.2">
-      <c r="A35" s="44"/>
-      <c r="B35" s="44"/>
-      <c r="C35" s="15">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="A20:A35"/>
+  <mergeCells count="6">
+    <mergeCell ref="B34:B37"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="B7:B13"/>
-    <mergeCell ref="B20:B31"/>
+    <mergeCell ref="B22:B33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6966,17 +7043,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57.6">
+    <row r="1" spans="1:5" ht="60">
       <c r="A1" s="22" t="s">
         <v>214</v>
       </c>
@@ -7003,9 +7080,9 @@
       <c r="C2" s="27">
         <v>45</v>
       </c>
-      <c r="D2" s="12">
-        <f>('Updated Sprint'!F15)*(1-(A2-1)/8)</f>
-        <v>45</v>
+      <c r="D2" s="12" t="e">
+        <f ca="1">('Updated Sprint'!F15)*(1-(A2-1)/8)</f>
+        <v>#NAME?</v>
       </c>
       <c r="E2" s="28">
         <v>1</v>
@@ -7018,13 +7095,13 @@
       <c r="B3" s="26">
         <v>46266</v>
       </c>
-      <c r="C3" s="27">
-        <f>('Updated Sprint'!F15)-SUM(E$2:E3)</f>
-        <v>44</v>
-      </c>
-      <c r="D3" s="12">
-        <f>('Updated Sprint'!F15)*(1-(A3-1)/8)</f>
-        <v>39.375</v>
+      <c r="C3" s="27" t="e">
+        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E3)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D3" s="12" t="e">
+        <f ca="1">('Updated Sprint'!F15)*(1-(A3-1)/8)</f>
+        <v>#NAME?</v>
       </c>
       <c r="E3" s="28">
         <v>0</v>
@@ -7037,13 +7114,13 @@
       <c r="B4" s="26">
         <v>46267</v>
       </c>
-      <c r="C4" s="27">
-        <f>('Updated Sprint'!F15)-SUM(E$2:E4)</f>
-        <v>39</v>
-      </c>
-      <c r="D4" s="12">
-        <f>('Updated Sprint'!F15)*(1-(A4-1)/8)</f>
-        <v>33.75</v>
+      <c r="C4" s="27" t="e">
+        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E4)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D4" s="12" t="e">
+        <f ca="1">('Updated Sprint'!F15)*(1-(A4-1)/8)</f>
+        <v>#NAME?</v>
       </c>
       <c r="E4" s="28">
         <v>5</v>
@@ -7056,13 +7133,13 @@
       <c r="B5" s="26">
         <v>46268</v>
       </c>
-      <c r="C5" s="27">
-        <f>('Updated Sprint'!F15)-SUM(E$2:E5)</f>
-        <v>39</v>
-      </c>
-      <c r="D5" s="12">
-        <f>('Updated Sprint'!F15)*(1-(A5-1)/8)</f>
-        <v>28.125</v>
+      <c r="C5" s="27" t="e">
+        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E5)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D5" s="12" t="e">
+        <f ca="1">('Updated Sprint'!F15)*(1-(A5-1)/8)</f>
+        <v>#NAME?</v>
       </c>
       <c r="E5" s="28">
         <v>0</v>
@@ -7075,13 +7152,13 @@
       <c r="B6" s="26">
         <v>46269</v>
       </c>
-      <c r="C6" s="27">
-        <f>('Updated Sprint'!F15)-SUM(E$2:E6)</f>
-        <v>36</v>
-      </c>
-      <c r="D6" s="12">
-        <f>('Updated Sprint'!F15)*(1-(A6-1)/8)</f>
-        <v>22.5</v>
+      <c r="C6" s="27" t="e">
+        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E6)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D6" s="12" t="e">
+        <f ca="1">('Updated Sprint'!F15)*(1-(A6-1)/8)</f>
+        <v>#NAME?</v>
       </c>
       <c r="E6" s="28">
         <v>3</v>
@@ -7094,13 +7171,13 @@
       <c r="B7" s="26">
         <v>46272</v>
       </c>
-      <c r="C7" s="27">
-        <f>('Updated Sprint'!F15)-SUM(E$2:E7)</f>
-        <v>31</v>
-      </c>
-      <c r="D7" s="12">
-        <f>('Updated Sprint'!F15)*(1-(A7-1)/8)</f>
-        <v>16.875</v>
+      <c r="C7" s="27" t="e">
+        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E7)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D7" s="12" t="e">
+        <f ca="1">('Updated Sprint'!F15)*(1-(A7-1)/8)</f>
+        <v>#NAME?</v>
       </c>
       <c r="E7" s="28">
         <v>5</v>
@@ -7113,13 +7190,13 @@
       <c r="B8" s="26">
         <v>46273</v>
       </c>
-      <c r="C8" s="27">
-        <f>('Updated Sprint'!F15)-SUM(E$2:E8)</f>
-        <v>31</v>
-      </c>
-      <c r="D8" s="12">
-        <f>('Updated Sprint'!F15)*(1-(A8-1)/8)</f>
-        <v>11.25</v>
+      <c r="C8" s="27" t="e">
+        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E8)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D8" s="12" t="e">
+        <f ca="1">('Updated Sprint'!F15)*(1-(A8-1)/8)</f>
+        <v>#NAME?</v>
       </c>
       <c r="E8" s="28">
         <v>0</v>
@@ -7132,13 +7209,13 @@
       <c r="B9" s="26">
         <v>46274</v>
       </c>
-      <c r="C9" s="27">
-        <f>('Updated Sprint'!F15)-SUM(E$2:E9)</f>
-        <v>30</v>
-      </c>
-      <c r="D9" s="12">
-        <f>('Updated Sprint'!F15)*(1-(A9-1)/8)</f>
-        <v>5.625</v>
+      <c r="C9" s="27" t="e">
+        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E9)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D9" s="12" t="e">
+        <f ca="1">('Updated Sprint'!F15)*(1-(A9-1)/8)</f>
+        <v>#NAME?</v>
       </c>
       <c r="E9" s="28">
         <v>1</v>
@@ -7151,13 +7228,13 @@
       <c r="B10" s="26">
         <v>46275</v>
       </c>
-      <c r="C10" s="27">
-        <f>('Updated Sprint'!F15)-SUM(E$2:E10)</f>
-        <v>30</v>
-      </c>
-      <c r="D10" s="12">
-        <f>('Updated Sprint'!F15)*(1-(A10-1)/8)</f>
-        <v>0</v>
+      <c r="C10" s="27" t="e">
+        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E10)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="D10" s="12" t="e">
+        <f ca="1">('Updated Sprint'!F15)*(1-(A10-1)/8)</f>
+        <v>#NAME?</v>
       </c>
       <c r="E10" s="28">
         <v>0</v>
@@ -7174,20 +7251,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="12" t="s">

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B4D0E2-045B-45F8-AF15-C64E3B4E5798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="13170" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="4" r:id="rId1"/>
@@ -16,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sprint Backlog'!$A$2:$J$181</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,12 +35,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="E5" authorId="0" shapeId="0">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -56,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -78,12 +79,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -109,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -133,7 +134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -157,7 +158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C15" authorId="0" shapeId="0">
+    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
@@ -181,7 +182,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C18" authorId="0" shapeId="0">
+    <comment ref="C18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
@@ -205,7 +206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C26" authorId="0" shapeId="0">
+    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
@@ -230,7 +231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C29" authorId="0" shapeId="0">
+    <comment ref="C29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
@@ -254,7 +255,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C31" authorId="0" shapeId="0">
+    <comment ref="C31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
@@ -278,7 +279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C38" authorId="0" shapeId="0">
+    <comment ref="C38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
         <r>
           <rPr>
@@ -302,7 +303,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C46" authorId="0" shapeId="0">
+    <comment ref="C46" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -326,7 +327,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C50" authorId="0" shapeId="0">
+    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -350,7 +351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C59" authorId="0" shapeId="0">
+    <comment ref="C59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -374,7 +375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C65" authorId="0" shapeId="0">
+    <comment ref="C65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -398,7 +399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C77" authorId="0" shapeId="0">
+    <comment ref="C77" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -422,7 +423,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C88" authorId="0" shapeId="0">
+    <comment ref="C88" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -446,7 +447,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C101" authorId="0" shapeId="0">
+    <comment ref="C101" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000010000000}">
       <text>
         <r>
           <rPr>
@@ -470,7 +471,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C110" authorId="0" shapeId="0">
+    <comment ref="C110" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000011000000}">
       <text>
         <r>
           <rPr>
@@ -494,7 +495,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C116" authorId="0" shapeId="0">
+    <comment ref="C116" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000012000000}">
       <text>
         <r>
           <rPr>
@@ -518,7 +519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C127" authorId="0" shapeId="0">
+    <comment ref="C127" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000013000000}">
       <text>
         <r>
           <rPr>
@@ -542,7 +543,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C137" authorId="0" shapeId="0">
+    <comment ref="C137" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000014000000}">
       <text>
         <r>
           <rPr>
@@ -566,7 +567,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C142" authorId="0" shapeId="0">
+    <comment ref="C142" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000015000000}">
       <text>
         <r>
           <rPr>
@@ -590,7 +591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C157" authorId="0" shapeId="0">
+    <comment ref="C157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000016000000}">
       <text>
         <r>
           <rPr>
@@ -614,7 +615,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C161" authorId="0" shapeId="0">
+    <comment ref="C161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000017000000}">
       <text>
         <r>
           <rPr>
@@ -638,7 +639,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C168" authorId="0" shapeId="0">
+    <comment ref="C168" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000018000000}">
       <text>
         <r>
           <rPr>
@@ -662,7 +663,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C174" authorId="0" shapeId="0">
+    <comment ref="C174" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000019000000}">
       <text>
         <r>
           <rPr>
@@ -691,12 +692,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -722,19 +723,44 @@
         </r>
       </text>
     </comment>
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{BA0C55A6-9B5D-4FD2-952C-1E24D2AF91E0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+candidate information
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -749,7 +775,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="280">
   <si>
     <t>Work Item</t>
   </si>
@@ -1925,19 +1951,6 @@
 Store final formatted response in recommendation_output</t>
   </si>
   <si>
-    <t>Build final response containing user full name
-Include combined primary skin concerns
-Include skin type
-Include sensitivity level
-Include recommended base
-Include recommended active ingredients
-Include active percentages/quantities
-Include formulation weight
-Include formulation explanation
-Include formulation/recommendation ID
-Return recommendation response to Shopify widget</t>
-  </si>
-  <si>
     <t>Display user name
 Display primary skin concerns
 Display "Your skin looks perfect!" when no concern is detected
@@ -1948,13 +1961,6 @@
 Display active percentages
 Display formulation explanation
 Display formulation information</t>
-  </si>
-  <si>
-    <t>Handle no-compatible-recommendation case
-Handle LLM failure
-Handle database failure
-Handle invalid recommendation/formulation
-Return appropriate frontend error response</t>
   </si>
   <si>
     <t>Test questionnaire submission
@@ -1980,23 +1986,6 @@
 Create/test Shopify product or variant</t>
   </si>
   <si>
-    <t>Receive formulation ID from frontend
-Retrieve saved formulation
-Verify formulation belongs to the logged-in customer/session
-Verify formulation is valid
-Add recommended formulation/product to Shopify cart
-Attach required formulation metadata
-Return cart response</t>
-  </si>
-  <si>
-    <t>Implement Add to Cart button
-Disable button while request is processing
-Call Add to Cart API
-Display successful cart-addition state
-Handle Add to Cart failure
-Prevent duplicate submissions</t>
-  </si>
-  <si>
     <t>Test formulation ID validation
 Test customer/formulation ownership
 Test Shopify cart item creation
@@ -2567,26 +2556,7 @@
 Define questionnaire-only concern handling</t>
   </si>
   <si>
-    <t>Retrieve combined skin concerns
-Retrieve relevant concern_benefit mappings
-Retrieve active_benefit_score data
-Retrieve applicable bases using questionnaire/session information
-Check base-active compatibility
-Produce candidate bases
-Produce candidate actives</t>
-  </si>
-  <si>
     <t>Validate LLM recommendation output</t>
-  </si>
-  <si>
-    <t>Pass candidate information , along with questionnaire answers to LLM
-Generate recommended base
-Generate recommended active ingredients
-Generate explanation for selected base
-Generate explanation for selected actives
-Ensure selected actives address detected concerns
-Ensure selected actives are compatible with selected base
-Generate formulation information</t>
   </si>
   <si>
     <t>Rename skin concerns to a more user friendly option ( it should not look like a diagnosis)
@@ -2594,9 +2564,6 @@
   </si>
   <si>
     <t>Create database migrations</t>
-  </si>
-  <si>
-    <t>{=_xlfn.SWITCH(E11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")}</t>
   </si>
   <si>
     <t>Revise db tables and model contracts (DML)</t>
@@ -2657,11 +2624,67 @@
 Associate questionnaire response with current customer_session
 Call questionnaire LLM analysis API</t>
   </si>
+  <si>
+    <t>Retreive combined skin concerns
+Retreive relevant concern_benefit mappings
+Retreive active_benefit_score data
+Retreive questionnaire json
+Retreive base-active compatibility</t>
+  </si>
+  <si>
+    <t>Define LLM system prompt and pass candidate information to the LLM, to get the following outputs:
+Generate recommended base from questionnaire json 
+Generate recommended active ingredients
+Generate explanation for selected base
+Generate explanation for selected actives
+Ensure selected actives address detected concerns
+Ensure selected actives are compatible with selected base</t>
+  </si>
+  <si>
+    <t>Build final response containing user full name
+Include combined primary skin concerns
+Include skin type
+Include recommended base
+Include recommended active ingredients
+Include active percentages (use recommended usage level by default)
+Include formulation weight (Oil/Serum -&gt; 50g ; others -&gt; 100g)
+Include formulation explanation
+Include formulation/recommendation ID
+Return recommendation response to Shopify widget</t>
+  </si>
+  <si>
+    <t>Handle no-compatible-recommendation case (no compatible formulation)
+Handle LLM failure
+Handle database failure
+Handle invalid recommendation/formulation (outside knowledge base)
+Return appropriate frontend error response</t>
+  </si>
+  <si>
+    <t>Vidit, Azad</t>
+  </si>
+  <si>
+    <t>Receive formulation ID from backend
+Retrieve saved formulation
+Verify formulation belongs to the logged-in customer+session
+Add recommended formulation/product to Shopify cart
+Attach required formulation metadata
+Return cart response</t>
+  </si>
+  <si>
+    <t>Implement Add to Cart button
+Call add-to-cart API
+Display successful cart-addition state
+Handle Add to Cart failure
+Prevent duplicate submissions</t>
+  </si>
+  <si>
+    <t>Vidit,Azad</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11">
     <font>
       <sz val="11"/>
@@ -2858,7 +2881,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2957,12 +2980,27 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2971,31 +3009,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3135,28 +3154,28 @@
                   <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3237,28 +3256,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>39.375</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>33.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>28.125</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>22.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>16.875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>11.25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>5.625</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -4178,9 +4197,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4218,9 +4237,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4255,7 +4274,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4290,7 +4309,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4463,25 +4482,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="35.7109375" customWidth="1"/>
-    <col min="5" max="5" width="51.140625" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" customWidth="1"/>
+    <col min="5" max="5" width="51.109375" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="10"/>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
     </row>
@@ -4505,7 +4524,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="105">
+    <row r="3" spans="1:6" ht="100.8">
       <c r="A3" s="16">
         <v>1</v>
       </c>
@@ -4550,13 +4569,13 @@
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="90">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="86.4">
       <c r="A6" s="15">
         <v>4</v>
       </c>
@@ -4607,32 +4626,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J181"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1">
       <c r="A2" s="10" t="s">
@@ -4667,632 +4686,632 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="49">
+      <c r="A3" s="54">
         <v>1</v>
       </c>
-      <c r="B3" s="50">
+      <c r="B3" s="49">
         <v>1</v>
       </c>
-      <c r="C3" s="50">
+      <c r="C3" s="49">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="47" t="s">
+      <c r="E3" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="47" cm="1">
+      <c r="F3" s="52" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="49"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
       <c r="D4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="49"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
+      <c r="A5" s="54"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="49"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
+      <c r="A6" s="54"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="49"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
+      <c r="A7" s="54"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="49"/>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
+      <c r="A8" s="54"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
       <c r="D8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="49"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
+      <c r="A9" s="54"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="49"/>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
+      <c r="A10" s="54"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
       <c r="D10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="49"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
+      <c r="A11" s="54"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="49"/>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50">
+      <c r="A12" s="54"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49">
         <v>1.2</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="47" t="s">
+      <c r="E12" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="47" cm="1">
+      <c r="F12" s="52" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="49"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
+      <c r="A13" s="54"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="49"/>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
+      <c r="A14" s="54"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="49"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50">
+      <c r="A15" s="54"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49">
         <v>1.3</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="47" t="s">
+      <c r="E15" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="47"/>
+      <c r="F15" s="52"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="49"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
+      <c r="A16" s="54"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
       <c r="D16" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="49"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="50"/>
+      <c r="A17" s="54"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
       <c r="D17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="49"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50">
+      <c r="A18" s="54"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49">
         <v>1.4</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="47" t="s">
+      <c r="E18" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="47"/>
+      <c r="F18" s="52"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="49"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
+      <c r="A19" s="54"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
       <c r="D19" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="49"/>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
+      <c r="A20" s="54"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
       <c r="D20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="49"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="50"/>
+      <c r="A21" s="54"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
       <c r="D21" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="49"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50"/>
+      <c r="A22" s="54"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
       <c r="D22" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="49"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
+      <c r="A23" s="54"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
       <c r="D23" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="49"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
+      <c r="A24" s="54"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
       <c r="D24" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="49"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
+      <c r="A25" s="54"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
       <c r="D25" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="49"/>
-      <c r="B26" s="51">
+      <c r="A26" s="54"/>
+      <c r="B26" s="55">
         <v>2</v>
       </c>
-      <c r="C26" s="50">
+      <c r="C26" s="49">
         <v>2.1</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E26" s="48" t="s">
+      <c r="E26" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="47"/>
+      <c r="F26" s="52"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="49"/>
-      <c r="B27" s="51"/>
-      <c r="C27" s="50"/>
+      <c r="A27" s="54"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="49"/>
       <c r="D27" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="48"/>
-      <c r="F27" s="47"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="52"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="49"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="50"/>
+      <c r="A28" s="54"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="49"/>
       <c r="D28" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E28" s="48"/>
-      <c r="F28" s="47"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="52"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="49"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="53">
+      <c r="A29" s="54"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="51">
         <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="47" t="s">
+      <c r="E29" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="47"/>
+      <c r="F29" s="52"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="49"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="53"/>
+      <c r="A30" s="54"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="51"/>
       <c r="D30" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="49"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="50">
+      <c r="A31" s="54"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="49">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="47" t="s">
+      <c r="E31" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47" t="s">
+      <c r="F31" s="52"/>
+      <c r="G31" s="52" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="49"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="50"/>
+      <c r="A32" s="54"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="49"/>
       <c r="D32" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="49"/>
-      <c r="B33" s="51"/>
-      <c r="C33" s="50"/>
+      <c r="A33" s="54"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="49"/>
       <c r="D33" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="49"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="50"/>
+      <c r="A34" s="54"/>
+      <c r="B34" s="55"/>
+      <c r="C34" s="49"/>
       <c r="D34" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="49"/>
-      <c r="B35" s="51"/>
-      <c r="C35" s="50"/>
+      <c r="A35" s="54"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="49"/>
       <c r="D35" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="49"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="50"/>
+      <c r="A36" s="54"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="49"/>
       <c r="D36" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="49"/>
-      <c r="B37" s="51"/>
-      <c r="C37" s="50"/>
+      <c r="A37" s="54"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="49"/>
       <c r="D37" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="47"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="49"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="50">
+      <c r="A38" s="54"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="49">
         <v>2.4</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E38" s="47" t="s">
+      <c r="E38" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="47"/>
+      <c r="F38" s="52"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="49"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="50"/>
+      <c r="A39" s="54"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="49"/>
       <c r="D39" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="49"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="50"/>
+      <c r="A40" s="54"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="49"/>
       <c r="D40" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="49"/>
-      <c r="B41" s="51"/>
-      <c r="C41" s="50"/>
+      <c r="A41" s="54"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="49"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="47"/>
-      <c r="F41" s="47"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="49"/>
-      <c r="B42" s="51"/>
-      <c r="C42" s="50"/>
+      <c r="A42" s="54"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="49"/>
       <c r="D42" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="49"/>
-      <c r="B43" s="51"/>
-      <c r="C43" s="50"/>
+      <c r="A43" s="54"/>
+      <c r="B43" s="55"/>
+      <c r="C43" s="49"/>
       <c r="D43" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="49"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="50"/>
+      <c r="A44" s="54"/>
+      <c r="B44" s="55"/>
+      <c r="C44" s="49"/>
       <c r="D44" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="49"/>
-      <c r="B45" s="51"/>
-      <c r="C45" s="50"/>
+      <c r="A45" s="54"/>
+      <c r="B45" s="55"/>
+      <c r="C45" s="49"/>
       <c r="D45" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="49"/>
-      <c r="B46" s="51"/>
-      <c r="C46" s="50">
+      <c r="A46" s="54"/>
+      <c r="B46" s="55"/>
+      <c r="C46" s="49">
         <v>2.5</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="E46" s="48" t="s">
+      <c r="E46" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="47"/>
+      <c r="F46" s="52"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="49"/>
-      <c r="B47" s="51"/>
-      <c r="C47" s="50"/>
+      <c r="A47" s="54"/>
+      <c r="B47" s="55"/>
+      <c r="C47" s="49"/>
       <c r="D47" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E47" s="48"/>
-      <c r="F47" s="47"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="52"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="49"/>
-      <c r="B48" s="51"/>
-      <c r="C48" s="50"/>
+      <c r="A48" s="54"/>
+      <c r="B48" s="55"/>
+      <c r="C48" s="49"/>
       <c r="D48" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E48" s="48"/>
-      <c r="F48" s="47"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="52"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="49"/>
-      <c r="B49" s="51"/>
-      <c r="C49" s="50"/>
+      <c r="A49" s="54"/>
+      <c r="B49" s="55"/>
+      <c r="C49" s="49"/>
       <c r="D49" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E49" s="48"/>
-      <c r="F49" s="47"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="52"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="49"/>
-      <c r="B50" s="51"/>
-      <c r="C50" s="50">
+      <c r="A50" s="54"/>
+      <c r="B50" s="55"/>
+      <c r="C50" s="49">
         <v>2.7</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E50" s="47" t="s">
+      <c r="E50" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="F50" s="47"/>
+      <c r="F50" s="52"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="49"/>
-      <c r="B51" s="51"/>
-      <c r="C51" s="50"/>
+      <c r="A51" s="54"/>
+      <c r="B51" s="55"/>
+      <c r="C51" s="49"/>
       <c r="D51" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="49"/>
-      <c r="B52" s="51"/>
-      <c r="C52" s="50"/>
+      <c r="A52" s="54"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="49"/>
       <c r="D52" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E52" s="47"/>
-      <c r="F52" s="47"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="49"/>
-      <c r="B53" s="51"/>
-      <c r="C53" s="50"/>
+      <c r="A53" s="54"/>
+      <c r="B53" s="55"/>
+      <c r="C53" s="49"/>
       <c r="D53" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E53" s="47"/>
-      <c r="F53" s="47"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="52"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="49"/>
-      <c r="B54" s="51"/>
-      <c r="C54" s="50"/>
+      <c r="A54" s="54"/>
+      <c r="B54" s="55"/>
+      <c r="C54" s="49"/>
       <c r="D54" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E54" s="47"/>
-      <c r="F54" s="47"/>
+      <c r="E54" s="52"/>
+      <c r="F54" s="52"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="49"/>
-      <c r="B55" s="51"/>
-      <c r="C55" s="50"/>
+      <c r="A55" s="54"/>
+      <c r="B55" s="55"/>
+      <c r="C55" s="49"/>
       <c r="D55" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E55" s="47"/>
-      <c r="F55" s="47"/>
+      <c r="E55" s="52"/>
+      <c r="F55" s="52"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="49"/>
-      <c r="B56" s="51"/>
-      <c r="C56" s="50"/>
+      <c r="A56" s="54"/>
+      <c r="B56" s="55"/>
+      <c r="C56" s="49"/>
       <c r="D56" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="47"/>
-      <c r="F56" s="47"/>
+      <c r="E56" s="52"/>
+      <c r="F56" s="52"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="49"/>
-      <c r="B57" s="51"/>
-      <c r="C57" s="50"/>
+      <c r="A57" s="54"/>
+      <c r="B57" s="55"/>
+      <c r="C57" s="49"/>
       <c r="D57" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E57" s="47"/>
-      <c r="F57" s="47"/>
+      <c r="E57" s="52"/>
+      <c r="F57" s="52"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="49"/>
-      <c r="B58" s="51"/>
-      <c r="C58" s="50"/>
+      <c r="A58" s="54"/>
+      <c r="B58" s="55"/>
+      <c r="C58" s="49"/>
       <c r="D58" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E58" s="47"/>
-      <c r="F58" s="47"/>
+      <c r="E58" s="52"/>
+      <c r="F58" s="52"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
-      <c r="B59" s="50">
+      <c r="B59" s="49">
         <v>3</v>
       </c>
-      <c r="C59" s="50">
+      <c r="C59" s="49">
         <v>3.1</v>
       </c>
       <c r="D59" s="7" t="s">
@@ -5301,48 +5320,48 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="19"/>
-      <c r="B60" s="50"/>
-      <c r="C60" s="50"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="49"/>
       <c r="D60" s="7" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="19"/>
-      <c r="B61" s="50"/>
-      <c r="C61" s="50"/>
+      <c r="B61" s="49"/>
+      <c r="C61" s="49"/>
       <c r="D61" s="7" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="19"/>
-      <c r="B62" s="50"/>
-      <c r="C62" s="50"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="49"/>
       <c r="D62" s="7" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="19"/>
-      <c r="B63" s="50"/>
-      <c r="C63" s="50"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="49"/>
       <c r="D63" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="19"/>
-      <c r="B64" s="50"/>
-      <c r="C64" s="50"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="49"/>
       <c r="D64" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="19"/>
-      <c r="B65" s="50"/>
-      <c r="C65" s="50">
+      <c r="B65" s="49"/>
+      <c r="C65" s="49">
         <v>3.2</v>
       </c>
       <c r="D65" s="7" t="s">
@@ -5351,96 +5370,96 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="19"/>
-      <c r="B66" s="50"/>
-      <c r="C66" s="50"/>
+      <c r="B66" s="49"/>
+      <c r="C66" s="49"/>
       <c r="D66" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="19"/>
-      <c r="B67" s="50"/>
-      <c r="C67" s="50"/>
+      <c r="B67" s="49"/>
+      <c r="C67" s="49"/>
       <c r="D67" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="19"/>
-      <c r="B68" s="50"/>
-      <c r="C68" s="50"/>
+      <c r="B68" s="49"/>
+      <c r="C68" s="49"/>
       <c r="D68" s="7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="19"/>
-      <c r="B69" s="50"/>
-      <c r="C69" s="50"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="49"/>
       <c r="D69" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="19"/>
-      <c r="B70" s="50"/>
-      <c r="C70" s="50"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="49"/>
       <c r="D70" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="19"/>
-      <c r="B71" s="50"/>
-      <c r="C71" s="50"/>
+      <c r="B71" s="49"/>
+      <c r="C71" s="49"/>
       <c r="D71" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="19"/>
-      <c r="B72" s="50"/>
-      <c r="C72" s="50"/>
+      <c r="B72" s="49"/>
+      <c r="C72" s="49"/>
       <c r="D72" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="19"/>
-      <c r="B73" s="50"/>
-      <c r="C73" s="50"/>
+      <c r="B73" s="49"/>
+      <c r="C73" s="49"/>
       <c r="D73" s="7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="19"/>
-      <c r="B74" s="50"/>
-      <c r="C74" s="50"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="49"/>
       <c r="D74" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="19"/>
-      <c r="B75" s="50"/>
-      <c r="C75" s="50"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="49"/>
       <c r="D75" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="19"/>
-      <c r="B76" s="50"/>
-      <c r="C76" s="50"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
       <c r="D76" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="19"/>
-      <c r="B77" s="50"/>
-      <c r="C77" s="50">
+      <c r="B77" s="49"/>
+      <c r="C77" s="49">
         <v>3.3</v>
       </c>
       <c r="D77" s="7" t="s">
@@ -5449,88 +5468,88 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="19"/>
-      <c r="B78" s="50"/>
-      <c r="C78" s="50"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="49"/>
       <c r="D78" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="19"/>
-      <c r="B79" s="50"/>
-      <c r="C79" s="50"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
       <c r="D79" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="19"/>
-      <c r="B80" s="50"/>
-      <c r="C80" s="50"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
       <c r="D80" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="19"/>
-      <c r="B81" s="50"/>
-      <c r="C81" s="50"/>
+      <c r="B81" s="49"/>
+      <c r="C81" s="49"/>
       <c r="D81" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="19"/>
-      <c r="B82" s="50"/>
-      <c r="C82" s="50"/>
+      <c r="B82" s="49"/>
+      <c r="C82" s="49"/>
       <c r="D82" s="7" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="19"/>
-      <c r="B83" s="50"/>
-      <c r="C83" s="50"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="49"/>
       <c r="D83" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="19"/>
-      <c r="B84" s="50"/>
-      <c r="C84" s="50"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="49"/>
       <c r="D84" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="19"/>
-      <c r="B85" s="50"/>
-      <c r="C85" s="50"/>
+      <c r="B85" s="49"/>
+      <c r="C85" s="49"/>
       <c r="D85" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="19"/>
-      <c r="B86" s="50"/>
-      <c r="C86" s="50"/>
+      <c r="B86" s="49"/>
+      <c r="C86" s="49"/>
       <c r="D86" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="19"/>
-      <c r="B87" s="50"/>
-      <c r="C87" s="50"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="49"/>
       <c r="D87" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="19"/>
-      <c r="B88" s="50"/>
-      <c r="C88" s="50">
+      <c r="B88" s="49"/>
+      <c r="C88" s="49">
         <v>3.4</v>
       </c>
       <c r="D88" s="15" t="s">
@@ -5539,104 +5558,104 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="19"/>
-      <c r="B89" s="50"/>
-      <c r="C89" s="50"/>
+      <c r="B89" s="49"/>
+      <c r="C89" s="49"/>
       <c r="D89" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="19"/>
-      <c r="B90" s="50"/>
-      <c r="C90" s="50"/>
+      <c r="B90" s="49"/>
+      <c r="C90" s="49"/>
       <c r="D90" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="19"/>
-      <c r="B91" s="50"/>
-      <c r="C91" s="50"/>
+      <c r="B91" s="49"/>
+      <c r="C91" s="49"/>
       <c r="D91" s="7" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="19"/>
-      <c r="B92" s="50"/>
-      <c r="C92" s="50"/>
+      <c r="B92" s="49"/>
+      <c r="C92" s="49"/>
       <c r="D92" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="19"/>
-      <c r="B93" s="50"/>
-      <c r="C93" s="50"/>
+      <c r="B93" s="49"/>
+      <c r="C93" s="49"/>
       <c r="D93" s="7" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="19"/>
-      <c r="B94" s="50"/>
-      <c r="C94" s="50"/>
+      <c r="B94" s="49"/>
+      <c r="C94" s="49"/>
       <c r="D94" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="19"/>
-      <c r="B95" s="50"/>
-      <c r="C95" s="50"/>
+      <c r="B95" s="49"/>
+      <c r="C95" s="49"/>
       <c r="D95" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="19"/>
-      <c r="B96" s="50"/>
-      <c r="C96" s="50"/>
+      <c r="B96" s="49"/>
+      <c r="C96" s="49"/>
       <c r="D96" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="19"/>
-      <c r="B97" s="50"/>
-      <c r="C97" s="50"/>
+      <c r="B97" s="49"/>
+      <c r="C97" s="49"/>
       <c r="D97" s="7" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="19"/>
-      <c r="B98" s="50"/>
-      <c r="C98" s="50"/>
+      <c r="B98" s="49"/>
+      <c r="C98" s="49"/>
       <c r="D98" s="7" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="19"/>
-      <c r="B99" s="50"/>
-      <c r="C99" s="50"/>
+      <c r="B99" s="49"/>
+      <c r="C99" s="49"/>
       <c r="D99" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="19"/>
-      <c r="B100" s="50"/>
-      <c r="C100" s="50"/>
+      <c r="B100" s="49"/>
+      <c r="C100" s="49"/>
       <c r="D100" s="7" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="19"/>
-      <c r="B101" s="50"/>
-      <c r="C101" s="50">
+      <c r="B101" s="49"/>
+      <c r="C101" s="49">
         <v>3.5</v>
       </c>
       <c r="D101" s="11" t="s">
@@ -5645,72 +5664,72 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="19"/>
-      <c r="B102" s="50"/>
-      <c r="C102" s="50"/>
+      <c r="B102" s="49"/>
+      <c r="C102" s="49"/>
       <c r="D102" s="7" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="19"/>
-      <c r="B103" s="50"/>
-      <c r="C103" s="50"/>
+      <c r="B103" s="49"/>
+      <c r="C103" s="49"/>
       <c r="D103" s="7" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="19"/>
-      <c r="B104" s="50"/>
-      <c r="C104" s="50"/>
+      <c r="B104" s="49"/>
+      <c r="C104" s="49"/>
       <c r="D104" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="19"/>
-      <c r="B105" s="50"/>
-      <c r="C105" s="50"/>
+      <c r="B105" s="49"/>
+      <c r="C105" s="49"/>
       <c r="D105" s="7" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="19"/>
-      <c r="B106" s="50"/>
-      <c r="C106" s="50"/>
+      <c r="B106" s="49"/>
+      <c r="C106" s="49"/>
       <c r="D106" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="19"/>
-      <c r="B107" s="50"/>
-      <c r="C107" s="50"/>
+      <c r="B107" s="49"/>
+      <c r="C107" s="49"/>
       <c r="D107" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="19"/>
-      <c r="B108" s="50"/>
-      <c r="C108" s="50"/>
+      <c r="B108" s="49"/>
+      <c r="C108" s="49"/>
       <c r="D108" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="19"/>
-      <c r="B109" s="50"/>
-      <c r="C109" s="50"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="49"/>
       <c r="D109" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="19"/>
-      <c r="B110" s="50"/>
-      <c r="C110" s="50">
+      <c r="B110" s="49"/>
+      <c r="C110" s="49">
         <v>3.6</v>
       </c>
       <c r="D110" s="7" t="s">
@@ -5719,48 +5738,48 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19"/>
-      <c r="B111" s="50"/>
-      <c r="C111" s="50"/>
+      <c r="B111" s="49"/>
+      <c r="C111" s="49"/>
       <c r="D111" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19"/>
-      <c r="B112" s="50"/>
-      <c r="C112" s="50"/>
+      <c r="B112" s="49"/>
+      <c r="C112" s="49"/>
       <c r="D112" s="7" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="19"/>
-      <c r="B113" s="50"/>
-      <c r="C113" s="50"/>
+      <c r="B113" s="49"/>
+      <c r="C113" s="49"/>
       <c r="D113" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="19"/>
-      <c r="B114" s="50"/>
-      <c r="C114" s="50"/>
+      <c r="B114" s="49"/>
+      <c r="C114" s="49"/>
       <c r="D114" s="7" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="19"/>
-      <c r="B115" s="50"/>
-      <c r="C115" s="50"/>
+      <c r="B115" s="49"/>
+      <c r="C115" s="49"/>
       <c r="D115" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="19"/>
-      <c r="B116" s="50"/>
-      <c r="C116" s="50">
+      <c r="B116" s="49"/>
+      <c r="C116" s="49">
         <v>3.7</v>
       </c>
       <c r="D116" s="7" t="s">
@@ -5769,88 +5788,88 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="19"/>
-      <c r="B117" s="50"/>
-      <c r="C117" s="50"/>
+      <c r="B117" s="49"/>
+      <c r="C117" s="49"/>
       <c r="D117" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="19"/>
-      <c r="B118" s="50"/>
-      <c r="C118" s="50"/>
+      <c r="B118" s="49"/>
+      <c r="C118" s="49"/>
       <c r="D118" s="7" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="19"/>
-      <c r="B119" s="50"/>
-      <c r="C119" s="50"/>
+      <c r="B119" s="49"/>
+      <c r="C119" s="49"/>
       <c r="D119" s="7" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="19"/>
-      <c r="B120" s="50"/>
-      <c r="C120" s="50"/>
+      <c r="B120" s="49"/>
+      <c r="C120" s="49"/>
       <c r="D120" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="19"/>
-      <c r="B121" s="50"/>
-      <c r="C121" s="50"/>
+      <c r="B121" s="49"/>
+      <c r="C121" s="49"/>
       <c r="D121" s="7" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="19"/>
-      <c r="B122" s="50"/>
-      <c r="C122" s="50"/>
+      <c r="B122" s="49"/>
+      <c r="C122" s="49"/>
       <c r="D122" s="7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="19"/>
-      <c r="B123" s="50"/>
-      <c r="C123" s="50"/>
+      <c r="B123" s="49"/>
+      <c r="C123" s="49"/>
       <c r="D123" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="19"/>
-      <c r="B124" s="50"/>
-      <c r="C124" s="50"/>
+      <c r="B124" s="49"/>
+      <c r="C124" s="49"/>
       <c r="D124" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="19"/>
-      <c r="B125" s="50"/>
-      <c r="C125" s="50"/>
+      <c r="B125" s="49"/>
+      <c r="C125" s="49"/>
       <c r="D125" s="7" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="19"/>
-      <c r="B126" s="50"/>
-      <c r="C126" s="50"/>
+      <c r="B126" s="49"/>
+      <c r="C126" s="49"/>
       <c r="D126" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="19"/>
-      <c r="B127" s="50"/>
-      <c r="C127" s="50">
+      <c r="B127" s="49"/>
+      <c r="C127" s="49">
         <v>3.8</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -5859,80 +5878,80 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="19"/>
-      <c r="B128" s="50"/>
-      <c r="C128" s="50"/>
+      <c r="B128" s="49"/>
+      <c r="C128" s="49"/>
       <c r="D128" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="19"/>
-      <c r="B129" s="50"/>
-      <c r="C129" s="50"/>
+      <c r="B129" s="49"/>
+      <c r="C129" s="49"/>
       <c r="D129" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="19"/>
-      <c r="B130" s="50"/>
-      <c r="C130" s="50"/>
+      <c r="B130" s="49"/>
+      <c r="C130" s="49"/>
       <c r="D130" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="19"/>
-      <c r="B131" s="50"/>
-      <c r="C131" s="50"/>
+      <c r="B131" s="49"/>
+      <c r="C131" s="49"/>
       <c r="D131" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="19"/>
-      <c r="B132" s="50"/>
-      <c r="C132" s="50"/>
+      <c r="B132" s="49"/>
+      <c r="C132" s="49"/>
       <c r="D132" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="19"/>
-      <c r="B133" s="50"/>
-      <c r="C133" s="50"/>
+      <c r="B133" s="49"/>
+      <c r="C133" s="49"/>
       <c r="D133" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="19"/>
-      <c r="B134" s="50"/>
-      <c r="C134" s="50"/>
+      <c r="B134" s="49"/>
+      <c r="C134" s="49"/>
       <c r="D134" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="19"/>
-      <c r="B135" s="50"/>
-      <c r="C135" s="50"/>
+      <c r="B135" s="49"/>
+      <c r="C135" s="49"/>
       <c r="D135" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="19"/>
-      <c r="B136" s="50"/>
-      <c r="C136" s="50"/>
+      <c r="B136" s="49"/>
+      <c r="C136" s="49"/>
       <c r="D136" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="19"/>
-      <c r="B137" s="50"/>
-      <c r="C137" s="50">
+      <c r="B137" s="49"/>
+      <c r="C137" s="49">
         <v>3.9</v>
       </c>
       <c r="D137" s="7" t="s">
@@ -5941,40 +5960,40 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="19"/>
-      <c r="B138" s="50"/>
-      <c r="C138" s="50"/>
+      <c r="B138" s="49"/>
+      <c r="C138" s="49"/>
       <c r="D138" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="19"/>
-      <c r="B139" s="50"/>
-      <c r="C139" s="50"/>
+      <c r="B139" s="49"/>
+      <c r="C139" s="49"/>
       <c r="D139" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="19"/>
-      <c r="B140" s="50"/>
-      <c r="C140" s="50"/>
+      <c r="B140" s="49"/>
+      <c r="C140" s="49"/>
       <c r="D140" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="19"/>
-      <c r="B141" s="50"/>
-      <c r="C141" s="50"/>
+      <c r="B141" s="49"/>
+      <c r="C141" s="49"/>
       <c r="D141" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
-      <c r="B142" s="50"/>
-      <c r="C142" s="54">
+      <c r="B142" s="49"/>
+      <c r="C142" s="50">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -5983,122 +6002,122 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
-      <c r="B143" s="50"/>
-      <c r="C143" s="54"/>
+      <c r="B143" s="49"/>
+      <c r="C143" s="50"/>
       <c r="D143" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
-      <c r="B144" s="50"/>
-      <c r="C144" s="54"/>
+      <c r="B144" s="49"/>
+      <c r="C144" s="50"/>
       <c r="D144" s="7" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
-      <c r="B145" s="50"/>
-      <c r="C145" s="54"/>
+      <c r="B145" s="49"/>
+      <c r="C145" s="50"/>
       <c r="D145" s="7" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
-      <c r="B146" s="50"/>
-      <c r="C146" s="54"/>
+      <c r="B146" s="49"/>
+      <c r="C146" s="50"/>
       <c r="D146" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
-      <c r="B147" s="50"/>
-      <c r="C147" s="54"/>
+      <c r="B147" s="49"/>
+      <c r="C147" s="50"/>
       <c r="D147" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
-      <c r="B148" s="50"/>
-      <c r="C148" s="54"/>
+      <c r="B148" s="49"/>
+      <c r="C148" s="50"/>
       <c r="D148" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
-      <c r="B149" s="50"/>
-      <c r="C149" s="54"/>
+      <c r="B149" s="49"/>
+      <c r="C149" s="50"/>
       <c r="D149" s="7" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
-      <c r="B150" s="50"/>
-      <c r="C150" s="54"/>
+      <c r="B150" s="49"/>
+      <c r="C150" s="50"/>
       <c r="D150" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
-      <c r="B151" s="50"/>
-      <c r="C151" s="54"/>
+      <c r="B151" s="49"/>
+      <c r="C151" s="50"/>
       <c r="D151" s="7" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
-      <c r="B152" s="50"/>
-      <c r="C152" s="54"/>
+      <c r="B152" s="49"/>
+      <c r="C152" s="50"/>
       <c r="D152" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
-      <c r="B153" s="50"/>
-      <c r="C153" s="54"/>
+      <c r="B153" s="49"/>
+      <c r="C153" s="50"/>
       <c r="D153" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
-      <c r="B154" s="50"/>
-      <c r="C154" s="54"/>
+      <c r="B154" s="49"/>
+      <c r="C154" s="50"/>
       <c r="D154" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
-      <c r="B155" s="50"/>
-      <c r="C155" s="54"/>
+      <c r="B155" s="49"/>
+      <c r="C155" s="50"/>
       <c r="D155" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
-      <c r="B156" s="50"/>
-      <c r="C156" s="54"/>
+      <c r="B156" s="49"/>
+      <c r="C156" s="50"/>
       <c r="D156" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="20"/>
-      <c r="B157" s="50">
+      <c r="B157" s="49">
         <v>4</v>
       </c>
-      <c r="C157" s="50">
+      <c r="C157" s="49">
         <v>4.0999999999999996</v>
       </c>
       <c r="D157" s="7" t="s">
@@ -6107,32 +6126,32 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="19"/>
-      <c r="B158" s="50"/>
-      <c r="C158" s="50"/>
+      <c r="B158" s="49"/>
+      <c r="C158" s="49"/>
       <c r="D158" s="7" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="19"/>
-      <c r="B159" s="50"/>
-      <c r="C159" s="50"/>
+      <c r="B159" s="49"/>
+      <c r="C159" s="49"/>
       <c r="D159" s="7" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="19"/>
-      <c r="B160" s="50"/>
-      <c r="C160" s="50"/>
+      <c r="B160" s="49"/>
+      <c r="C160" s="49"/>
       <c r="D160" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="19"/>
-      <c r="B161" s="50"/>
-      <c r="C161" s="50">
+      <c r="B161" s="49"/>
+      <c r="C161" s="49">
         <v>4.2</v>
       </c>
       <c r="D161" s="7" t="s">
@@ -6141,56 +6160,56 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="19"/>
-      <c r="B162" s="50"/>
-      <c r="C162" s="50"/>
+      <c r="B162" s="49"/>
+      <c r="C162" s="49"/>
       <c r="D162" s="7" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="19"/>
-      <c r="B163" s="50"/>
-      <c r="C163" s="50"/>
+      <c r="B163" s="49"/>
+      <c r="C163" s="49"/>
       <c r="D163" s="7" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="19"/>
-      <c r="B164" s="50"/>
-      <c r="C164" s="50"/>
+      <c r="B164" s="49"/>
+      <c r="C164" s="49"/>
       <c r="D164" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="19"/>
-      <c r="B165" s="50"/>
-      <c r="C165" s="50"/>
+      <c r="B165" s="49"/>
+      <c r="C165" s="49"/>
       <c r="D165" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="19"/>
-      <c r="B166" s="50"/>
-      <c r="C166" s="50"/>
+      <c r="B166" s="49"/>
+      <c r="C166" s="49"/>
       <c r="D166" s="7" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="19"/>
-      <c r="B167" s="50"/>
-      <c r="C167" s="50"/>
+      <c r="B167" s="49"/>
+      <c r="C167" s="49"/>
       <c r="D167" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="19"/>
-      <c r="B168" s="50"/>
-      <c r="C168" s="50">
+      <c r="B168" s="49"/>
+      <c r="C168" s="49">
         <v>4.3</v>
       </c>
       <c r="D168" s="7" t="s">
@@ -6199,48 +6218,48 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="19"/>
-      <c r="B169" s="50"/>
-      <c r="C169" s="50"/>
+      <c r="B169" s="49"/>
+      <c r="C169" s="49"/>
       <c r="D169" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="19"/>
-      <c r="B170" s="50"/>
-      <c r="C170" s="50"/>
+      <c r="B170" s="49"/>
+      <c r="C170" s="49"/>
       <c r="D170" s="7" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="19"/>
-      <c r="B171" s="50"/>
-      <c r="C171" s="50"/>
+      <c r="B171" s="49"/>
+      <c r="C171" s="49"/>
       <c r="D171" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="19"/>
-      <c r="B172" s="50"/>
-      <c r="C172" s="50"/>
+      <c r="B172" s="49"/>
+      <c r="C172" s="49"/>
       <c r="D172" s="7" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="19"/>
-      <c r="B173" s="50"/>
-      <c r="C173" s="50"/>
+      <c r="B173" s="49"/>
+      <c r="C173" s="49"/>
       <c r="D173" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="19"/>
-      <c r="B174" s="50"/>
-      <c r="C174" s="50">
+      <c r="B174" s="49"/>
+      <c r="C174" s="49">
         <v>4.4000000000000004</v>
       </c>
       <c r="D174" s="7" t="s">
@@ -6249,63 +6268,98 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="19"/>
-      <c r="B175" s="50"/>
-      <c r="C175" s="50"/>
+      <c r="B175" s="49"/>
+      <c r="C175" s="49"/>
       <c r="D175" s="7" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="19"/>
-      <c r="B176" s="50"/>
-      <c r="C176" s="50"/>
+      <c r="B176" s="49"/>
+      <c r="C176" s="49"/>
       <c r="D176" s="7" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="19"/>
-      <c r="B177" s="50"/>
-      <c r="C177" s="50"/>
+      <c r="B177" s="49"/>
+      <c r="C177" s="49"/>
       <c r="D177" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="19"/>
-      <c r="B178" s="50"/>
-      <c r="C178" s="50"/>
+      <c r="B178" s="49"/>
+      <c r="C178" s="49"/>
       <c r="D178" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="19"/>
-      <c r="B179" s="50"/>
-      <c r="C179" s="50"/>
+      <c r="B179" s="49"/>
+      <c r="C179" s="49"/>
       <c r="D179" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="19"/>
-      <c r="B180" s="50"/>
-      <c r="C180" s="50"/>
+      <c r="B180" s="49"/>
+      <c r="C180" s="49"/>
       <c r="D180" s="7" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="19"/>
-      <c r="B181" s="50"/>
-      <c r="C181" s="50"/>
+      <c r="B181" s="49"/>
+      <c r="C181" s="49"/>
       <c r="D181" s="7" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J181"/>
+  <autoFilter ref="A2:J181" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="51">
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -6322,41 +6376,6 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6365,32 +6384,32 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:12" s="4" customFormat="1">
       <c r="A2" s="32" t="s">
@@ -6424,63 +6443,63 @@
         <v>2</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="L2" s="40"/>
     </row>
-    <row r="3" spans="1:12" ht="135">
-      <c r="A3" s="55">
+    <row r="3" spans="1:12" ht="129.6">
+      <c r="A3" s="45">
         <v>1</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="45">
         <v>1</v>
       </c>
       <c r="C3" s="15">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="e" cm="1">
-        <f t="array" aca="1" ref="F3" ca="1">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>#NAME?</v>
+      <c r="F3" cm="1">
+        <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="60">
-      <c r="A4" s="55"/>
-      <c r="B4" s="55"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="57.6">
+      <c r="A4" s="45"/>
+      <c r="B4" s="45"/>
       <c r="C4" s="15">
         <v>1.2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" t="e" cm="1">
-        <f t="array" aca="1" ref="F4" ca="1">_xlfn.SWITCH(E4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>#NAME?</v>
+      <c r="F4" cm="1">
+        <f t="array" ref="F4">_xlfn.SWITCH(E4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H4" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="45">
-      <c r="A5" s="55"/>
-      <c r="B5" s="55"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="43.2">
+      <c r="A5" s="45"/>
+      <c r="B5" s="45"/>
       <c r="C5" s="15">
         <v>1.3</v>
       </c>
@@ -6490,20 +6509,20 @@
       <c r="E5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" t="e" cm="1">
-        <f t="array" aca="1" ref="F5" ca="1">_xlfn.SWITCH(E5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>#NAME?</v>
+      <c r="F5" cm="1">
+        <f t="array" ref="F5">_xlfn.SWITCH(E5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H5" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="120">
-      <c r="A6" s="55"/>
-      <c r="B6" s="55"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="115.2">
+      <c r="A6" s="45"/>
+      <c r="B6" s="45"/>
       <c r="C6" s="36">
         <v>1.4</v>
       </c>
@@ -6513,161 +6532,162 @@
       <c r="E6" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="38" t="e" cm="1">
-        <f t="array" aca="1" ref="F6" ca="1">_xlfn.SWITCH(E6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>#NAME?</v>
+      <c r="F6" s="38" cm="1">
+        <f t="array" ref="F6">_xlfn.SWITCH(E6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="I6" s="38"/>
       <c r="J6" s="38"/>
     </row>
-    <row r="7" spans="1:12" ht="90">
-      <c r="A7" s="55"/>
-      <c r="B7" s="55">
+    <row r="7" spans="1:12" ht="72">
+      <c r="A7" s="45"/>
+      <c r="B7" s="45">
         <v>2</v>
       </c>
       <c r="C7" s="15">
         <v>2.1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
       </c>
-      <c r="F7" t="e" cm="1">
-        <f t="array" aca="1" ref="F7" ca="1">_xlfn.SWITCH(E7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>#NAME?</v>
+      <c r="F7" cm="1">
+        <f t="array" ref="F7">_xlfn.SWITCH(E7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="60">
-      <c r="A8" s="55"/>
-      <c r="B8" s="55"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="57.6">
+      <c r="A8" s="45"/>
+      <c r="B8" s="45"/>
       <c r="C8" s="15">
         <v>2.2000000000000002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
       </c>
-      <c r="F8" t="e" cm="1">
-        <f t="array" aca="1" ref="F8" ca="1">_xlfn.SWITCH(E8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>#NAME?</v>
+      <c r="F8" cm="1">
+        <f t="array" ref="F8">_xlfn.SWITCH(E8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="105">
-      <c r="A9" s="55"/>
-      <c r="B9" s="55"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="100.8">
+      <c r="A9" s="45"/>
+      <c r="B9" s="45"/>
       <c r="C9" s="15">
         <v>2.2999999999999998</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
       </c>
-      <c r="F9" t="e" cm="1">
-        <f t="array" aca="1" ref="F9" ca="1">_xlfn.SWITCH(E9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>#NAME?</v>
+      <c r="F9" cm="1">
+        <f t="array" ref="F9">_xlfn.SWITCH(E9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H9" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="120">
-      <c r="A10" s="55"/>
-      <c r="B10" s="55"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="115.2">
+      <c r="A10" s="45"/>
+      <c r="B10" s="45"/>
       <c r="C10" s="15">
         <v>2.4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
       </c>
-      <c r="F10" t="e" cm="1">
-        <f t="array" aca="1" ref="F10" ca="1">_xlfn.SWITCH(E10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>#NAME?</v>
+      <c r="F10" cm="1">
+        <f t="array" ref="F10">_xlfn.SWITCH(E10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="120">
-      <c r="A11" s="55"/>
-      <c r="B11" s="55"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="100.8">
+      <c r="A11" s="45"/>
+      <c r="B11" s="45"/>
       <c r="C11" s="15">
         <v>2.5</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
       </c>
-      <c r="F11" t="s">
-        <v>271</v>
+      <c r="F11" cm="1">
+        <f t="array" ref="F11">_xlfn.SWITCH(E11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H11" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="120">
-      <c r="A12" s="55"/>
-      <c r="B12" s="55"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="115.2">
+      <c r="A12" s="45"/>
+      <c r="B12" s="45"/>
       <c r="C12" s="15">
         <v>2.6</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
-      <c r="F12" t="e">
-        <f ca="1">_xlfn.SWITCH(E12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>#NAME?</v>
+      <c r="F12">
+        <f>_xlfn.SWITCH(E12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H12" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="165">
-      <c r="A13" s="55"/>
-      <c r="B13" s="55"/>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="158.4">
+      <c r="A13" s="45"/>
+      <c r="B13" s="45"/>
       <c r="C13" s="36">
         <v>2.7</v>
       </c>
@@ -6677,38 +6697,38 @@
       <c r="E13" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="38" t="e" cm="1">
-        <f t="array" aca="1" ref="F13" ca="1">_xlfn.SWITCH(E13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>#NAME?</v>
+      <c r="F13" s="38" cm="1">
+        <f t="array" ref="F13">_xlfn.SWITCH(E13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I13" s="38"/>
       <c r="J13" s="38"/>
     </row>
-    <row r="14" spans="1:12" ht="165">
+    <row r="14" spans="1:12" ht="144">
       <c r="C14" s="41">
         <v>2.8</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E14" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="43" t="e" cm="1">
-        <f t="array" aca="1" ref="F14" ca="1">_xlfn.SWITCH(E14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>#NAME?</v>
+      <c r="F14" s="43" cm="1">
+        <f t="array" ref="F14">_xlfn.SWITCH(E14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H14" s="43" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="I14" s="43"/>
       <c r="J14" s="43"/>
@@ -6721,177 +6741,190 @@
         <v>233</v>
       </c>
       <c r="E15" s="29"/>
-      <c r="F15" s="29" t="e">
-        <f ca="1">SUM(F3:F14)</f>
-        <v>#NAME?</v>
+      <c r="F15" s="29">
+        <f>SUM(F3:F14)</f>
+        <v>45</v>
       </c>
       <c r="G15" s="29"/>
       <c r="H15" s="29"/>
       <c r="I15" s="29"/>
       <c r="J15" s="31"/>
     </row>
-    <row r="16" spans="1:12" s="45" customFormat="1">
-      <c r="A16" s="44"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44">
+    <row r="16" spans="1:12">
+      <c r="C16" s="15">
         <v>2.9</v>
       </c>
-      <c r="D16" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="E16" s="45" t="s">
+      <c r="D16" t="s">
+        <v>265</v>
+      </c>
+      <c r="E16" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="45" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" s="45" customFormat="1" ht="90">
-      <c r="A17" s="44"/>
-      <c r="B17" s="44"/>
+      <c r="F16" cm="1">
+        <f t="array" ref="F16">_xlfn.SWITCH(E16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="G16" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="86.4">
       <c r="C17" s="35">
         <v>2.1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="E17" s="45" t="s">
+        <v>269</v>
+      </c>
+      <c r="E17" t="s">
         <v>20</v>
       </c>
-      <c r="G17" s="45" t="s">
-        <v>273</v>
-      </c>
-      <c r="J17" s="58" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" s="45" customFormat="1" ht="105">
-      <c r="A18" s="44"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44">
+      <c r="F17" cm="1">
+        <f t="array" ref="F17">_xlfn.SWITCH(E17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="G17" t="s">
+        <v>266</v>
+      </c>
+      <c r="J17" s="44" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="100.8">
+      <c r="C18" s="15">
         <v>2.11</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E18" s="45" t="s">
+        <v>267</v>
+      </c>
+      <c r="E18" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="45" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="45">
-      <c r="A19" s="44"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44">
+      <c r="F18" cm="1">
+        <f t="array" ref="F18">_xlfn.SWITCH(E18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="G18" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="43.2">
+      <c r="C19" s="15">
         <v>2.12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E19" s="45" t="s">
+        <v>268</v>
+      </c>
+      <c r="E19" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45" t="s">
-        <v>244</v>
-      </c>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
-    </row>
-    <row r="20" spans="1:10" ht="60">
-      <c r="A20" s="44"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44">
+      <c r="F19" cm="1">
+        <f t="array" ref="F19">_xlfn.SWITCH(E19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="G19" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="43.2">
+      <c r="C20" s="15">
         <v>2.13</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E20" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="E20" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
-    </row>
-    <row r="21" spans="1:10" s="45" customFormat="1">
-      <c r="A21" s="44"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44">
+      <c r="F20" cm="1">
+        <f t="array" ref="F20">_xlfn.SWITCH(E20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G20" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="C21" s="15">
         <v>2.14</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E21" s="45" t="s">
+        <v>264</v>
+      </c>
+      <c r="E21" t="s">
         <v>18</v>
       </c>
-      <c r="G21" s="45" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="90">
-      <c r="A22" s="44">
+      <c r="F21" cm="1">
+        <f t="array" ref="F21">_xlfn.SWITCH(E21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="B22" s="56">
+      <c r="G21" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="86.4">
+      <c r="A22" s="15">
+        <v>2</v>
+      </c>
+      <c r="B22" s="47">
         <v>3</v>
       </c>
       <c r="C22" s="15">
         <v>3.1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
       </c>
+      <c r="F22" cm="1">
+        <f t="array" ref="F22">_xlfn.SWITCH(E22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
       <c r="G22" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="90">
-      <c r="A23" s="44"/>
-      <c r="B23" s="55"/>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="86.4">
+      <c r="B23" s="45"/>
       <c r="C23" s="15">
         <v>3.2</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E23" t="s">
         <v>18</v>
       </c>
+      <c r="F23" cm="1">
+        <f t="array" ref="F23">_xlfn.SWITCH(E23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
       <c r="G23" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="90">
-      <c r="A24" s="44"/>
-      <c r="B24" s="55"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="86.4">
+      <c r="B24" s="45"/>
       <c r="C24" s="15">
         <v>3.3</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E24" t="s">
         <v>18</v>
       </c>
+      <c r="F24" cm="1">
+        <f t="array" ref="F24">_xlfn.SWITCH(E24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
       <c r="G24" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="165">
-      <c r="A25" s="44"/>
-      <c r="B25" s="55"/>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="158.4">
+      <c r="B25" s="45"/>
       <c r="C25" s="15">
         <v>3.4</v>
       </c>
@@ -6901,130 +6934,248 @@
       <c r="E25" t="s">
         <v>18</v>
       </c>
+      <c r="F25" cm="1">
+        <f t="array" ref="F25">_xlfn.SWITCH(E25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
       <c r="G25" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="105">
-      <c r="A26" s="44"/>
-      <c r="B26" s="55"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="72">
+      <c r="B26" s="45"/>
       <c r="C26" s="15">
         <v>3.5</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="120">
-      <c r="A27" s="44"/>
-      <c r="B27" s="55"/>
+        <v>272</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" cm="1">
+        <f t="array" ref="F26">_xlfn.SWITCH(E26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G26" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="115.2">
+      <c r="B27" s="45"/>
       <c r="C27" s="15">
         <v>3.6</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
+      </c>
+      <c r="E27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" cm="1">
+        <f t="array" ref="F27">_xlfn.SWITCH(E27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="G27" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="44"/>
-      <c r="B28" s="55"/>
+      <c r="B28" s="45"/>
       <c r="C28" s="15">
         <v>3.7</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="90">
-      <c r="A29" s="44"/>
-      <c r="B29" s="55"/>
+        <v>262</v>
+      </c>
+      <c r="E28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" cm="1">
+        <f t="array" ref="F28">_xlfn.SWITCH(E28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="G28" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="86.4">
+      <c r="B29" s="45"/>
       <c r="C29" s="15">
         <v>3.8</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="165">
-      <c r="A30" s="44"/>
-      <c r="B30" s="55"/>
+      <c r="E29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" cm="1">
+        <f t="array" ref="F29">_xlfn.SWITCH(E29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="144">
+      <c r="B30" s="45"/>
       <c r="C30" s="15">
         <v>3.9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="150">
-      <c r="A31" s="44"/>
-      <c r="B31" s="55"/>
+        <v>274</v>
+      </c>
+      <c r="E30" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" cm="1">
+        <f t="array" ref="F30">_xlfn.SWITCH(E30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="144">
+      <c r="B31" s="45"/>
       <c r="C31" s="35">
         <v>3.1</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="75">
-      <c r="A32" s="44"/>
-      <c r="B32" s="55"/>
+        <v>236</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" cm="1">
+        <f t="array" ref="F31">_xlfn.SWITCH(E31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G31" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="72">
+      <c r="B32" s="45"/>
       <c r="C32" s="15">
         <v>3.11</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="225">
-      <c r="A33" s="44"/>
-      <c r="B33" s="55"/>
+        <v>275</v>
+      </c>
+      <c r="E32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" cm="1">
+        <f t="array" ref="F32">_xlfn.SWITCH(E32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="G32" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="216">
+      <c r="B33" s="45"/>
       <c r="C33" s="35">
         <v>3.12</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="60">
-      <c r="A34" s="44"/>
-      <c r="B34" s="55">
+        <v>237</v>
+      </c>
+      <c r="E33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" cm="1">
+        <f t="array" ref="F33">_xlfn.SWITCH(E33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="G33" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="57.6">
+      <c r="B34" s="45">
         <v>4</v>
       </c>
       <c r="C34" s="15">
         <v>4.0999999999999996</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="105">
-      <c r="A35" s="44"/>
-      <c r="B35" s="55"/>
+        <v>238</v>
+      </c>
+      <c r="E34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" cm="1">
+        <f t="array" ref="F34">_xlfn.SWITCH(E34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G34" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="86.4">
+      <c r="B35" s="45"/>
       <c r="C35" s="15">
         <v>4.2</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="90">
-      <c r="A36" s="44"/>
-      <c r="B36" s="55"/>
+        <v>277</v>
+      </c>
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" cm="1">
+        <f t="array" ref="F35">_xlfn.SWITCH(E35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="G35" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="72">
+      <c r="B36" s="45"/>
       <c r="C36" s="15">
         <v>4.3</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="120">
-      <c r="A37" s="44"/>
-      <c r="B37" s="55"/>
+        <v>278</v>
+      </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" cm="1">
+        <f t="array" ref="F36">_xlfn.SWITCH(E36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G36" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="115.2">
+      <c r="B37" s="45"/>
       <c r="C37" s="15">
         <v>4.4000000000000004</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
+      </c>
+      <c r="E37" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" cm="1">
+        <f t="array" ref="F37">_xlfn.SWITCH(E37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="G37" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="F38">
+        <f>SUM(F16:F37)</f>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -7043,17 +7194,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="60">
+    <row r="1" spans="1:5" ht="57.6">
       <c r="A1" s="22" t="s">
         <v>214</v>
       </c>
@@ -7080,9 +7231,9 @@
       <c r="C2" s="27">
         <v>45</v>
       </c>
-      <c r="D2" s="12" t="e">
-        <f ca="1">('Updated Sprint'!F15)*(1-(A2-1)/8)</f>
-        <v>#NAME?</v>
+      <c r="D2" s="12">
+        <f>('Updated Sprint'!F15)*(1-(A2-1)/8)</f>
+        <v>45</v>
       </c>
       <c r="E2" s="28">
         <v>1</v>
@@ -7095,13 +7246,13 @@
       <c r="B3" s="26">
         <v>46266</v>
       </c>
-      <c r="C3" s="27" t="e">
-        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E3)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D3" s="12" t="e">
-        <f ca="1">('Updated Sprint'!F15)*(1-(A3-1)/8)</f>
-        <v>#NAME?</v>
+      <c r="C3" s="27">
+        <f>('Updated Sprint'!F15)-SUM(E$2:E3)</f>
+        <v>44</v>
+      </c>
+      <c r="D3" s="12">
+        <f>('Updated Sprint'!F15)*(1-(A3-1)/8)</f>
+        <v>39.375</v>
       </c>
       <c r="E3" s="28">
         <v>0</v>
@@ -7114,13 +7265,13 @@
       <c r="B4" s="26">
         <v>46267</v>
       </c>
-      <c r="C4" s="27" t="e">
-        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E4)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D4" s="12" t="e">
-        <f ca="1">('Updated Sprint'!F15)*(1-(A4-1)/8)</f>
-        <v>#NAME?</v>
+      <c r="C4" s="27">
+        <f>('Updated Sprint'!F15)-SUM(E$2:E4)</f>
+        <v>39</v>
+      </c>
+      <c r="D4" s="12">
+        <f>('Updated Sprint'!F15)*(1-(A4-1)/8)</f>
+        <v>33.75</v>
       </c>
       <c r="E4" s="28">
         <v>5</v>
@@ -7133,13 +7284,13 @@
       <c r="B5" s="26">
         <v>46268</v>
       </c>
-      <c r="C5" s="27" t="e">
-        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E5)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D5" s="12" t="e">
-        <f ca="1">('Updated Sprint'!F15)*(1-(A5-1)/8)</f>
-        <v>#NAME?</v>
+      <c r="C5" s="27">
+        <f>('Updated Sprint'!F15)-SUM(E$2:E5)</f>
+        <v>39</v>
+      </c>
+      <c r="D5" s="12">
+        <f>('Updated Sprint'!F15)*(1-(A5-1)/8)</f>
+        <v>28.125</v>
       </c>
       <c r="E5" s="28">
         <v>0</v>
@@ -7152,13 +7303,13 @@
       <c r="B6" s="26">
         <v>46269</v>
       </c>
-      <c r="C6" s="27" t="e">
-        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E6)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D6" s="12" t="e">
-        <f ca="1">('Updated Sprint'!F15)*(1-(A6-1)/8)</f>
-        <v>#NAME?</v>
+      <c r="C6" s="27">
+        <f>('Updated Sprint'!F15)-SUM(E$2:E6)</f>
+        <v>36</v>
+      </c>
+      <c r="D6" s="12">
+        <f>('Updated Sprint'!F15)*(1-(A6-1)/8)</f>
+        <v>22.5</v>
       </c>
       <c r="E6" s="28">
         <v>3</v>
@@ -7171,13 +7322,13 @@
       <c r="B7" s="26">
         <v>46272</v>
       </c>
-      <c r="C7" s="27" t="e">
-        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E7)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D7" s="12" t="e">
-        <f ca="1">('Updated Sprint'!F15)*(1-(A7-1)/8)</f>
-        <v>#NAME?</v>
+      <c r="C7" s="27">
+        <f>('Updated Sprint'!F15)-SUM(E$2:E7)</f>
+        <v>31</v>
+      </c>
+      <c r="D7" s="12">
+        <f>('Updated Sprint'!F15)*(1-(A7-1)/8)</f>
+        <v>16.875</v>
       </c>
       <c r="E7" s="28">
         <v>5</v>
@@ -7190,13 +7341,13 @@
       <c r="B8" s="26">
         <v>46273</v>
       </c>
-      <c r="C8" s="27" t="e">
-        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E8)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D8" s="12" t="e">
-        <f ca="1">('Updated Sprint'!F15)*(1-(A8-1)/8)</f>
-        <v>#NAME?</v>
+      <c r="C8" s="27">
+        <f>('Updated Sprint'!F15)-SUM(E$2:E8)</f>
+        <v>31</v>
+      </c>
+      <c r="D8" s="12">
+        <f>('Updated Sprint'!F15)*(1-(A8-1)/8)</f>
+        <v>11.25</v>
       </c>
       <c r="E8" s="28">
         <v>0</v>
@@ -7209,13 +7360,13 @@
       <c r="B9" s="26">
         <v>46274</v>
       </c>
-      <c r="C9" s="27" t="e">
-        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E9)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D9" s="12" t="e">
-        <f ca="1">('Updated Sprint'!F15)*(1-(A9-1)/8)</f>
-        <v>#NAME?</v>
+      <c r="C9" s="27">
+        <f>('Updated Sprint'!F15)-SUM(E$2:E9)</f>
+        <v>30</v>
+      </c>
+      <c r="D9" s="12">
+        <f>('Updated Sprint'!F15)*(1-(A9-1)/8)</f>
+        <v>5.625</v>
       </c>
       <c r="E9" s="28">
         <v>1</v>
@@ -7228,13 +7379,13 @@
       <c r="B10" s="26">
         <v>46275</v>
       </c>
-      <c r="C10" s="27" t="e">
-        <f ca="1">('Updated Sprint'!F15)-SUM(E$2:E10)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D10" s="12" t="e">
-        <f ca="1">('Updated Sprint'!F15)*(1-(A10-1)/8)</f>
-        <v>#NAME?</v>
+      <c r="C10" s="27">
+        <f>('Updated Sprint'!F15)-SUM(E$2:E10)</f>
+        <v>30</v>
+      </c>
+      <c r="D10" s="12">
+        <f>('Updated Sprint'!F15)*(1-(A10-1)/8)</f>
+        <v>0</v>
       </c>
       <c r="E10" s="28">
         <v>0</v>
@@ -7251,20 +7402,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="12" t="s">

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B4D0E2-045B-45F8-AF15-C64E3B4E5798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB83E566-FA09-483D-8770-FD55689CD7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2993,15 +2993,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3009,7 +3000,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4686,632 +4686,632 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="54">
+      <c r="A3" s="51">
         <v>1</v>
       </c>
-      <c r="B3" s="49">
+      <c r="B3" s="52">
         <v>1</v>
       </c>
-      <c r="C3" s="49">
+      <c r="C3" s="52">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="52" cm="1">
+      <c r="F3" s="49" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="54"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
       <c r="D4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="54"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="54"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
+      <c r="A6" s="51"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="54"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
+      <c r="A7" s="51"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
       <c r="D7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="54"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
       <c r="D8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="54"/>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
       <c r="D9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="54"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
       <c r="D10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="54"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
+      <c r="A11" s="51"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
       <c r="D11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="54"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49">
+      <c r="A12" s="51"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52">
         <v>1.2</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="52" cm="1">
+      <c r="F12" s="49" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="54"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
       <c r="D13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="54"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
+      <c r="A14" s="51"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
       <c r="D14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="54"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="49">
+      <c r="A15" s="51"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52">
         <v>1.3</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="52" t="s">
+      <c r="E15" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="52"/>
+      <c r="F15" s="49"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="54"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
       <c r="D16" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="54"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
+      <c r="A17" s="51"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="52"/>
-      <c r="F17" s="52"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="54"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49">
+      <c r="A18" s="51"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="52">
         <v>1.4</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="52" t="s">
+      <c r="E18" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="52"/>
+      <c r="F18" s="49"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="54"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
       <c r="D19" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="54"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
+      <c r="A20" s="51"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
       <c r="D20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="54"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
       <c r="D21" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="54"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
+      <c r="A22" s="51"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="52"/>
       <c r="D22" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="54"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
+      <c r="A23" s="51"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
       <c r="D23" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="54"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49"/>
+      <c r="A24" s="51"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
       <c r="D24" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="54"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
+      <c r="A25" s="51"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
       <c r="D25" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="52"/>
-      <c r="F25" s="52"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="54"/>
-      <c r="B26" s="55">
+      <c r="A26" s="51"/>
+      <c r="B26" s="53">
         <v>2</v>
       </c>
-      <c r="C26" s="49">
+      <c r="C26" s="52">
         <v>2.1</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E26" s="53" t="s">
+      <c r="E26" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="52"/>
+      <c r="F26" s="49"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="54"/>
-      <c r="B27" s="55"/>
-      <c r="C27" s="49"/>
+      <c r="A27" s="51"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="52"/>
       <c r="D27" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="53"/>
-      <c r="F27" s="52"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="49"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="54"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="49"/>
+      <c r="A28" s="51"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="52"/>
       <c r="D28" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E28" s="53"/>
-      <c r="F28" s="52"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="49"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="54"/>
-      <c r="B29" s="55"/>
-      <c r="C29" s="51">
+      <c r="A29" s="51"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="54">
         <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="52" t="s">
+      <c r="E29" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="52"/>
+      <c r="F29" s="49"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="54"/>
-      <c r="B30" s="55"/>
-      <c r="C30" s="51"/>
+      <c r="A30" s="51"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="54"/>
       <c r="D30" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="49"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="54"/>
-      <c r="B31" s="55"/>
-      <c r="C31" s="49">
+      <c r="A31" s="51"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="52">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="52" t="s">
+      <c r="E31" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52" t="s">
+      <c r="F31" s="49"/>
+      <c r="G31" s="49" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="54"/>
-      <c r="B32" s="55"/>
-      <c r="C32" s="49"/>
+      <c r="A32" s="51"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="52"/>
       <c r="D32" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="49"/>
+      <c r="G32" s="49"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="54"/>
-      <c r="B33" s="55"/>
-      <c r="C33" s="49"/>
+      <c r="A33" s="51"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="52"/>
       <c r="D33" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="54"/>
-      <c r="B34" s="55"/>
-      <c r="C34" s="49"/>
+      <c r="A34" s="51"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="52"/>
       <c r="D34" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="54"/>
-      <c r="B35" s="55"/>
-      <c r="C35" s="49"/>
+      <c r="A35" s="51"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="52"/>
       <c r="D35" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="54"/>
-      <c r="B36" s="55"/>
-      <c r="C36" s="49"/>
+      <c r="A36" s="51"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="52"/>
       <c r="D36" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="49"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="54"/>
-      <c r="B37" s="55"/>
-      <c r="C37" s="49"/>
+      <c r="A37" s="51"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="52"/>
       <c r="D37" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="54"/>
-      <c r="B38" s="55"/>
-      <c r="C38" s="49">
+      <c r="A38" s="51"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="52">
         <v>2.4</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E38" s="52" t="s">
+      <c r="E38" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="52"/>
+      <c r="F38" s="49"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="54"/>
-      <c r="B39" s="55"/>
-      <c r="C39" s="49"/>
+      <c r="A39" s="51"/>
+      <c r="B39" s="53"/>
+      <c r="C39" s="52"/>
       <c r="D39" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="49"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="54"/>
-      <c r="B40" s="55"/>
-      <c r="C40" s="49"/>
+      <c r="A40" s="51"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="52"/>
       <c r="D40" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="49"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="54"/>
-      <c r="B41" s="55"/>
-      <c r="C41" s="49"/>
+      <c r="A41" s="51"/>
+      <c r="B41" s="53"/>
+      <c r="C41" s="52"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="54"/>
-      <c r="B42" s="55"/>
-      <c r="C42" s="49"/>
+      <c r="A42" s="51"/>
+      <c r="B42" s="53"/>
+      <c r="C42" s="52"/>
       <c r="D42" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="54"/>
-      <c r="B43" s="55"/>
-      <c r="C43" s="49"/>
+      <c r="A43" s="51"/>
+      <c r="B43" s="53"/>
+      <c r="C43" s="52"/>
       <c r="D43" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="54"/>
-      <c r="B44" s="55"/>
-      <c r="C44" s="49"/>
+      <c r="A44" s="51"/>
+      <c r="B44" s="53"/>
+      <c r="C44" s="52"/>
       <c r="D44" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="54"/>
-      <c r="B45" s="55"/>
-      <c r="C45" s="49"/>
+      <c r="A45" s="51"/>
+      <c r="B45" s="53"/>
+      <c r="C45" s="52"/>
       <c r="D45" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="54"/>
-      <c r="B46" s="55"/>
-      <c r="C46" s="49">
+      <c r="A46" s="51"/>
+      <c r="B46" s="53"/>
+      <c r="C46" s="52">
         <v>2.5</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="E46" s="53" t="s">
+      <c r="E46" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="52"/>
+      <c r="F46" s="49"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="54"/>
-      <c r="B47" s="55"/>
-      <c r="C47" s="49"/>
+      <c r="A47" s="51"/>
+      <c r="B47" s="53"/>
+      <c r="C47" s="52"/>
       <c r="D47" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E47" s="53"/>
-      <c r="F47" s="52"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="49"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="54"/>
-      <c r="B48" s="55"/>
-      <c r="C48" s="49"/>
+      <c r="A48" s="51"/>
+      <c r="B48" s="53"/>
+      <c r="C48" s="52"/>
       <c r="D48" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E48" s="53"/>
-      <c r="F48" s="52"/>
+      <c r="E48" s="50"/>
+      <c r="F48" s="49"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="54"/>
-      <c r="B49" s="55"/>
-      <c r="C49" s="49"/>
+      <c r="A49" s="51"/>
+      <c r="B49" s="53"/>
+      <c r="C49" s="52"/>
       <c r="D49" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E49" s="53"/>
-      <c r="F49" s="52"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="49"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="54"/>
-      <c r="B50" s="55"/>
-      <c r="C50" s="49">
+      <c r="A50" s="51"/>
+      <c r="B50" s="53"/>
+      <c r="C50" s="52">
         <v>2.7</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E50" s="52" t="s">
+      <c r="E50" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="F50" s="52"/>
+      <c r="F50" s="49"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="54"/>
-      <c r="B51" s="55"/>
-      <c r="C51" s="49"/>
+      <c r="A51" s="51"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="52"/>
       <c r="D51" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E51" s="52"/>
-      <c r="F51" s="52"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="54"/>
-      <c r="B52" s="55"/>
-      <c r="C52" s="49"/>
+      <c r="A52" s="51"/>
+      <c r="B52" s="53"/>
+      <c r="C52" s="52"/>
       <c r="D52" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="49"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="54"/>
-      <c r="B53" s="55"/>
-      <c r="C53" s="49"/>
+      <c r="A53" s="51"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="52"/>
       <c r="D53" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E53" s="52"/>
-      <c r="F53" s="52"/>
+      <c r="E53" s="49"/>
+      <c r="F53" s="49"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="54"/>
-      <c r="B54" s="55"/>
-      <c r="C54" s="49"/>
+      <c r="A54" s="51"/>
+      <c r="B54" s="53"/>
+      <c r="C54" s="52"/>
       <c r="D54" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E54" s="52"/>
-      <c r="F54" s="52"/>
+      <c r="E54" s="49"/>
+      <c r="F54" s="49"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="54"/>
-      <c r="B55" s="55"/>
-      <c r="C55" s="49"/>
+      <c r="A55" s="51"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="52"/>
       <c r="D55" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E55" s="52"/>
-      <c r="F55" s="52"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="49"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="54"/>
-      <c r="B56" s="55"/>
-      <c r="C56" s="49"/>
+      <c r="A56" s="51"/>
+      <c r="B56" s="53"/>
+      <c r="C56" s="52"/>
       <c r="D56" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="52"/>
-      <c r="F56" s="52"/>
+      <c r="E56" s="49"/>
+      <c r="F56" s="49"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="54"/>
-      <c r="B57" s="55"/>
-      <c r="C57" s="49"/>
+      <c r="A57" s="51"/>
+      <c r="B57" s="53"/>
+      <c r="C57" s="52"/>
       <c r="D57" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E57" s="52"/>
-      <c r="F57" s="52"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="54"/>
-      <c r="B58" s="55"/>
-      <c r="C58" s="49"/>
+      <c r="A58" s="51"/>
+      <c r="B58" s="53"/>
+      <c r="C58" s="52"/>
       <c r="D58" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E58" s="52"/>
-      <c r="F58" s="52"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
-      <c r="B59" s="49">
+      <c r="B59" s="52">
         <v>3</v>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="52">
         <v>3.1</v>
       </c>
       <c r="D59" s="7" t="s">
@@ -5320,48 +5320,48 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="19"/>
-      <c r="B60" s="49"/>
-      <c r="C60" s="49"/>
+      <c r="B60" s="52"/>
+      <c r="C60" s="52"/>
       <c r="D60" s="7" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="19"/>
-      <c r="B61" s="49"/>
-      <c r="C61" s="49"/>
+      <c r="B61" s="52"/>
+      <c r="C61" s="52"/>
       <c r="D61" s="7" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="19"/>
-      <c r="B62" s="49"/>
-      <c r="C62" s="49"/>
+      <c r="B62" s="52"/>
+      <c r="C62" s="52"/>
       <c r="D62" s="7" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="19"/>
-      <c r="B63" s="49"/>
-      <c r="C63" s="49"/>
+      <c r="B63" s="52"/>
+      <c r="C63" s="52"/>
       <c r="D63" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="19"/>
-      <c r="B64" s="49"/>
-      <c r="C64" s="49"/>
+      <c r="B64" s="52"/>
+      <c r="C64" s="52"/>
       <c r="D64" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="19"/>
-      <c r="B65" s="49"/>
-      <c r="C65" s="49">
+      <c r="B65" s="52"/>
+      <c r="C65" s="52">
         <v>3.2</v>
       </c>
       <c r="D65" s="7" t="s">
@@ -5370,96 +5370,96 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="19"/>
-      <c r="B66" s="49"/>
-      <c r="C66" s="49"/>
+      <c r="B66" s="52"/>
+      <c r="C66" s="52"/>
       <c r="D66" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="19"/>
-      <c r="B67" s="49"/>
-      <c r="C67" s="49"/>
+      <c r="B67" s="52"/>
+      <c r="C67" s="52"/>
       <c r="D67" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="19"/>
-      <c r="B68" s="49"/>
-      <c r="C68" s="49"/>
+      <c r="B68" s="52"/>
+      <c r="C68" s="52"/>
       <c r="D68" s="7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="19"/>
-      <c r="B69" s="49"/>
-      <c r="C69" s="49"/>
+      <c r="B69" s="52"/>
+      <c r="C69" s="52"/>
       <c r="D69" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="19"/>
-      <c r="B70" s="49"/>
-      <c r="C70" s="49"/>
+      <c r="B70" s="52"/>
+      <c r="C70" s="52"/>
       <c r="D70" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="19"/>
-      <c r="B71" s="49"/>
-      <c r="C71" s="49"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="52"/>
       <c r="D71" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="19"/>
-      <c r="B72" s="49"/>
-      <c r="C72" s="49"/>
+      <c r="B72" s="52"/>
+      <c r="C72" s="52"/>
       <c r="D72" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="19"/>
-      <c r="B73" s="49"/>
-      <c r="C73" s="49"/>
+      <c r="B73" s="52"/>
+      <c r="C73" s="52"/>
       <c r="D73" s="7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="19"/>
-      <c r="B74" s="49"/>
-      <c r="C74" s="49"/>
+      <c r="B74" s="52"/>
+      <c r="C74" s="52"/>
       <c r="D74" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="19"/>
-      <c r="B75" s="49"/>
-      <c r="C75" s="49"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="52"/>
       <c r="D75" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="19"/>
-      <c r="B76" s="49"/>
-      <c r="C76" s="49"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
       <c r="D76" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="19"/>
-      <c r="B77" s="49"/>
-      <c r="C77" s="49">
+      <c r="B77" s="52"/>
+      <c r="C77" s="52">
         <v>3.3</v>
       </c>
       <c r="D77" s="7" t="s">
@@ -5468,88 +5468,88 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="19"/>
-      <c r="B78" s="49"/>
-      <c r="C78" s="49"/>
+      <c r="B78" s="52"/>
+      <c r="C78" s="52"/>
       <c r="D78" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="19"/>
-      <c r="B79" s="49"/>
-      <c r="C79" s="49"/>
+      <c r="B79" s="52"/>
+      <c r="C79" s="52"/>
       <c r="D79" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="19"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
+      <c r="B80" s="52"/>
+      <c r="C80" s="52"/>
       <c r="D80" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="19"/>
-      <c r="B81" s="49"/>
-      <c r="C81" s="49"/>
+      <c r="B81" s="52"/>
+      <c r="C81" s="52"/>
       <c r="D81" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="19"/>
-      <c r="B82" s="49"/>
-      <c r="C82" s="49"/>
+      <c r="B82" s="52"/>
+      <c r="C82" s="52"/>
       <c r="D82" s="7" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="19"/>
-      <c r="B83" s="49"/>
-      <c r="C83" s="49"/>
+      <c r="B83" s="52"/>
+      <c r="C83" s="52"/>
       <c r="D83" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="19"/>
-      <c r="B84" s="49"/>
-      <c r="C84" s="49"/>
+      <c r="B84" s="52"/>
+      <c r="C84" s="52"/>
       <c r="D84" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="19"/>
-      <c r="B85" s="49"/>
-      <c r="C85" s="49"/>
+      <c r="B85" s="52"/>
+      <c r="C85" s="52"/>
       <c r="D85" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="19"/>
-      <c r="B86" s="49"/>
-      <c r="C86" s="49"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="52"/>
       <c r="D86" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="19"/>
-      <c r="B87" s="49"/>
-      <c r="C87" s="49"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
       <c r="D87" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="19"/>
-      <c r="B88" s="49"/>
-      <c r="C88" s="49">
+      <c r="B88" s="52"/>
+      <c r="C88" s="52">
         <v>3.4</v>
       </c>
       <c r="D88" s="15" t="s">
@@ -5558,104 +5558,104 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="19"/>
-      <c r="B89" s="49"/>
-      <c r="C89" s="49"/>
+      <c r="B89" s="52"/>
+      <c r="C89" s="52"/>
       <c r="D89" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="19"/>
-      <c r="B90" s="49"/>
-      <c r="C90" s="49"/>
+      <c r="B90" s="52"/>
+      <c r="C90" s="52"/>
       <c r="D90" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="19"/>
-      <c r="B91" s="49"/>
-      <c r="C91" s="49"/>
+      <c r="B91" s="52"/>
+      <c r="C91" s="52"/>
       <c r="D91" s="7" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="19"/>
-      <c r="B92" s="49"/>
-      <c r="C92" s="49"/>
+      <c r="B92" s="52"/>
+      <c r="C92" s="52"/>
       <c r="D92" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="19"/>
-      <c r="B93" s="49"/>
-      <c r="C93" s="49"/>
+      <c r="B93" s="52"/>
+      <c r="C93" s="52"/>
       <c r="D93" s="7" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="19"/>
-      <c r="B94" s="49"/>
-      <c r="C94" s="49"/>
+      <c r="B94" s="52"/>
+      <c r="C94" s="52"/>
       <c r="D94" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="19"/>
-      <c r="B95" s="49"/>
-      <c r="C95" s="49"/>
+      <c r="B95" s="52"/>
+      <c r="C95" s="52"/>
       <c r="D95" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="19"/>
-      <c r="B96" s="49"/>
-      <c r="C96" s="49"/>
+      <c r="B96" s="52"/>
+      <c r="C96" s="52"/>
       <c r="D96" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="19"/>
-      <c r="B97" s="49"/>
-      <c r="C97" s="49"/>
+      <c r="B97" s="52"/>
+      <c r="C97" s="52"/>
       <c r="D97" s="7" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="19"/>
-      <c r="B98" s="49"/>
-      <c r="C98" s="49"/>
+      <c r="B98" s="52"/>
+      <c r="C98" s="52"/>
       <c r="D98" s="7" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="19"/>
-      <c r="B99" s="49"/>
-      <c r="C99" s="49"/>
+      <c r="B99" s="52"/>
+      <c r="C99" s="52"/>
       <c r="D99" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="19"/>
-      <c r="B100" s="49"/>
-      <c r="C100" s="49"/>
+      <c r="B100" s="52"/>
+      <c r="C100" s="52"/>
       <c r="D100" s="7" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="19"/>
-      <c r="B101" s="49"/>
-      <c r="C101" s="49">
+      <c r="B101" s="52"/>
+      <c r="C101" s="52">
         <v>3.5</v>
       </c>
       <c r="D101" s="11" t="s">
@@ -5664,72 +5664,72 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="19"/>
-      <c r="B102" s="49"/>
-      <c r="C102" s="49"/>
+      <c r="B102" s="52"/>
+      <c r="C102" s="52"/>
       <c r="D102" s="7" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="19"/>
-      <c r="B103" s="49"/>
-      <c r="C103" s="49"/>
+      <c r="B103" s="52"/>
+      <c r="C103" s="52"/>
       <c r="D103" s="7" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="19"/>
-      <c r="B104" s="49"/>
-      <c r="C104" s="49"/>
+      <c r="B104" s="52"/>
+      <c r="C104" s="52"/>
       <c r="D104" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="19"/>
-      <c r="B105" s="49"/>
-      <c r="C105" s="49"/>
+      <c r="B105" s="52"/>
+      <c r="C105" s="52"/>
       <c r="D105" s="7" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="19"/>
-      <c r="B106" s="49"/>
-      <c r="C106" s="49"/>
+      <c r="B106" s="52"/>
+      <c r="C106" s="52"/>
       <c r="D106" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="19"/>
-      <c r="B107" s="49"/>
-      <c r="C107" s="49"/>
+      <c r="B107" s="52"/>
+      <c r="C107" s="52"/>
       <c r="D107" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="19"/>
-      <c r="B108" s="49"/>
-      <c r="C108" s="49"/>
+      <c r="B108" s="52"/>
+      <c r="C108" s="52"/>
       <c r="D108" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="19"/>
-      <c r="B109" s="49"/>
-      <c r="C109" s="49"/>
+      <c r="B109" s="52"/>
+      <c r="C109" s="52"/>
       <c r="D109" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="19"/>
-      <c r="B110" s="49"/>
-      <c r="C110" s="49">
+      <c r="B110" s="52"/>
+      <c r="C110" s="52">
         <v>3.6</v>
       </c>
       <c r="D110" s="7" t="s">
@@ -5738,48 +5738,48 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19"/>
-      <c r="B111" s="49"/>
-      <c r="C111" s="49"/>
+      <c r="B111" s="52"/>
+      <c r="C111" s="52"/>
       <c r="D111" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19"/>
-      <c r="B112" s="49"/>
-      <c r="C112" s="49"/>
+      <c r="B112" s="52"/>
+      <c r="C112" s="52"/>
       <c r="D112" s="7" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="19"/>
-      <c r="B113" s="49"/>
-      <c r="C113" s="49"/>
+      <c r="B113" s="52"/>
+      <c r="C113" s="52"/>
       <c r="D113" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="19"/>
-      <c r="B114" s="49"/>
-      <c r="C114" s="49"/>
+      <c r="B114" s="52"/>
+      <c r="C114" s="52"/>
       <c r="D114" s="7" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="19"/>
-      <c r="B115" s="49"/>
-      <c r="C115" s="49"/>
+      <c r="B115" s="52"/>
+      <c r="C115" s="52"/>
       <c r="D115" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="19"/>
-      <c r="B116" s="49"/>
-      <c r="C116" s="49">
+      <c r="B116" s="52"/>
+      <c r="C116" s="52">
         <v>3.7</v>
       </c>
       <c r="D116" s="7" t="s">
@@ -5788,88 +5788,88 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="19"/>
-      <c r="B117" s="49"/>
-      <c r="C117" s="49"/>
+      <c r="B117" s="52"/>
+      <c r="C117" s="52"/>
       <c r="D117" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="19"/>
-      <c r="B118" s="49"/>
-      <c r="C118" s="49"/>
+      <c r="B118" s="52"/>
+      <c r="C118" s="52"/>
       <c r="D118" s="7" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="19"/>
-      <c r="B119" s="49"/>
-      <c r="C119" s="49"/>
+      <c r="B119" s="52"/>
+      <c r="C119" s="52"/>
       <c r="D119" s="7" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="19"/>
-      <c r="B120" s="49"/>
-      <c r="C120" s="49"/>
+      <c r="B120" s="52"/>
+      <c r="C120" s="52"/>
       <c r="D120" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="19"/>
-      <c r="B121" s="49"/>
-      <c r="C121" s="49"/>
+      <c r="B121" s="52"/>
+      <c r="C121" s="52"/>
       <c r="D121" s="7" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="19"/>
-      <c r="B122" s="49"/>
-      <c r="C122" s="49"/>
+      <c r="B122" s="52"/>
+      <c r="C122" s="52"/>
       <c r="D122" s="7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="19"/>
-      <c r="B123" s="49"/>
-      <c r="C123" s="49"/>
+      <c r="B123" s="52"/>
+      <c r="C123" s="52"/>
       <c r="D123" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="19"/>
-      <c r="B124" s="49"/>
-      <c r="C124" s="49"/>
+      <c r="B124" s="52"/>
+      <c r="C124" s="52"/>
       <c r="D124" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="19"/>
-      <c r="B125" s="49"/>
-      <c r="C125" s="49"/>
+      <c r="B125" s="52"/>
+      <c r="C125" s="52"/>
       <c r="D125" s="7" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="19"/>
-      <c r="B126" s="49"/>
-      <c r="C126" s="49"/>
+      <c r="B126" s="52"/>
+      <c r="C126" s="52"/>
       <c r="D126" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="19"/>
-      <c r="B127" s="49"/>
-      <c r="C127" s="49">
+      <c r="B127" s="52"/>
+      <c r="C127" s="52">
         <v>3.8</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -5878,80 +5878,80 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="19"/>
-      <c r="B128" s="49"/>
-      <c r="C128" s="49"/>
+      <c r="B128" s="52"/>
+      <c r="C128" s="52"/>
       <c r="D128" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="19"/>
-      <c r="B129" s="49"/>
-      <c r="C129" s="49"/>
+      <c r="B129" s="52"/>
+      <c r="C129" s="52"/>
       <c r="D129" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="19"/>
-      <c r="B130" s="49"/>
-      <c r="C130" s="49"/>
+      <c r="B130" s="52"/>
+      <c r="C130" s="52"/>
       <c r="D130" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="19"/>
-      <c r="B131" s="49"/>
-      <c r="C131" s="49"/>
+      <c r="B131" s="52"/>
+      <c r="C131" s="52"/>
       <c r="D131" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="19"/>
-      <c r="B132" s="49"/>
-      <c r="C132" s="49"/>
+      <c r="B132" s="52"/>
+      <c r="C132" s="52"/>
       <c r="D132" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="19"/>
-      <c r="B133" s="49"/>
-      <c r="C133" s="49"/>
+      <c r="B133" s="52"/>
+      <c r="C133" s="52"/>
       <c r="D133" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="19"/>
-      <c r="B134" s="49"/>
-      <c r="C134" s="49"/>
+      <c r="B134" s="52"/>
+      <c r="C134" s="52"/>
       <c r="D134" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="19"/>
-      <c r="B135" s="49"/>
-      <c r="C135" s="49"/>
+      <c r="B135" s="52"/>
+      <c r="C135" s="52"/>
       <c r="D135" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="19"/>
-      <c r="B136" s="49"/>
-      <c r="C136" s="49"/>
+      <c r="B136" s="52"/>
+      <c r="C136" s="52"/>
       <c r="D136" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="19"/>
-      <c r="B137" s="49"/>
-      <c r="C137" s="49">
+      <c r="B137" s="52"/>
+      <c r="C137" s="52">
         <v>3.9</v>
       </c>
       <c r="D137" s="7" t="s">
@@ -5960,40 +5960,40 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="19"/>
-      <c r="B138" s="49"/>
-      <c r="C138" s="49"/>
+      <c r="B138" s="52"/>
+      <c r="C138" s="52"/>
       <c r="D138" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="19"/>
-      <c r="B139" s="49"/>
-      <c r="C139" s="49"/>
+      <c r="B139" s="52"/>
+      <c r="C139" s="52"/>
       <c r="D139" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="19"/>
-      <c r="B140" s="49"/>
-      <c r="C140" s="49"/>
+      <c r="B140" s="52"/>
+      <c r="C140" s="52"/>
       <c r="D140" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="19"/>
-      <c r="B141" s="49"/>
-      <c r="C141" s="49"/>
+      <c r="B141" s="52"/>
+      <c r="C141" s="52"/>
       <c r="D141" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
-      <c r="B142" s="49"/>
-      <c r="C142" s="50">
+      <c r="B142" s="52"/>
+      <c r="C142" s="55">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -6002,122 +6002,122 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
-      <c r="B143" s="49"/>
-      <c r="C143" s="50"/>
+      <c r="B143" s="52"/>
+      <c r="C143" s="55"/>
       <c r="D143" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
-      <c r="B144" s="49"/>
-      <c r="C144" s="50"/>
+      <c r="B144" s="52"/>
+      <c r="C144" s="55"/>
       <c r="D144" s="7" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
-      <c r="B145" s="49"/>
-      <c r="C145" s="50"/>
+      <c r="B145" s="52"/>
+      <c r="C145" s="55"/>
       <c r="D145" s="7" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
-      <c r="B146" s="49"/>
-      <c r="C146" s="50"/>
+      <c r="B146" s="52"/>
+      <c r="C146" s="55"/>
       <c r="D146" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
-      <c r="B147" s="49"/>
-      <c r="C147" s="50"/>
+      <c r="B147" s="52"/>
+      <c r="C147" s="55"/>
       <c r="D147" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
-      <c r="B148" s="49"/>
-      <c r="C148" s="50"/>
+      <c r="B148" s="52"/>
+      <c r="C148" s="55"/>
       <c r="D148" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
-      <c r="B149" s="49"/>
-      <c r="C149" s="50"/>
+      <c r="B149" s="52"/>
+      <c r="C149" s="55"/>
       <c r="D149" s="7" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
-      <c r="B150" s="49"/>
-      <c r="C150" s="50"/>
+      <c r="B150" s="52"/>
+      <c r="C150" s="55"/>
       <c r="D150" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
-      <c r="B151" s="49"/>
-      <c r="C151" s="50"/>
+      <c r="B151" s="52"/>
+      <c r="C151" s="55"/>
       <c r="D151" s="7" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
-      <c r="B152" s="49"/>
-      <c r="C152" s="50"/>
+      <c r="B152" s="52"/>
+      <c r="C152" s="55"/>
       <c r="D152" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
-      <c r="B153" s="49"/>
-      <c r="C153" s="50"/>
+      <c r="B153" s="52"/>
+      <c r="C153" s="55"/>
       <c r="D153" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
-      <c r="B154" s="49"/>
-      <c r="C154" s="50"/>
+      <c r="B154" s="52"/>
+      <c r="C154" s="55"/>
       <c r="D154" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
-      <c r="B155" s="49"/>
-      <c r="C155" s="50"/>
+      <c r="B155" s="52"/>
+      <c r="C155" s="55"/>
       <c r="D155" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
-      <c r="B156" s="49"/>
-      <c r="C156" s="50"/>
+      <c r="B156" s="52"/>
+      <c r="C156" s="55"/>
       <c r="D156" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="20"/>
-      <c r="B157" s="49">
+      <c r="B157" s="52">
         <v>4</v>
       </c>
-      <c r="C157" s="49">
+      <c r="C157" s="52">
         <v>4.0999999999999996</v>
       </c>
       <c r="D157" s="7" t="s">
@@ -6126,32 +6126,32 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="19"/>
-      <c r="B158" s="49"/>
-      <c r="C158" s="49"/>
+      <c r="B158" s="52"/>
+      <c r="C158" s="52"/>
       <c r="D158" s="7" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="19"/>
-      <c r="B159" s="49"/>
-      <c r="C159" s="49"/>
+      <c r="B159" s="52"/>
+      <c r="C159" s="52"/>
       <c r="D159" s="7" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="19"/>
-      <c r="B160" s="49"/>
-      <c r="C160" s="49"/>
+      <c r="B160" s="52"/>
+      <c r="C160" s="52"/>
       <c r="D160" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="19"/>
-      <c r="B161" s="49"/>
-      <c r="C161" s="49">
+      <c r="B161" s="52"/>
+      <c r="C161" s="52">
         <v>4.2</v>
       </c>
       <c r="D161" s="7" t="s">
@@ -6160,56 +6160,56 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="19"/>
-      <c r="B162" s="49"/>
-      <c r="C162" s="49"/>
+      <c r="B162" s="52"/>
+      <c r="C162" s="52"/>
       <c r="D162" s="7" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="19"/>
-      <c r="B163" s="49"/>
-      <c r="C163" s="49"/>
+      <c r="B163" s="52"/>
+      <c r="C163" s="52"/>
       <c r="D163" s="7" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="19"/>
-      <c r="B164" s="49"/>
-      <c r="C164" s="49"/>
+      <c r="B164" s="52"/>
+      <c r="C164" s="52"/>
       <c r="D164" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="19"/>
-      <c r="B165" s="49"/>
-      <c r="C165" s="49"/>
+      <c r="B165" s="52"/>
+      <c r="C165" s="52"/>
       <c r="D165" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="19"/>
-      <c r="B166" s="49"/>
-      <c r="C166" s="49"/>
+      <c r="B166" s="52"/>
+      <c r="C166" s="52"/>
       <c r="D166" s="7" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="19"/>
-      <c r="B167" s="49"/>
-      <c r="C167" s="49"/>
+      <c r="B167" s="52"/>
+      <c r="C167" s="52"/>
       <c r="D167" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="19"/>
-      <c r="B168" s="49"/>
-      <c r="C168" s="49">
+      <c r="B168" s="52"/>
+      <c r="C168" s="52">
         <v>4.3</v>
       </c>
       <c r="D168" s="7" t="s">
@@ -6218,48 +6218,48 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="19"/>
-      <c r="B169" s="49"/>
-      <c r="C169" s="49"/>
+      <c r="B169" s="52"/>
+      <c r="C169" s="52"/>
       <c r="D169" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="19"/>
-      <c r="B170" s="49"/>
-      <c r="C170" s="49"/>
+      <c r="B170" s="52"/>
+      <c r="C170" s="52"/>
       <c r="D170" s="7" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="19"/>
-      <c r="B171" s="49"/>
-      <c r="C171" s="49"/>
+      <c r="B171" s="52"/>
+      <c r="C171" s="52"/>
       <c r="D171" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="19"/>
-      <c r="B172" s="49"/>
-      <c r="C172" s="49"/>
+      <c r="B172" s="52"/>
+      <c r="C172" s="52"/>
       <c r="D172" s="7" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="19"/>
-      <c r="B173" s="49"/>
-      <c r="C173" s="49"/>
+      <c r="B173" s="52"/>
+      <c r="C173" s="52"/>
       <c r="D173" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="19"/>
-      <c r="B174" s="49"/>
-      <c r="C174" s="49">
+      <c r="B174" s="52"/>
+      <c r="C174" s="52">
         <v>4.4000000000000004</v>
       </c>
       <c r="D174" s="7" t="s">
@@ -6268,56 +6268,56 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="19"/>
-      <c r="B175" s="49"/>
-      <c r="C175" s="49"/>
+      <c r="B175" s="52"/>
+      <c r="C175" s="52"/>
       <c r="D175" s="7" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="19"/>
-      <c r="B176" s="49"/>
-      <c r="C176" s="49"/>
+      <c r="B176" s="52"/>
+      <c r="C176" s="52"/>
       <c r="D176" s="7" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="19"/>
-      <c r="B177" s="49"/>
-      <c r="C177" s="49"/>
+      <c r="B177" s="52"/>
+      <c r="C177" s="52"/>
       <c r="D177" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="19"/>
-      <c r="B178" s="49"/>
-      <c r="C178" s="49"/>
+      <c r="B178" s="52"/>
+      <c r="C178" s="52"/>
       <c r="D178" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="19"/>
-      <c r="B179" s="49"/>
-      <c r="C179" s="49"/>
+      <c r="B179" s="52"/>
+      <c r="C179" s="52"/>
       <c r="D179" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="19"/>
-      <c r="B180" s="49"/>
-      <c r="C180" s="49"/>
+      <c r="B180" s="52"/>
+      <c r="C180" s="52"/>
       <c r="D180" s="7" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="19"/>
-      <c r="B181" s="49"/>
-      <c r="C181" s="49"/>
+      <c r="B181" s="52"/>
+      <c r="C181" s="52"/>
       <c r="D181" s="7" t="s">
         <v>57</v>
       </c>
@@ -6325,41 +6325,6 @@
   </sheetData>
   <autoFilter ref="A2:J181" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="51">
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -6376,6 +6341,41 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6395,6 +6395,7 @@
     <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -3,16 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB83E566-FA09-483D-8770-FD55689CD7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6ED44A-1EAB-4888-B5B3-205B280BC7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="4" r:id="rId1"/>
     <sheet name="Sprint Backlog" sheetId="8" r:id="rId2"/>
     <sheet name="Updated Sprint" sheetId="10" r:id="rId3"/>
-    <sheet name="Burndown Chart" sheetId="9" r:id="rId4"/>
-    <sheet name="T Shirt sizing rules" sheetId="5" r:id="rId5"/>
+    <sheet name="Sprint 1 Burndown" sheetId="9" r:id="rId4"/>
+    <sheet name="Sprint 2 Burndown" sheetId="11" r:id="rId5"/>
+    <sheet name="T Shirt sizing rules" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sprint Backlog'!$A$2:$J$181</definedName>
@@ -723,7 +724,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{BA0C55A6-9B5D-4FD2-952C-1E24D2AF91E0}">
+    <comment ref="D27" authorId="0" shapeId="0" xr:uid="{BA0C55A6-9B5D-4FD2-952C-1E24D2AF91E0}">
       <text>
         <r>
           <rPr>
@@ -753,7 +754,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -775,7 +776,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="290">
   <si>
     <t>Work Item</t>
   </si>
@@ -2679,6 +2680,36 @@
   </si>
   <si>
     <t>Vidit,Azad</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
 </sst>
 </file>
@@ -2881,7 +2912,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2993,6 +3024,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3000,19 +3040,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3047,6 +3084,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Sprint</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IN" baseline="0"/>
+              <a:t> 1 Burndown</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3087,7 +3154,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Burndown Chart'!$C$1</c:f>
+              <c:f>'Sprint 1 Burndown'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3110,7 +3177,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Burndown Chart'!$B$2:$B$11</c:f>
+              <c:f>'Sprint 1 Burndown'!$B$2:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3146,7 +3213,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Burndown Chart'!$C$2:$C$11</c:f>
+              <c:f>'Sprint 1 Burndown'!$C$2:$C$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3192,7 +3259,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Burndown Chart'!$D$1</c:f>
+              <c:f>'Sprint 1 Burndown'!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3215,7 +3282,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Burndown Chart'!$B$2:$B$11</c:f>
+              <c:f>'Sprint 1 Burndown'!$B$2:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3251,7 +3318,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Burndown Chart'!$D$2:$D$11</c:f>
+              <c:f>'Sprint 1 Burndown'!$D$2:$D$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3297,7 +3364,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Burndown Chart'!$E$1</c:f>
+              <c:f>'Sprint 1 Burndown'!$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3320,7 +3387,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Burndown Chart'!$B$2:$B$11</c:f>
+              <c:f>'Sprint 1 Burndown'!$B$2:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3356,7 +3423,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Burndown Chart'!$E$2:$E$11</c:f>
+              <c:f>'Sprint 1 Burndown'!$E$2:$E$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3599,6 +3666,616 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Sprint</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IN" baseline="0"/>
+              <a:t> 2 Burndown</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 2 Burndown'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Actual Story Points Left</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sprint 2 Burndown'!$B$2:$B$20</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>46286</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46287</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46288</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46289</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46290</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46291</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46292</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46293</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46294</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46295</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46296</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46297</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46298</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46299</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46300</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46301</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46302</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46303</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46304</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 2 Burndown'!$C$2:$C$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AD70-4417-BF95-7A8337088C83}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 2 Burndown'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Excepted Story Points Left</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sprint 2 Burndown'!$B$2:$B$20</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>46286</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46287</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46288</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46289</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46290</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46291</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46292</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46293</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46294</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46295</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46296</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46297</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46298</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46299</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46300</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46301</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46302</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46303</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46304</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 2 Burndown'!$D$2:$D$20</c:f>
+              <c:numCache>
+                <c:formatCode>@</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>47.222222222222221</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44.444444444444443</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>41.666666666666671</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>38.888888888888893</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>36.111111111111107</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>33.333333333333336</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30.555555555555557</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>27.777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>22.222222222222221</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>19.444444444444443</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>16.666666666666668</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13.888888888888889</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>11.111111111111111</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.3333333333333321</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.555555555555558</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AD70-4417-BF95-7A8337088C83}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1122693840"/>
+        <c:axId val="1094183408"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1122693840"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1094183408"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1094183408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1122693840"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -3639,7 +4316,563 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4196,6 +5429,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{617EFBFD-BF01-06B2-F3BB-DA068949924D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -4686,632 +5960,632 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="51">
+      <c r="A3" s="54">
         <v>1</v>
       </c>
-      <c r="B3" s="52">
+      <c r="B3" s="49">
         <v>1</v>
       </c>
-      <c r="C3" s="52">
+      <c r="C3" s="49">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="49" t="s">
+      <c r="E3" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="49" cm="1">
+      <c r="F3" s="52" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
       <c r="D4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="51"/>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
+      <c r="A5" s="54"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="51"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
+      <c r="A6" s="54"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="51"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
+      <c r="A7" s="54"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="51"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
+      <c r="A8" s="54"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
       <c r="D8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="51"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
+      <c r="A9" s="54"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
       <c r="D9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
+      <c r="A10" s="54"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
       <c r="D10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="51"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
+      <c r="A11" s="54"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="51"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52">
+      <c r="A12" s="54"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49">
         <v>1.2</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="49" t="s">
+      <c r="E12" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="49" cm="1">
+      <c r="F12" s="52" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="51"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
+      <c r="A13" s="54"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="51"/>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
+      <c r="A14" s="54"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="51"/>
-      <c r="B15" s="52"/>
-      <c r="C15" s="52">
+      <c r="A15" s="54"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49">
         <v>1.3</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="49" t="s">
+      <c r="E15" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="49"/>
+      <c r="F15" s="52"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="51"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
+      <c r="A16" s="54"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
       <c r="D16" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="51"/>
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
+      <c r="A17" s="54"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
       <c r="D17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="51"/>
-      <c r="B18" s="52"/>
-      <c r="C18" s="52">
+      <c r="A18" s="54"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49">
         <v>1.4</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="49" t="s">
+      <c r="E18" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="49"/>
+      <c r="F18" s="52"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="51"/>
-      <c r="B19" s="52"/>
-      <c r="C19" s="52"/>
+      <c r="A19" s="54"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
       <c r="D19" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="51"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
+      <c r="A20" s="54"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
       <c r="D20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="51"/>
-      <c r="B21" s="52"/>
-      <c r="C21" s="52"/>
+      <c r="A21" s="54"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
       <c r="D21" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="51"/>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
+      <c r="A22" s="54"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
       <c r="D22" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="51"/>
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
+      <c r="A23" s="54"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
       <c r="D23" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="51"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
+      <c r="A24" s="54"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
       <c r="D24" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="51"/>
-      <c r="B25" s="52"/>
-      <c r="C25" s="52"/>
+      <c r="A25" s="54"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
       <c r="D25" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="51"/>
-      <c r="B26" s="53">
+      <c r="A26" s="54"/>
+      <c r="B26" s="55">
         <v>2</v>
       </c>
-      <c r="C26" s="52">
+      <c r="C26" s="49">
         <v>2.1</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E26" s="50" t="s">
+      <c r="E26" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="49"/>
+      <c r="F26" s="52"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="51"/>
-      <c r="B27" s="53"/>
-      <c r="C27" s="52"/>
+      <c r="A27" s="54"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="49"/>
       <c r="D27" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="50"/>
-      <c r="F27" s="49"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="52"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="51"/>
-      <c r="B28" s="53"/>
-      <c r="C28" s="52"/>
+      <c r="A28" s="54"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="49"/>
       <c r="D28" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E28" s="50"/>
-      <c r="F28" s="49"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="52"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="51"/>
-      <c r="B29" s="53"/>
-      <c r="C29" s="54">
+      <c r="A29" s="54"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="51">
         <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="49" t="s">
+      <c r="E29" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="49"/>
+      <c r="F29" s="52"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="51"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="54"/>
+      <c r="A30" s="54"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="51"/>
       <c r="D30" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="51"/>
-      <c r="B31" s="53"/>
-      <c r="C31" s="52">
+      <c r="A31" s="54"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="49">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="49" t="s">
+      <c r="E31" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49" t="s">
+      <c r="F31" s="52"/>
+      <c r="G31" s="52" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="51"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="52"/>
+      <c r="A32" s="54"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="49"/>
       <c r="D32" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="51"/>
-      <c r="B33" s="53"/>
-      <c r="C33" s="52"/>
+      <c r="A33" s="54"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="49"/>
       <c r="D33" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="49"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="49"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="51"/>
-      <c r="B34" s="53"/>
-      <c r="C34" s="52"/>
+      <c r="A34" s="54"/>
+      <c r="B34" s="55"/>
+      <c r="C34" s="49"/>
       <c r="D34" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="51"/>
-      <c r="B35" s="53"/>
-      <c r="C35" s="52"/>
+      <c r="A35" s="54"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="49"/>
       <c r="D35" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="49"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="51"/>
-      <c r="B36" s="53"/>
-      <c r="C36" s="52"/>
+      <c r="A36" s="54"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="49"/>
       <c r="D36" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="51"/>
-      <c r="B37" s="53"/>
-      <c r="C37" s="52"/>
+      <c r="A37" s="54"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="49"/>
       <c r="D37" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E37" s="49"/>
-      <c r="F37" s="49"/>
-      <c r="G37" s="49"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="51"/>
-      <c r="B38" s="53"/>
-      <c r="C38" s="52">
+      <c r="A38" s="54"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="49">
         <v>2.4</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E38" s="49" t="s">
+      <c r="E38" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="49"/>
+      <c r="F38" s="52"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="51"/>
-      <c r="B39" s="53"/>
-      <c r="C39" s="52"/>
+      <c r="A39" s="54"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="49"/>
       <c r="D39" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E39" s="49"/>
-      <c r="F39" s="49"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="51"/>
-      <c r="B40" s="53"/>
-      <c r="C40" s="52"/>
+      <c r="A40" s="54"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="49"/>
       <c r="D40" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E40" s="49"/>
-      <c r="F40" s="49"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="51"/>
-      <c r="B41" s="53"/>
-      <c r="C41" s="52"/>
+      <c r="A41" s="54"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="49"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="49"/>
-      <c r="F41" s="49"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="51"/>
-      <c r="B42" s="53"/>
-      <c r="C42" s="52"/>
+      <c r="A42" s="54"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="49"/>
       <c r="D42" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="49"/>
-      <c r="F42" s="49"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="51"/>
-      <c r="B43" s="53"/>
-      <c r="C43" s="52"/>
+      <c r="A43" s="54"/>
+      <c r="B43" s="55"/>
+      <c r="C43" s="49"/>
       <c r="D43" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="51"/>
-      <c r="B44" s="53"/>
-      <c r="C44" s="52"/>
+      <c r="A44" s="54"/>
+      <c r="B44" s="55"/>
+      <c r="C44" s="49"/>
       <c r="D44" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E44" s="49"/>
-      <c r="F44" s="49"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="51"/>
-      <c r="B45" s="53"/>
-      <c r="C45" s="52"/>
+      <c r="A45" s="54"/>
+      <c r="B45" s="55"/>
+      <c r="C45" s="49"/>
       <c r="D45" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="51"/>
-      <c r="B46" s="53"/>
-      <c r="C46" s="52">
+      <c r="A46" s="54"/>
+      <c r="B46" s="55"/>
+      <c r="C46" s="49">
         <v>2.5</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="E46" s="50" t="s">
+      <c r="E46" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="49"/>
+      <c r="F46" s="52"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="51"/>
-      <c r="B47" s="53"/>
-      <c r="C47" s="52"/>
+      <c r="A47" s="54"/>
+      <c r="B47" s="55"/>
+      <c r="C47" s="49"/>
       <c r="D47" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E47" s="50"/>
-      <c r="F47" s="49"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="52"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="51"/>
-      <c r="B48" s="53"/>
-      <c r="C48" s="52"/>
+      <c r="A48" s="54"/>
+      <c r="B48" s="55"/>
+      <c r="C48" s="49"/>
       <c r="D48" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E48" s="50"/>
-      <c r="F48" s="49"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="52"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="51"/>
-      <c r="B49" s="53"/>
-      <c r="C49" s="52"/>
+      <c r="A49" s="54"/>
+      <c r="B49" s="55"/>
+      <c r="C49" s="49"/>
       <c r="D49" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E49" s="50"/>
-      <c r="F49" s="49"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="52"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="51"/>
-      <c r="B50" s="53"/>
-      <c r="C50" s="52">
+      <c r="A50" s="54"/>
+      <c r="B50" s="55"/>
+      <c r="C50" s="49">
         <v>2.7</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E50" s="49" t="s">
+      <c r="E50" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="F50" s="49"/>
+      <c r="F50" s="52"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="51"/>
-      <c r="B51" s="53"/>
-      <c r="C51" s="52"/>
+      <c r="A51" s="54"/>
+      <c r="B51" s="55"/>
+      <c r="C51" s="49"/>
       <c r="D51" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E51" s="49"/>
-      <c r="F51" s="49"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="51"/>
-      <c r="B52" s="53"/>
-      <c r="C52" s="52"/>
+      <c r="A52" s="54"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="49"/>
       <c r="D52" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E52" s="49"/>
-      <c r="F52" s="49"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="51"/>
-      <c r="B53" s="53"/>
-      <c r="C53" s="52"/>
+      <c r="A53" s="54"/>
+      <c r="B53" s="55"/>
+      <c r="C53" s="49"/>
       <c r="D53" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E53" s="49"/>
-      <c r="F53" s="49"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="52"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="51"/>
-      <c r="B54" s="53"/>
-      <c r="C54" s="52"/>
+      <c r="A54" s="54"/>
+      <c r="B54" s="55"/>
+      <c r="C54" s="49"/>
       <c r="D54" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E54" s="49"/>
-      <c r="F54" s="49"/>
+      <c r="E54" s="52"/>
+      <c r="F54" s="52"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="51"/>
-      <c r="B55" s="53"/>
-      <c r="C55" s="52"/>
+      <c r="A55" s="54"/>
+      <c r="B55" s="55"/>
+      <c r="C55" s="49"/>
       <c r="D55" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E55" s="49"/>
-      <c r="F55" s="49"/>
+      <c r="E55" s="52"/>
+      <c r="F55" s="52"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="51"/>
-      <c r="B56" s="53"/>
-      <c r="C56" s="52"/>
+      <c r="A56" s="54"/>
+      <c r="B56" s="55"/>
+      <c r="C56" s="49"/>
       <c r="D56" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="49"/>
-      <c r="F56" s="49"/>
+      <c r="E56" s="52"/>
+      <c r="F56" s="52"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="51"/>
-      <c r="B57" s="53"/>
-      <c r="C57" s="52"/>
+      <c r="A57" s="54"/>
+      <c r="B57" s="55"/>
+      <c r="C57" s="49"/>
       <c r="D57" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E57" s="49"/>
-      <c r="F57" s="49"/>
+      <c r="E57" s="52"/>
+      <c r="F57" s="52"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="51"/>
-      <c r="B58" s="53"/>
-      <c r="C58" s="52"/>
+      <c r="A58" s="54"/>
+      <c r="B58" s="55"/>
+      <c r="C58" s="49"/>
       <c r="D58" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E58" s="49"/>
-      <c r="F58" s="49"/>
+      <c r="E58" s="52"/>
+      <c r="F58" s="52"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
-      <c r="B59" s="52">
+      <c r="B59" s="49">
         <v>3</v>
       </c>
-      <c r="C59" s="52">
+      <c r="C59" s="49">
         <v>3.1</v>
       </c>
       <c r="D59" s="7" t="s">
@@ -5320,48 +6594,48 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="19"/>
-      <c r="B60" s="52"/>
-      <c r="C60" s="52"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="49"/>
       <c r="D60" s="7" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="19"/>
-      <c r="B61" s="52"/>
-      <c r="C61" s="52"/>
+      <c r="B61" s="49"/>
+      <c r="C61" s="49"/>
       <c r="D61" s="7" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="19"/>
-      <c r="B62" s="52"/>
-      <c r="C62" s="52"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="49"/>
       <c r="D62" s="7" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="19"/>
-      <c r="B63" s="52"/>
-      <c r="C63" s="52"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="49"/>
       <c r="D63" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="19"/>
-      <c r="B64" s="52"/>
-      <c r="C64" s="52"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="49"/>
       <c r="D64" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="19"/>
-      <c r="B65" s="52"/>
-      <c r="C65" s="52">
+      <c r="B65" s="49"/>
+      <c r="C65" s="49">
         <v>3.2</v>
       </c>
       <c r="D65" s="7" t="s">
@@ -5370,96 +6644,96 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="19"/>
-      <c r="B66" s="52"/>
-      <c r="C66" s="52"/>
+      <c r="B66" s="49"/>
+      <c r="C66" s="49"/>
       <c r="D66" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="19"/>
-      <c r="B67" s="52"/>
-      <c r="C67" s="52"/>
+      <c r="B67" s="49"/>
+      <c r="C67" s="49"/>
       <c r="D67" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="19"/>
-      <c r="B68" s="52"/>
-      <c r="C68" s="52"/>
+      <c r="B68" s="49"/>
+      <c r="C68" s="49"/>
       <c r="D68" s="7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="19"/>
-      <c r="B69" s="52"/>
-      <c r="C69" s="52"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="49"/>
       <c r="D69" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="19"/>
-      <c r="B70" s="52"/>
-      <c r="C70" s="52"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="49"/>
       <c r="D70" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="19"/>
-      <c r="B71" s="52"/>
-      <c r="C71" s="52"/>
+      <c r="B71" s="49"/>
+      <c r="C71" s="49"/>
       <c r="D71" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="19"/>
-      <c r="B72" s="52"/>
-      <c r="C72" s="52"/>
+      <c r="B72" s="49"/>
+      <c r="C72" s="49"/>
       <c r="D72" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="19"/>
-      <c r="B73" s="52"/>
-      <c r="C73" s="52"/>
+      <c r="B73" s="49"/>
+      <c r="C73" s="49"/>
       <c r="D73" s="7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="19"/>
-      <c r="B74" s="52"/>
-      <c r="C74" s="52"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="49"/>
       <c r="D74" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="19"/>
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="49"/>
       <c r="D75" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="19"/>
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
       <c r="D76" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="19"/>
-      <c r="B77" s="52"/>
-      <c r="C77" s="52">
+      <c r="B77" s="49"/>
+      <c r="C77" s="49">
         <v>3.3</v>
       </c>
       <c r="D77" s="7" t="s">
@@ -5468,88 +6742,88 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="19"/>
-      <c r="B78" s="52"/>
-      <c r="C78" s="52"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="49"/>
       <c r="D78" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="19"/>
-      <c r="B79" s="52"/>
-      <c r="C79" s="52"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
       <c r="D79" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="19"/>
-      <c r="B80" s="52"/>
-      <c r="C80" s="52"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
       <c r="D80" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="19"/>
-      <c r="B81" s="52"/>
-      <c r="C81" s="52"/>
+      <c r="B81" s="49"/>
+      <c r="C81" s="49"/>
       <c r="D81" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="19"/>
-      <c r="B82" s="52"/>
-      <c r="C82" s="52"/>
+      <c r="B82" s="49"/>
+      <c r="C82" s="49"/>
       <c r="D82" s="7" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="19"/>
-      <c r="B83" s="52"/>
-      <c r="C83" s="52"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="49"/>
       <c r="D83" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="19"/>
-      <c r="B84" s="52"/>
-      <c r="C84" s="52"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="49"/>
       <c r="D84" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="19"/>
-      <c r="B85" s="52"/>
-      <c r="C85" s="52"/>
+      <c r="B85" s="49"/>
+      <c r="C85" s="49"/>
       <c r="D85" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="19"/>
-      <c r="B86" s="52"/>
-      <c r="C86" s="52"/>
+      <c r="B86" s="49"/>
+      <c r="C86" s="49"/>
       <c r="D86" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="19"/>
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="49"/>
       <c r="D87" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="19"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="52">
+      <c r="B88" s="49"/>
+      <c r="C88" s="49">
         <v>3.4</v>
       </c>
       <c r="D88" s="15" t="s">
@@ -5558,104 +6832,104 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="19"/>
-      <c r="B89" s="52"/>
-      <c r="C89" s="52"/>
+      <c r="B89" s="49"/>
+      <c r="C89" s="49"/>
       <c r="D89" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="19"/>
-      <c r="B90" s="52"/>
-      <c r="C90" s="52"/>
+      <c r="B90" s="49"/>
+      <c r="C90" s="49"/>
       <c r="D90" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="19"/>
-      <c r="B91" s="52"/>
-      <c r="C91" s="52"/>
+      <c r="B91" s="49"/>
+      <c r="C91" s="49"/>
       <c r="D91" s="7" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="19"/>
-      <c r="B92" s="52"/>
-      <c r="C92" s="52"/>
+      <c r="B92" s="49"/>
+      <c r="C92" s="49"/>
       <c r="D92" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="19"/>
-      <c r="B93" s="52"/>
-      <c r="C93" s="52"/>
+      <c r="B93" s="49"/>
+      <c r="C93" s="49"/>
       <c r="D93" s="7" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="19"/>
-      <c r="B94" s="52"/>
-      <c r="C94" s="52"/>
+      <c r="B94" s="49"/>
+      <c r="C94" s="49"/>
       <c r="D94" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="19"/>
-      <c r="B95" s="52"/>
-      <c r="C95" s="52"/>
+      <c r="B95" s="49"/>
+      <c r="C95" s="49"/>
       <c r="D95" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="19"/>
-      <c r="B96" s="52"/>
-      <c r="C96" s="52"/>
+      <c r="B96" s="49"/>
+      <c r="C96" s="49"/>
       <c r="D96" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="19"/>
-      <c r="B97" s="52"/>
-      <c r="C97" s="52"/>
+      <c r="B97" s="49"/>
+      <c r="C97" s="49"/>
       <c r="D97" s="7" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="19"/>
-      <c r="B98" s="52"/>
-      <c r="C98" s="52"/>
+      <c r="B98" s="49"/>
+      <c r="C98" s="49"/>
       <c r="D98" s="7" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="19"/>
-      <c r="B99" s="52"/>
-      <c r="C99" s="52"/>
+      <c r="B99" s="49"/>
+      <c r="C99" s="49"/>
       <c r="D99" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="19"/>
-      <c r="B100" s="52"/>
-      <c r="C100" s="52"/>
+      <c r="B100" s="49"/>
+      <c r="C100" s="49"/>
       <c r="D100" s="7" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="19"/>
-      <c r="B101" s="52"/>
-      <c r="C101" s="52">
+      <c r="B101" s="49"/>
+      <c r="C101" s="49">
         <v>3.5</v>
       </c>
       <c r="D101" s="11" t="s">
@@ -5664,72 +6938,72 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="19"/>
-      <c r="B102" s="52"/>
-      <c r="C102" s="52"/>
+      <c r="B102" s="49"/>
+      <c r="C102" s="49"/>
       <c r="D102" s="7" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="19"/>
-      <c r="B103" s="52"/>
-      <c r="C103" s="52"/>
+      <c r="B103" s="49"/>
+      <c r="C103" s="49"/>
       <c r="D103" s="7" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="19"/>
-      <c r="B104" s="52"/>
-      <c r="C104" s="52"/>
+      <c r="B104" s="49"/>
+      <c r="C104" s="49"/>
       <c r="D104" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="19"/>
-      <c r="B105" s="52"/>
-      <c r="C105" s="52"/>
+      <c r="B105" s="49"/>
+      <c r="C105" s="49"/>
       <c r="D105" s="7" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="19"/>
-      <c r="B106" s="52"/>
-      <c r="C106" s="52"/>
+      <c r="B106" s="49"/>
+      <c r="C106" s="49"/>
       <c r="D106" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="19"/>
-      <c r="B107" s="52"/>
-      <c r="C107" s="52"/>
+      <c r="B107" s="49"/>
+      <c r="C107" s="49"/>
       <c r="D107" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="19"/>
-      <c r="B108" s="52"/>
-      <c r="C108" s="52"/>
+      <c r="B108" s="49"/>
+      <c r="C108" s="49"/>
       <c r="D108" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="19"/>
-      <c r="B109" s="52"/>
-      <c r="C109" s="52"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="49"/>
       <c r="D109" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="19"/>
-      <c r="B110" s="52"/>
-      <c r="C110" s="52">
+      <c r="B110" s="49"/>
+      <c r="C110" s="49">
         <v>3.6</v>
       </c>
       <c r="D110" s="7" t="s">
@@ -5738,48 +7012,48 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19"/>
-      <c r="B111" s="52"/>
-      <c r="C111" s="52"/>
+      <c r="B111" s="49"/>
+      <c r="C111" s="49"/>
       <c r="D111" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19"/>
-      <c r="B112" s="52"/>
-      <c r="C112" s="52"/>
+      <c r="B112" s="49"/>
+      <c r="C112" s="49"/>
       <c r="D112" s="7" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="19"/>
-      <c r="B113" s="52"/>
-      <c r="C113" s="52"/>
+      <c r="B113" s="49"/>
+      <c r="C113" s="49"/>
       <c r="D113" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="19"/>
-      <c r="B114" s="52"/>
-      <c r="C114" s="52"/>
+      <c r="B114" s="49"/>
+      <c r="C114" s="49"/>
       <c r="D114" s="7" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="19"/>
-      <c r="B115" s="52"/>
-      <c r="C115" s="52"/>
+      <c r="B115" s="49"/>
+      <c r="C115" s="49"/>
       <c r="D115" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="19"/>
-      <c r="B116" s="52"/>
-      <c r="C116" s="52">
+      <c r="B116" s="49"/>
+      <c r="C116" s="49">
         <v>3.7</v>
       </c>
       <c r="D116" s="7" t="s">
@@ -5788,88 +7062,88 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="19"/>
-      <c r="B117" s="52"/>
-      <c r="C117" s="52"/>
+      <c r="B117" s="49"/>
+      <c r="C117" s="49"/>
       <c r="D117" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="19"/>
-      <c r="B118" s="52"/>
-      <c r="C118" s="52"/>
+      <c r="B118" s="49"/>
+      <c r="C118" s="49"/>
       <c r="D118" s="7" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="19"/>
-      <c r="B119" s="52"/>
-      <c r="C119" s="52"/>
+      <c r="B119" s="49"/>
+      <c r="C119" s="49"/>
       <c r="D119" s="7" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="19"/>
-      <c r="B120" s="52"/>
-      <c r="C120" s="52"/>
+      <c r="B120" s="49"/>
+      <c r="C120" s="49"/>
       <c r="D120" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="19"/>
-      <c r="B121" s="52"/>
-      <c r="C121" s="52"/>
+      <c r="B121" s="49"/>
+      <c r="C121" s="49"/>
       <c r="D121" s="7" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="19"/>
-      <c r="B122" s="52"/>
-      <c r="C122" s="52"/>
+      <c r="B122" s="49"/>
+      <c r="C122" s="49"/>
       <c r="D122" s="7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="19"/>
-      <c r="B123" s="52"/>
-      <c r="C123" s="52"/>
+      <c r="B123" s="49"/>
+      <c r="C123" s="49"/>
       <c r="D123" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="19"/>
-      <c r="B124" s="52"/>
-      <c r="C124" s="52"/>
+      <c r="B124" s="49"/>
+      <c r="C124" s="49"/>
       <c r="D124" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="19"/>
-      <c r="B125" s="52"/>
-      <c r="C125" s="52"/>
+      <c r="B125" s="49"/>
+      <c r="C125" s="49"/>
       <c r="D125" s="7" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="19"/>
-      <c r="B126" s="52"/>
-      <c r="C126" s="52"/>
+      <c r="B126" s="49"/>
+      <c r="C126" s="49"/>
       <c r="D126" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="19"/>
-      <c r="B127" s="52"/>
-      <c r="C127" s="52">
+      <c r="B127" s="49"/>
+      <c r="C127" s="49">
         <v>3.8</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -5878,80 +7152,80 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="19"/>
-      <c r="B128" s="52"/>
-      <c r="C128" s="52"/>
+      <c r="B128" s="49"/>
+      <c r="C128" s="49"/>
       <c r="D128" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="19"/>
-      <c r="B129" s="52"/>
-      <c r="C129" s="52"/>
+      <c r="B129" s="49"/>
+      <c r="C129" s="49"/>
       <c r="D129" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="19"/>
-      <c r="B130" s="52"/>
-      <c r="C130" s="52"/>
+      <c r="B130" s="49"/>
+      <c r="C130" s="49"/>
       <c r="D130" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="19"/>
-      <c r="B131" s="52"/>
-      <c r="C131" s="52"/>
+      <c r="B131" s="49"/>
+      <c r="C131" s="49"/>
       <c r="D131" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="19"/>
-      <c r="B132" s="52"/>
-      <c r="C132" s="52"/>
+      <c r="B132" s="49"/>
+      <c r="C132" s="49"/>
       <c r="D132" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="19"/>
-      <c r="B133" s="52"/>
-      <c r="C133" s="52"/>
+      <c r="B133" s="49"/>
+      <c r="C133" s="49"/>
       <c r="D133" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="19"/>
-      <c r="B134" s="52"/>
-      <c r="C134" s="52"/>
+      <c r="B134" s="49"/>
+      <c r="C134" s="49"/>
       <c r="D134" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="19"/>
-      <c r="B135" s="52"/>
-      <c r="C135" s="52"/>
+      <c r="B135" s="49"/>
+      <c r="C135" s="49"/>
       <c r="D135" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="19"/>
-      <c r="B136" s="52"/>
-      <c r="C136" s="52"/>
+      <c r="B136" s="49"/>
+      <c r="C136" s="49"/>
       <c r="D136" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="19"/>
-      <c r="B137" s="52"/>
-      <c r="C137" s="52">
+      <c r="B137" s="49"/>
+      <c r="C137" s="49">
         <v>3.9</v>
       </c>
       <c r="D137" s="7" t="s">
@@ -5960,40 +7234,40 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="19"/>
-      <c r="B138" s="52"/>
-      <c r="C138" s="52"/>
+      <c r="B138" s="49"/>
+      <c r="C138" s="49"/>
       <c r="D138" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="19"/>
-      <c r="B139" s="52"/>
-      <c r="C139" s="52"/>
+      <c r="B139" s="49"/>
+      <c r="C139" s="49"/>
       <c r="D139" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="19"/>
-      <c r="B140" s="52"/>
-      <c r="C140" s="52"/>
+      <c r="B140" s="49"/>
+      <c r="C140" s="49"/>
       <c r="D140" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="19"/>
-      <c r="B141" s="52"/>
-      <c r="C141" s="52"/>
+      <c r="B141" s="49"/>
+      <c r="C141" s="49"/>
       <c r="D141" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
-      <c r="B142" s="52"/>
-      <c r="C142" s="55">
+      <c r="B142" s="49"/>
+      <c r="C142" s="50">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -6002,122 +7276,122 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
-      <c r="B143" s="52"/>
-      <c r="C143" s="55"/>
+      <c r="B143" s="49"/>
+      <c r="C143" s="50"/>
       <c r="D143" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
-      <c r="B144" s="52"/>
-      <c r="C144" s="55"/>
+      <c r="B144" s="49"/>
+      <c r="C144" s="50"/>
       <c r="D144" s="7" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
-      <c r="B145" s="52"/>
-      <c r="C145" s="55"/>
+      <c r="B145" s="49"/>
+      <c r="C145" s="50"/>
       <c r="D145" s="7" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
-      <c r="B146" s="52"/>
-      <c r="C146" s="55"/>
+      <c r="B146" s="49"/>
+      <c r="C146" s="50"/>
       <c r="D146" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
-      <c r="B147" s="52"/>
-      <c r="C147" s="55"/>
+      <c r="B147" s="49"/>
+      <c r="C147" s="50"/>
       <c r="D147" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
-      <c r="B148" s="52"/>
-      <c r="C148" s="55"/>
+      <c r="B148" s="49"/>
+      <c r="C148" s="50"/>
       <c r="D148" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
-      <c r="B149" s="52"/>
-      <c r="C149" s="55"/>
+      <c r="B149" s="49"/>
+      <c r="C149" s="50"/>
       <c r="D149" s="7" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
-      <c r="B150" s="52"/>
-      <c r="C150" s="55"/>
+      <c r="B150" s="49"/>
+      <c r="C150" s="50"/>
       <c r="D150" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
-      <c r="B151" s="52"/>
-      <c r="C151" s="55"/>
+      <c r="B151" s="49"/>
+      <c r="C151" s="50"/>
       <c r="D151" s="7" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
-      <c r="B152" s="52"/>
-      <c r="C152" s="55"/>
+      <c r="B152" s="49"/>
+      <c r="C152" s="50"/>
       <c r="D152" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
-      <c r="B153" s="52"/>
-      <c r="C153" s="55"/>
+      <c r="B153" s="49"/>
+      <c r="C153" s="50"/>
       <c r="D153" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
-      <c r="B154" s="52"/>
-      <c r="C154" s="55"/>
+      <c r="B154" s="49"/>
+      <c r="C154" s="50"/>
       <c r="D154" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
-      <c r="B155" s="52"/>
-      <c r="C155" s="55"/>
+      <c r="B155" s="49"/>
+      <c r="C155" s="50"/>
       <c r="D155" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
-      <c r="B156" s="52"/>
-      <c r="C156" s="55"/>
+      <c r="B156" s="49"/>
+      <c r="C156" s="50"/>
       <c r="D156" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="20"/>
-      <c r="B157" s="52">
+      <c r="B157" s="49">
         <v>4</v>
       </c>
-      <c r="C157" s="52">
+      <c r="C157" s="49">
         <v>4.0999999999999996</v>
       </c>
       <c r="D157" s="7" t="s">
@@ -6126,32 +7400,32 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="19"/>
-      <c r="B158" s="52"/>
-      <c r="C158" s="52"/>
+      <c r="B158" s="49"/>
+      <c r="C158" s="49"/>
       <c r="D158" s="7" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="19"/>
-      <c r="B159" s="52"/>
-      <c r="C159" s="52"/>
+      <c r="B159" s="49"/>
+      <c r="C159" s="49"/>
       <c r="D159" s="7" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="19"/>
-      <c r="B160" s="52"/>
-      <c r="C160" s="52"/>
+      <c r="B160" s="49"/>
+      <c r="C160" s="49"/>
       <c r="D160" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="19"/>
-      <c r="B161" s="52"/>
-      <c r="C161" s="52">
+      <c r="B161" s="49"/>
+      <c r="C161" s="49">
         <v>4.2</v>
       </c>
       <c r="D161" s="7" t="s">
@@ -6160,56 +7434,56 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="19"/>
-      <c r="B162" s="52"/>
-      <c r="C162" s="52"/>
+      <c r="B162" s="49"/>
+      <c r="C162" s="49"/>
       <c r="D162" s="7" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="19"/>
-      <c r="B163" s="52"/>
-      <c r="C163" s="52"/>
+      <c r="B163" s="49"/>
+      <c r="C163" s="49"/>
       <c r="D163" s="7" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="19"/>
-      <c r="B164" s="52"/>
-      <c r="C164" s="52"/>
+      <c r="B164" s="49"/>
+      <c r="C164" s="49"/>
       <c r="D164" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="19"/>
-      <c r="B165" s="52"/>
-      <c r="C165" s="52"/>
+      <c r="B165" s="49"/>
+      <c r="C165" s="49"/>
       <c r="D165" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="19"/>
-      <c r="B166" s="52"/>
-      <c r="C166" s="52"/>
+      <c r="B166" s="49"/>
+      <c r="C166" s="49"/>
       <c r="D166" s="7" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="19"/>
-      <c r="B167" s="52"/>
-      <c r="C167" s="52"/>
+      <c r="B167" s="49"/>
+      <c r="C167" s="49"/>
       <c r="D167" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="19"/>
-      <c r="B168" s="52"/>
-      <c r="C168" s="52">
+      <c r="B168" s="49"/>
+      <c r="C168" s="49">
         <v>4.3</v>
       </c>
       <c r="D168" s="7" t="s">
@@ -6218,48 +7492,48 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="19"/>
-      <c r="B169" s="52"/>
-      <c r="C169" s="52"/>
+      <c r="B169" s="49"/>
+      <c r="C169" s="49"/>
       <c r="D169" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="19"/>
-      <c r="B170" s="52"/>
-      <c r="C170" s="52"/>
+      <c r="B170" s="49"/>
+      <c r="C170" s="49"/>
       <c r="D170" s="7" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="19"/>
-      <c r="B171" s="52"/>
-      <c r="C171" s="52"/>
+      <c r="B171" s="49"/>
+      <c r="C171" s="49"/>
       <c r="D171" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="19"/>
-      <c r="B172" s="52"/>
-      <c r="C172" s="52"/>
+      <c r="B172" s="49"/>
+      <c r="C172" s="49"/>
       <c r="D172" s="7" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="19"/>
-      <c r="B173" s="52"/>
-      <c r="C173" s="52"/>
+      <c r="B173" s="49"/>
+      <c r="C173" s="49"/>
       <c r="D173" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="19"/>
-      <c r="B174" s="52"/>
-      <c r="C174" s="52">
+      <c r="B174" s="49"/>
+      <c r="C174" s="49">
         <v>4.4000000000000004</v>
       </c>
       <c r="D174" s="7" t="s">
@@ -6268,56 +7542,56 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="19"/>
-      <c r="B175" s="52"/>
-      <c r="C175" s="52"/>
+      <c r="B175" s="49"/>
+      <c r="C175" s="49"/>
       <c r="D175" s="7" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="19"/>
-      <c r="B176" s="52"/>
-      <c r="C176" s="52"/>
+      <c r="B176" s="49"/>
+      <c r="C176" s="49"/>
       <c r="D176" s="7" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="19"/>
-      <c r="B177" s="52"/>
-      <c r="C177" s="52"/>
+      <c r="B177" s="49"/>
+      <c r="C177" s="49"/>
       <c r="D177" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="19"/>
-      <c r="B178" s="52"/>
-      <c r="C178" s="52"/>
+      <c r="B178" s="49"/>
+      <c r="C178" s="49"/>
       <c r="D178" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="19"/>
-      <c r="B179" s="52"/>
-      <c r="C179" s="52"/>
+      <c r="B179" s="49"/>
+      <c r="C179" s="49"/>
       <c r="D179" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="19"/>
-      <c r="B180" s="52"/>
-      <c r="C180" s="52"/>
+      <c r="B180" s="49"/>
+      <c r="C180" s="49"/>
       <c r="D180" s="7" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="19"/>
-      <c r="B181" s="52"/>
-      <c r="C181" s="52"/>
+      <c r="B181" s="49"/>
+      <c r="C181" s="49"/>
       <c r="D181" s="7" t="s">
         <v>57</v>
       </c>
@@ -6325,6 +7599,41 @@
   </sheetData>
   <autoFilter ref="A2:J181" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="51">
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -6341,41 +7650,6 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6385,7 +7659,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="15" customWidth="1"/>
@@ -6845,73 +8119,70 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="C21" s="15">
+      <c r="A21" s="33"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29">
+        <v>50</v>
+      </c>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="31"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="C22" s="15">
         <v>2.14</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E22" t="s">
         <v>18</v>
-      </c>
-      <c r="F21" cm="1">
-        <f t="array" ref="F21">_xlfn.SWITCH(E21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="G21" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="86.4">
-      <c r="A22" s="15">
-        <v>2</v>
-      </c>
-      <c r="B22" s="47">
-        <v>3</v>
-      </c>
-      <c r="C22" s="15">
-        <v>3.1</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E22" t="s">
-        <v>19</v>
       </c>
       <c r="F22" cm="1">
         <f t="array" ref="F22">_xlfn.SWITCH(E22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G22" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="86.4">
+      <c r="A23" s="15">
+        <v>2</v>
+      </c>
+      <c r="B23" s="47">
         <v>3</v>
       </c>
-      <c r="G22" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="86.4">
-      <c r="B23" s="45"/>
       <c r="C23" s="15">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F23" cm="1">
         <f t="array" ref="F23">_xlfn.SWITCH(E23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="86.4">
       <c r="B24" s="45"/>
       <c r="C24" s="15">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E24" t="s">
         <v>18</v>
@@ -6921,16 +8192,16 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="158.4">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="86.4">
       <c r="B25" s="45"/>
       <c r="C25" s="15">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="E25" t="s">
         <v>18</v>
@@ -6940,16 +8211,16 @@
         <v>2</v>
       </c>
       <c r="G25" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="72">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="158.4">
       <c r="B26" s="45"/>
       <c r="C26" s="15">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>272</v>
+        <v>234</v>
       </c>
       <c r="E26" t="s">
         <v>18</v>
@@ -6962,51 +8233,51 @@
         <v>240</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="115.2">
+    <row r="27" spans="1:10" ht="72">
       <c r="B27" s="45"/>
       <c r="C27" s="15">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F27" cm="1">
         <f t="array" ref="F27">_xlfn.SWITCH(E27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="115.2">
       <c r="B28" s="45"/>
       <c r="C28" s="15">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F28" cm="1">
         <f t="array" ref="F28">_xlfn.SWITCH(E28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="86.4">
+    <row r="29" spans="1:10">
       <c r="B29" s="45"/>
       <c r="C29" s="15">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
@@ -7019,13 +8290,13 @@
         <v>243</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="144">
+    <row r="30" spans="1:10" ht="86.4">
       <c r="B30" s="45"/>
       <c r="C30" s="15">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="E30" t="s">
         <v>17</v>
@@ -7035,158 +8306,177 @@
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="144">
       <c r="B31" s="45"/>
-      <c r="C31" s="35">
-        <v>3.1</v>
+      <c r="C31" s="15">
+        <v>3.9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>236</v>
+        <v>274</v>
       </c>
       <c r="E31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F31" cm="1">
         <f t="array" ref="F31">_xlfn.SWITCH(E31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="72">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="144">
       <c r="B32" s="45"/>
-      <c r="C32" s="15">
-        <v>3.11</v>
+      <c r="C32" s="35">
+        <v>3.1</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F32" cm="1">
         <f t="array" ref="F32">_xlfn.SWITCH(E32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" ht="216">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="72">
       <c r="B33" s="45"/>
-      <c r="C33" s="35">
-        <v>3.12</v>
+      <c r="C33" s="15">
+        <v>3.11</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F33" cm="1">
         <f t="array" ref="F33">_xlfn.SWITCH(E33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G33" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" ht="57.6">
-      <c r="B34" s="45">
-        <v>4</v>
-      </c>
-      <c r="C34" s="15">
-        <v>4.0999999999999996</v>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="216">
+      <c r="B34" s="45"/>
+      <c r="C34" s="35">
+        <v>3.12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E34" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F34" cm="1">
         <f t="array" ref="F34">_xlfn.SWITCH(E34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G34" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" ht="86.4">
-      <c r="B35" s="45"/>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="57.6">
+      <c r="B35" s="45">
+        <v>4</v>
+      </c>
       <c r="C35" s="15">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F35" cm="1">
         <f t="array" ref="F35">_xlfn.SWITCH(E35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" ht="72">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="86.4">
       <c r="B36" s="45"/>
       <c r="C36" s="15">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F36" cm="1">
         <f t="array" ref="F36">_xlfn.SWITCH(E36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" ht="115.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="72">
       <c r="B37" s="45"/>
       <c r="C37" s="15">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>239</v>
+        <v>278</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F37" cm="1">
         <f t="array" ref="F37">_xlfn.SWITCH(E37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G37" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="115.2">
+      <c r="B38" s="45"/>
+      <c r="C38" s="15">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E38" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" cm="1">
+        <f t="array" ref="F38">_xlfn.SWITCH(E38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G38" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="38" spans="2:7">
-      <c r="F38">
-        <f>SUM(F16:F37)</f>
-        <v>61</v>
+    <row r="39" spans="2:7">
+      <c r="F39">
+        <f>SUM(F16:F38)</f>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B35:B38"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="B7:B13"/>
-    <mergeCell ref="B22:B33"/>
+    <mergeCell ref="B23:B34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7403,6 +8693,401 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0EF2629-DF98-442F-A4DA-55187BF5098E}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="4.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="10.6640625" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="43.2">
+      <c r="A1" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" s="26">
+        <v>46286</v>
+      </c>
+      <c r="C2" s="58">
+        <v>50</v>
+      </c>
+      <c r="D2" s="27">
+        <f>('Updated Sprint'!F21)*(1-(A2-1)/18)</f>
+        <v>50</v>
+      </c>
+      <c r="E2" s="28">
+        <v>3</v>
+      </c>
+      <c r="F2" s="21"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="B3" s="26">
+        <v>46287</v>
+      </c>
+      <c r="C3" s="27">
+        <f>50-SUM($E$2:E3)</f>
+        <v>47</v>
+      </c>
+      <c r="D3" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A3-1)/18)</f>
+        <v>47.222222222222221</v>
+      </c>
+      <c r="E3" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4" s="26">
+        <v>46288</v>
+      </c>
+      <c r="C4" s="27">
+        <f>50-SUM($E$2:E4)</f>
+        <v>43</v>
+      </c>
+      <c r="D4" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A4-1)/18)</f>
+        <v>44.444444444444443</v>
+      </c>
+      <c r="E4" s="28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" s="26">
+        <v>46289</v>
+      </c>
+      <c r="C5" s="27">
+        <f>50-SUM($E$2:E5)</f>
+        <v>41</v>
+      </c>
+      <c r="D5" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A5-1)/18)</f>
+        <v>41.666666666666671</v>
+      </c>
+      <c r="E5" s="28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="B6" s="26">
+        <v>46290</v>
+      </c>
+      <c r="C6" s="27">
+        <f>50-SUM($E$2:E6)</f>
+        <v>36</v>
+      </c>
+      <c r="D6" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A6-1)/18)</f>
+        <v>38.888888888888893</v>
+      </c>
+      <c r="E6" s="28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" s="26">
+        <v>46291</v>
+      </c>
+      <c r="C7" s="27">
+        <f>50-SUM($E$2:E7)</f>
+        <v>36</v>
+      </c>
+      <c r="D7" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A7-1)/18)</f>
+        <v>36.111111111111107</v>
+      </c>
+      <c r="E7" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" s="26">
+        <v>46292</v>
+      </c>
+      <c r="C8" s="27">
+        <f>50-SUM($E$2:E8)</f>
+        <v>36</v>
+      </c>
+      <c r="D8" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A8-1)/18)</f>
+        <v>33.333333333333336</v>
+      </c>
+      <c r="E8" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" s="26">
+        <v>46293</v>
+      </c>
+      <c r="C9" s="27">
+        <f>50-SUM($E$2:E9)</f>
+        <v>32</v>
+      </c>
+      <c r="D9" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A9-1)/18)</f>
+        <v>30.555555555555557</v>
+      </c>
+      <c r="E9" s="28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="B10" s="26">
+        <v>46294</v>
+      </c>
+      <c r="C10" s="27">
+        <f>50-SUM($E$2:E10)</f>
+        <v>28</v>
+      </c>
+      <c r="D10" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A10-1)/18)</f>
+        <v>27.777777777777779</v>
+      </c>
+      <c r="E10" s="28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" s="26">
+        <v>46295</v>
+      </c>
+      <c r="C11" s="27">
+        <f>50-SUM($E$2:E11)</f>
+        <v>28</v>
+      </c>
+      <c r="D11" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A11-1)/18)</f>
+        <v>25</v>
+      </c>
+      <c r="E11" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="B12" s="26">
+        <v>46296</v>
+      </c>
+      <c r="C12" s="27">
+        <f>50-SUM($E$2:E12)</f>
+        <v>26</v>
+      </c>
+      <c r="D12" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A12-1)/18)</f>
+        <v>22.222222222222221</v>
+      </c>
+      <c r="E12" s="28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="B13" s="26">
+        <v>46297</v>
+      </c>
+      <c r="C13" s="27">
+        <f>50-SUM($E$2:E13)</f>
+        <v>21</v>
+      </c>
+      <c r="D13" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A13-1)/18)</f>
+        <v>19.444444444444443</v>
+      </c>
+      <c r="E13" s="28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="B14" s="26">
+        <v>46298</v>
+      </c>
+      <c r="C14" s="27">
+        <f>50-SUM($E$2:E14)</f>
+        <v>21</v>
+      </c>
+      <c r="D14" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A14-1)/18)</f>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="E14" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="B15" s="26">
+        <v>46299</v>
+      </c>
+      <c r="C15" s="27">
+        <f>50-SUM($E$2:E15)</f>
+        <v>21</v>
+      </c>
+      <c r="D15" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A15-1)/18)</f>
+        <v>13.888888888888889</v>
+      </c>
+      <c r="E15" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="25" t="s">
+        <v>285</v>
+      </c>
+      <c r="B16" s="26">
+        <v>46300</v>
+      </c>
+      <c r="C16" s="27">
+        <f>50-SUM($E$2:E16)</f>
+        <v>17</v>
+      </c>
+      <c r="D16" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A16-1)/18)</f>
+        <v>11.111111111111111</v>
+      </c>
+      <c r="E16" s="28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="B17" s="26">
+        <v>46301</v>
+      </c>
+      <c r="C17" s="27">
+        <f>50-SUM($E$2:E17)</f>
+        <v>15</v>
+      </c>
+      <c r="D17" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A17-1)/18)</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="E17" s="28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="B18" s="26">
+        <v>46302</v>
+      </c>
+      <c r="C18" s="27">
+        <f>50-SUM($E$2:E18)</f>
+        <v>12</v>
+      </c>
+      <c r="D18" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A18-1)/18)</f>
+        <v>5.555555555555558</v>
+      </c>
+      <c r="E18" s="28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="B19" s="26">
+        <v>46303</v>
+      </c>
+      <c r="C19" s="27">
+        <f>50-SUM($E$2:E19)</f>
+        <v>7</v>
+      </c>
+      <c r="D19" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A19-1)/18)</f>
+        <v>2.777777777777779</v>
+      </c>
+      <c r="E19" s="28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="B20" s="26">
+        <v>46304</v>
+      </c>
+      <c r="C20" s="27">
+        <f>50-SUM($E$2:E20)</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="57">
+        <f>('Updated Sprint'!F21)*(1-(A20-1)/18)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="28">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6ED44A-1EAB-4888-B5B3-205B280BC7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7ABFE51-C519-43E7-AAC4-EA6863C247FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="4" r:id="rId1"/>
@@ -754,7 +754,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -776,7 +776,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="291">
   <si>
     <t>Work Item</t>
   </si>
@@ -2661,9 +2661,6 @@
 Return appropriate frontend error response</t>
   </si>
   <si>
-    <t>Vidit, Azad</t>
-  </si>
-  <si>
     <t>Receive formulation ID from backend
 Retrieve saved formulation
 Verify formulation belongs to the logged-in customer+session
@@ -2679,9 +2676,6 @@
 Prevent duplicate submissions</t>
   </si>
   <si>
-    <t>Vidit,Azad</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -2710,6 +2704,17 @@
   </si>
   <si>
     <t>19</t>
+  </si>
+  <si>
+    <t>DB Visualiazation Dashboard</t>
+  </si>
+  <si>
+    <t>Backend Deployment (render)
+Configure shopify app proxy</t>
+  </si>
+  <si>
+    <t>DB Deployment (supabase)
+Configure buckets for Image storage</t>
   </si>
 </sst>
 </file>
@@ -3012,26 +3017,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3040,16 +3033,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3139,7 +3144,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-IN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5770,11 +5775,11 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="10"/>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
     </row>
@@ -5914,18 +5919,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1">
       <c r="A2" s="10" t="s">
@@ -5960,632 +5965,632 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="54">
+      <c r="A3" s="50">
         <v>1</v>
       </c>
-      <c r="B3" s="49">
+      <c r="B3" s="51">
         <v>1</v>
       </c>
-      <c r="C3" s="49">
+      <c r="C3" s="51">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="52" cm="1">
+      <c r="F3" s="48" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="54"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
+      <c r="A4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
       <c r="D4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="54"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
+      <c r="A5" s="50"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="54"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
+      <c r="A6" s="50"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="54"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
+      <c r="A7" s="50"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
       <c r="D7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="54"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
+      <c r="A8" s="50"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
       <c r="D8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="54"/>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
+      <c r="A9" s="50"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
       <c r="D9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="54"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
+      <c r="A10" s="50"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
       <c r="D10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="54"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
+      <c r="A11" s="50"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
       <c r="D11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="54"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49">
+      <c r="A12" s="50"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51">
         <v>1.2</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="52" cm="1">
+      <c r="F12" s="48" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="54"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
+      <c r="A13" s="50"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="54"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
+      <c r="A14" s="50"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
       <c r="D14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="54"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="49">
+      <c r="A15" s="50"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51">
         <v>1.3</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="52" t="s">
+      <c r="E15" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="52"/>
+      <c r="F15" s="48"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="54"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
+      <c r="A16" s="50"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="54"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
+      <c r="A17" s="50"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
       <c r="D17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="52"/>
-      <c r="F17" s="52"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="54"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49">
+      <c r="A18" s="50"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51">
         <v>1.4</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="52" t="s">
+      <c r="E18" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="52"/>
+      <c r="F18" s="48"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="54"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
+      <c r="A19" s="50"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
       <c r="D19" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="54"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
+      <c r="A20" s="50"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
       <c r="D20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="54"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
+      <c r="A21" s="50"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
       <c r="D21" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="54"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
+      <c r="A22" s="50"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
       <c r="D22" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="54"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
+      <c r="A23" s="50"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
       <c r="D23" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="54"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49"/>
+      <c r="A24" s="50"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="51"/>
       <c r="D24" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="54"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
+      <c r="A25" s="50"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
       <c r="D25" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="52"/>
-      <c r="F25" s="52"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="54"/>
-      <c r="B26" s="55">
+      <c r="A26" s="50"/>
+      <c r="B26" s="52">
         <v>2</v>
       </c>
-      <c r="C26" s="49">
+      <c r="C26" s="51">
         <v>2.1</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E26" s="53" t="s">
+      <c r="E26" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="52"/>
+      <c r="F26" s="48"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="54"/>
-      <c r="B27" s="55"/>
-      <c r="C27" s="49"/>
+      <c r="A27" s="50"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="51"/>
       <c r="D27" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="53"/>
-      <c r="F27" s="52"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="48"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="54"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="49"/>
+      <c r="A28" s="50"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="51"/>
       <c r="D28" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E28" s="53"/>
-      <c r="F28" s="52"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="48"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="54"/>
-      <c r="B29" s="55"/>
-      <c r="C29" s="51">
+      <c r="A29" s="50"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="54">
         <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="52" t="s">
+      <c r="E29" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="52"/>
+      <c r="F29" s="48"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="54"/>
-      <c r="B30" s="55"/>
-      <c r="C30" s="51"/>
+      <c r="A30" s="50"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="54"/>
       <c r="D30" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="54"/>
-      <c r="B31" s="55"/>
-      <c r="C31" s="49">
+      <c r="A31" s="50"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="51">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="52" t="s">
+      <c r="E31" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52" t="s">
+      <c r="F31" s="48"/>
+      <c r="G31" s="48" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="54"/>
-      <c r="B32" s="55"/>
-      <c r="C32" s="49"/>
+      <c r="A32" s="50"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="51"/>
       <c r="D32" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="54"/>
-      <c r="B33" s="55"/>
-      <c r="C33" s="49"/>
+      <c r="A33" s="50"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="51"/>
       <c r="D33" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="54"/>
-      <c r="B34" s="55"/>
-      <c r="C34" s="49"/>
+      <c r="A34" s="50"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="51"/>
       <c r="D34" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="54"/>
-      <c r="B35" s="55"/>
-      <c r="C35" s="49"/>
+      <c r="A35" s="50"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="51"/>
       <c r="D35" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="54"/>
-      <c r="B36" s="55"/>
-      <c r="C36" s="49"/>
+      <c r="A36" s="50"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="51"/>
       <c r="D36" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="54"/>
-      <c r="B37" s="55"/>
-      <c r="C37" s="49"/>
+      <c r="A37" s="50"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="51"/>
       <c r="D37" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="54"/>
-      <c r="B38" s="55"/>
-      <c r="C38" s="49">
+      <c r="A38" s="50"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="51">
         <v>2.4</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E38" s="52" t="s">
+      <c r="E38" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="52"/>
+      <c r="F38" s="48"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="54"/>
-      <c r="B39" s="55"/>
-      <c r="C39" s="49"/>
+      <c r="A39" s="50"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="51"/>
       <c r="D39" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="54"/>
-      <c r="B40" s="55"/>
-      <c r="C40" s="49"/>
+      <c r="A40" s="50"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="51"/>
       <c r="D40" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="54"/>
-      <c r="B41" s="55"/>
-      <c r="C41" s="49"/>
+      <c r="A41" s="50"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="51"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="54"/>
-      <c r="B42" s="55"/>
-      <c r="C42" s="49"/>
+      <c r="A42" s="50"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="51"/>
       <c r="D42" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="54"/>
-      <c r="B43" s="55"/>
-      <c r="C43" s="49"/>
+      <c r="A43" s="50"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="51"/>
       <c r="D43" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="54"/>
-      <c r="B44" s="55"/>
-      <c r="C44" s="49"/>
+      <c r="A44" s="50"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="51"/>
       <c r="D44" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="54"/>
-      <c r="B45" s="55"/>
-      <c r="C45" s="49"/>
+      <c r="A45" s="50"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="51"/>
       <c r="D45" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="48"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="54"/>
-      <c r="B46" s="55"/>
-      <c r="C46" s="49">
+      <c r="A46" s="50"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="51">
         <v>2.5</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="E46" s="53" t="s">
+      <c r="E46" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="52"/>
+      <c r="F46" s="48"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="54"/>
-      <c r="B47" s="55"/>
-      <c r="C47" s="49"/>
+      <c r="A47" s="50"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="51"/>
       <c r="D47" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E47" s="53"/>
-      <c r="F47" s="52"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="48"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="54"/>
-      <c r="B48" s="55"/>
-      <c r="C48" s="49"/>
+      <c r="A48" s="50"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="51"/>
       <c r="D48" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E48" s="53"/>
-      <c r="F48" s="52"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="48"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="54"/>
-      <c r="B49" s="55"/>
-      <c r="C49" s="49"/>
+      <c r="A49" s="50"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="51"/>
       <c r="D49" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E49" s="53"/>
-      <c r="F49" s="52"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="48"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="54"/>
-      <c r="B50" s="55"/>
-      <c r="C50" s="49">
+      <c r="A50" s="50"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="51">
         <v>2.7</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E50" s="52" t="s">
+      <c r="E50" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F50" s="52"/>
+      <c r="F50" s="48"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="54"/>
-      <c r="B51" s="55"/>
-      <c r="C51" s="49"/>
+      <c r="A51" s="50"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="51"/>
       <c r="D51" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E51" s="52"/>
-      <c r="F51" s="52"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="54"/>
-      <c r="B52" s="55"/>
-      <c r="C52" s="49"/>
+      <c r="A52" s="50"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="51"/>
       <c r="D52" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
+      <c r="E52" s="48"/>
+      <c r="F52" s="48"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="54"/>
-      <c r="B53" s="55"/>
-      <c r="C53" s="49"/>
+      <c r="A53" s="50"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="51"/>
       <c r="D53" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E53" s="52"/>
-      <c r="F53" s="52"/>
+      <c r="E53" s="48"/>
+      <c r="F53" s="48"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="54"/>
-      <c r="B54" s="55"/>
-      <c r="C54" s="49"/>
+      <c r="A54" s="50"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="51"/>
       <c r="D54" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E54" s="52"/>
-      <c r="F54" s="52"/>
+      <c r="E54" s="48"/>
+      <c r="F54" s="48"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="54"/>
-      <c r="B55" s="55"/>
-      <c r="C55" s="49"/>
+      <c r="A55" s="50"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="51"/>
       <c r="D55" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E55" s="52"/>
-      <c r="F55" s="52"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="54"/>
-      <c r="B56" s="55"/>
-      <c r="C56" s="49"/>
+      <c r="A56" s="50"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="51"/>
       <c r="D56" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="52"/>
-      <c r="F56" s="52"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="54"/>
-      <c r="B57" s="55"/>
-      <c r="C57" s="49"/>
+      <c r="A57" s="50"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="51"/>
       <c r="D57" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E57" s="52"/>
-      <c r="F57" s="52"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="48"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="54"/>
-      <c r="B58" s="55"/>
-      <c r="C58" s="49"/>
+      <c r="A58" s="50"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="51"/>
       <c r="D58" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E58" s="52"/>
-      <c r="F58" s="52"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="48"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
-      <c r="B59" s="49">
+      <c r="B59" s="51">
         <v>3</v>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="51">
         <v>3.1</v>
       </c>
       <c r="D59" s="7" t="s">
@@ -6594,48 +6599,48 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="19"/>
-      <c r="B60" s="49"/>
-      <c r="C60" s="49"/>
+      <c r="B60" s="51"/>
+      <c r="C60" s="51"/>
       <c r="D60" s="7" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="19"/>
-      <c r="B61" s="49"/>
-      <c r="C61" s="49"/>
+      <c r="B61" s="51"/>
+      <c r="C61" s="51"/>
       <c r="D61" s="7" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="19"/>
-      <c r="B62" s="49"/>
-      <c r="C62" s="49"/>
+      <c r="B62" s="51"/>
+      <c r="C62" s="51"/>
       <c r="D62" s="7" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="19"/>
-      <c r="B63" s="49"/>
-      <c r="C63" s="49"/>
+      <c r="B63" s="51"/>
+      <c r="C63" s="51"/>
       <c r="D63" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="19"/>
-      <c r="B64" s="49"/>
-      <c r="C64" s="49"/>
+      <c r="B64" s="51"/>
+      <c r="C64" s="51"/>
       <c r="D64" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="19"/>
-      <c r="B65" s="49"/>
-      <c r="C65" s="49">
+      <c r="B65" s="51"/>
+      <c r="C65" s="51">
         <v>3.2</v>
       </c>
       <c r="D65" s="7" t="s">
@@ -6644,96 +6649,96 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="19"/>
-      <c r="B66" s="49"/>
-      <c r="C66" s="49"/>
+      <c r="B66" s="51"/>
+      <c r="C66" s="51"/>
       <c r="D66" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="19"/>
-      <c r="B67" s="49"/>
-      <c r="C67" s="49"/>
+      <c r="B67" s="51"/>
+      <c r="C67" s="51"/>
       <c r="D67" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="19"/>
-      <c r="B68" s="49"/>
-      <c r="C68" s="49"/>
+      <c r="B68" s="51"/>
+      <c r="C68" s="51"/>
       <c r="D68" s="7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="19"/>
-      <c r="B69" s="49"/>
-      <c r="C69" s="49"/>
+      <c r="B69" s="51"/>
+      <c r="C69" s="51"/>
       <c r="D69" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="19"/>
-      <c r="B70" s="49"/>
-      <c r="C70" s="49"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="51"/>
       <c r="D70" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="19"/>
-      <c r="B71" s="49"/>
-      <c r="C71" s="49"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="51"/>
       <c r="D71" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="19"/>
-      <c r="B72" s="49"/>
-      <c r="C72" s="49"/>
+      <c r="B72" s="51"/>
+      <c r="C72" s="51"/>
       <c r="D72" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="19"/>
-      <c r="B73" s="49"/>
-      <c r="C73" s="49"/>
+      <c r="B73" s="51"/>
+      <c r="C73" s="51"/>
       <c r="D73" s="7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="19"/>
-      <c r="B74" s="49"/>
-      <c r="C74" s="49"/>
+      <c r="B74" s="51"/>
+      <c r="C74" s="51"/>
       <c r="D74" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="19"/>
-      <c r="B75" s="49"/>
-      <c r="C75" s="49"/>
+      <c r="B75" s="51"/>
+      <c r="C75" s="51"/>
       <c r="D75" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="19"/>
-      <c r="B76" s="49"/>
-      <c r="C76" s="49"/>
+      <c r="B76" s="51"/>
+      <c r="C76" s="51"/>
       <c r="D76" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="19"/>
-      <c r="B77" s="49"/>
-      <c r="C77" s="49">
+      <c r="B77" s="51"/>
+      <c r="C77" s="51">
         <v>3.3</v>
       </c>
       <c r="D77" s="7" t="s">
@@ -6742,88 +6747,88 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="19"/>
-      <c r="B78" s="49"/>
-      <c r="C78" s="49"/>
+      <c r="B78" s="51"/>
+      <c r="C78" s="51"/>
       <c r="D78" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="19"/>
-      <c r="B79" s="49"/>
-      <c r="C79" s="49"/>
+      <c r="B79" s="51"/>
+      <c r="C79" s="51"/>
       <c r="D79" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="19"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
+      <c r="B80" s="51"/>
+      <c r="C80" s="51"/>
       <c r="D80" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="19"/>
-      <c r="B81" s="49"/>
-      <c r="C81" s="49"/>
+      <c r="B81" s="51"/>
+      <c r="C81" s="51"/>
       <c r="D81" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="19"/>
-      <c r="B82" s="49"/>
-      <c r="C82" s="49"/>
+      <c r="B82" s="51"/>
+      <c r="C82" s="51"/>
       <c r="D82" s="7" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="19"/>
-      <c r="B83" s="49"/>
-      <c r="C83" s="49"/>
+      <c r="B83" s="51"/>
+      <c r="C83" s="51"/>
       <c r="D83" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="19"/>
-      <c r="B84" s="49"/>
-      <c r="C84" s="49"/>
+      <c r="B84" s="51"/>
+      <c r="C84" s="51"/>
       <c r="D84" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="19"/>
-      <c r="B85" s="49"/>
-      <c r="C85" s="49"/>
+      <c r="B85" s="51"/>
+      <c r="C85" s="51"/>
       <c r="D85" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="19"/>
-      <c r="B86" s="49"/>
-      <c r="C86" s="49"/>
+      <c r="B86" s="51"/>
+      <c r="C86" s="51"/>
       <c r="D86" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="19"/>
-      <c r="B87" s="49"/>
-      <c r="C87" s="49"/>
+      <c r="B87" s="51"/>
+      <c r="C87" s="51"/>
       <c r="D87" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="19"/>
-      <c r="B88" s="49"/>
-      <c r="C88" s="49">
+      <c r="B88" s="51"/>
+      <c r="C88" s="51">
         <v>3.4</v>
       </c>
       <c r="D88" s="15" t="s">
@@ -6832,104 +6837,104 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="19"/>
-      <c r="B89" s="49"/>
-      <c r="C89" s="49"/>
+      <c r="B89" s="51"/>
+      <c r="C89" s="51"/>
       <c r="D89" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="19"/>
-      <c r="B90" s="49"/>
-      <c r="C90" s="49"/>
+      <c r="B90" s="51"/>
+      <c r="C90" s="51"/>
       <c r="D90" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="19"/>
-      <c r="B91" s="49"/>
-      <c r="C91" s="49"/>
+      <c r="B91" s="51"/>
+      <c r="C91" s="51"/>
       <c r="D91" s="7" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="19"/>
-      <c r="B92" s="49"/>
-      <c r="C92" s="49"/>
+      <c r="B92" s="51"/>
+      <c r="C92" s="51"/>
       <c r="D92" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="19"/>
-      <c r="B93" s="49"/>
-      <c r="C93" s="49"/>
+      <c r="B93" s="51"/>
+      <c r="C93" s="51"/>
       <c r="D93" s="7" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="19"/>
-      <c r="B94" s="49"/>
-      <c r="C94" s="49"/>
+      <c r="B94" s="51"/>
+      <c r="C94" s="51"/>
       <c r="D94" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="19"/>
-      <c r="B95" s="49"/>
-      <c r="C95" s="49"/>
+      <c r="B95" s="51"/>
+      <c r="C95" s="51"/>
       <c r="D95" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="19"/>
-      <c r="B96" s="49"/>
-      <c r="C96" s="49"/>
+      <c r="B96" s="51"/>
+      <c r="C96" s="51"/>
       <c r="D96" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="19"/>
-      <c r="B97" s="49"/>
-      <c r="C97" s="49"/>
+      <c r="B97" s="51"/>
+      <c r="C97" s="51"/>
       <c r="D97" s="7" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="19"/>
-      <c r="B98" s="49"/>
-      <c r="C98" s="49"/>
+      <c r="B98" s="51"/>
+      <c r="C98" s="51"/>
       <c r="D98" s="7" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="19"/>
-      <c r="B99" s="49"/>
-      <c r="C99" s="49"/>
+      <c r="B99" s="51"/>
+      <c r="C99" s="51"/>
       <c r="D99" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="19"/>
-      <c r="B100" s="49"/>
-      <c r="C100" s="49"/>
+      <c r="B100" s="51"/>
+      <c r="C100" s="51"/>
       <c r="D100" s="7" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="19"/>
-      <c r="B101" s="49"/>
-      <c r="C101" s="49">
+      <c r="B101" s="51"/>
+      <c r="C101" s="51">
         <v>3.5</v>
       </c>
       <c r="D101" s="11" t="s">
@@ -6938,72 +6943,72 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="19"/>
-      <c r="B102" s="49"/>
-      <c r="C102" s="49"/>
+      <c r="B102" s="51"/>
+      <c r="C102" s="51"/>
       <c r="D102" s="7" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="19"/>
-      <c r="B103" s="49"/>
-      <c r="C103" s="49"/>
+      <c r="B103" s="51"/>
+      <c r="C103" s="51"/>
       <c r="D103" s="7" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="19"/>
-      <c r="B104" s="49"/>
-      <c r="C104" s="49"/>
+      <c r="B104" s="51"/>
+      <c r="C104" s="51"/>
       <c r="D104" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="19"/>
-      <c r="B105" s="49"/>
-      <c r="C105" s="49"/>
+      <c r="B105" s="51"/>
+      <c r="C105" s="51"/>
       <c r="D105" s="7" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="19"/>
-      <c r="B106" s="49"/>
-      <c r="C106" s="49"/>
+      <c r="B106" s="51"/>
+      <c r="C106" s="51"/>
       <c r="D106" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="19"/>
-      <c r="B107" s="49"/>
-      <c r="C107" s="49"/>
+      <c r="B107" s="51"/>
+      <c r="C107" s="51"/>
       <c r="D107" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="19"/>
-      <c r="B108" s="49"/>
-      <c r="C108" s="49"/>
+      <c r="B108" s="51"/>
+      <c r="C108" s="51"/>
       <c r="D108" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="19"/>
-      <c r="B109" s="49"/>
-      <c r="C109" s="49"/>
+      <c r="B109" s="51"/>
+      <c r="C109" s="51"/>
       <c r="D109" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="19"/>
-      <c r="B110" s="49"/>
-      <c r="C110" s="49">
+      <c r="B110" s="51"/>
+      <c r="C110" s="51">
         <v>3.6</v>
       </c>
       <c r="D110" s="7" t="s">
@@ -7012,48 +7017,48 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19"/>
-      <c r="B111" s="49"/>
-      <c r="C111" s="49"/>
+      <c r="B111" s="51"/>
+      <c r="C111" s="51"/>
       <c r="D111" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19"/>
-      <c r="B112" s="49"/>
-      <c r="C112" s="49"/>
+      <c r="B112" s="51"/>
+      <c r="C112" s="51"/>
       <c r="D112" s="7" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="19"/>
-      <c r="B113" s="49"/>
-      <c r="C113" s="49"/>
+      <c r="B113" s="51"/>
+      <c r="C113" s="51"/>
       <c r="D113" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="19"/>
-      <c r="B114" s="49"/>
-      <c r="C114" s="49"/>
+      <c r="B114" s="51"/>
+      <c r="C114" s="51"/>
       <c r="D114" s="7" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="19"/>
-      <c r="B115" s="49"/>
-      <c r="C115" s="49"/>
+      <c r="B115" s="51"/>
+      <c r="C115" s="51"/>
       <c r="D115" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="19"/>
-      <c r="B116" s="49"/>
-      <c r="C116" s="49">
+      <c r="B116" s="51"/>
+      <c r="C116" s="51">
         <v>3.7</v>
       </c>
       <c r="D116" s="7" t="s">
@@ -7062,88 +7067,88 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="19"/>
-      <c r="B117" s="49"/>
-      <c r="C117" s="49"/>
+      <c r="B117" s="51"/>
+      <c r="C117" s="51"/>
       <c r="D117" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="19"/>
-      <c r="B118" s="49"/>
-      <c r="C118" s="49"/>
+      <c r="B118" s="51"/>
+      <c r="C118" s="51"/>
       <c r="D118" s="7" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="19"/>
-      <c r="B119" s="49"/>
-      <c r="C119" s="49"/>
+      <c r="B119" s="51"/>
+      <c r="C119" s="51"/>
       <c r="D119" s="7" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="19"/>
-      <c r="B120" s="49"/>
-      <c r="C120" s="49"/>
+      <c r="B120" s="51"/>
+      <c r="C120" s="51"/>
       <c r="D120" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="19"/>
-      <c r="B121" s="49"/>
-      <c r="C121" s="49"/>
+      <c r="B121" s="51"/>
+      <c r="C121" s="51"/>
       <c r="D121" s="7" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="19"/>
-      <c r="B122" s="49"/>
-      <c r="C122" s="49"/>
+      <c r="B122" s="51"/>
+      <c r="C122" s="51"/>
       <c r="D122" s="7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="19"/>
-      <c r="B123" s="49"/>
-      <c r="C123" s="49"/>
+      <c r="B123" s="51"/>
+      <c r="C123" s="51"/>
       <c r="D123" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="19"/>
-      <c r="B124" s="49"/>
-      <c r="C124" s="49"/>
+      <c r="B124" s="51"/>
+      <c r="C124" s="51"/>
       <c r="D124" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="19"/>
-      <c r="B125" s="49"/>
-      <c r="C125" s="49"/>
+      <c r="B125" s="51"/>
+      <c r="C125" s="51"/>
       <c r="D125" s="7" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="19"/>
-      <c r="B126" s="49"/>
-      <c r="C126" s="49"/>
+      <c r="B126" s="51"/>
+      <c r="C126" s="51"/>
       <c r="D126" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="19"/>
-      <c r="B127" s="49"/>
-      <c r="C127" s="49">
+      <c r="B127" s="51"/>
+      <c r="C127" s="51">
         <v>3.8</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -7152,80 +7157,80 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="19"/>
-      <c r="B128" s="49"/>
-      <c r="C128" s="49"/>
+      <c r="B128" s="51"/>
+      <c r="C128" s="51"/>
       <c r="D128" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="19"/>
-      <c r="B129" s="49"/>
-      <c r="C129" s="49"/>
+      <c r="B129" s="51"/>
+      <c r="C129" s="51"/>
       <c r="D129" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="19"/>
-      <c r="B130" s="49"/>
-      <c r="C130" s="49"/>
+      <c r="B130" s="51"/>
+      <c r="C130" s="51"/>
       <c r="D130" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="19"/>
-      <c r="B131" s="49"/>
-      <c r="C131" s="49"/>
+      <c r="B131" s="51"/>
+      <c r="C131" s="51"/>
       <c r="D131" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="19"/>
-      <c r="B132" s="49"/>
-      <c r="C132" s="49"/>
+      <c r="B132" s="51"/>
+      <c r="C132" s="51"/>
       <c r="D132" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="19"/>
-      <c r="B133" s="49"/>
-      <c r="C133" s="49"/>
+      <c r="B133" s="51"/>
+      <c r="C133" s="51"/>
       <c r="D133" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="19"/>
-      <c r="B134" s="49"/>
-      <c r="C134" s="49"/>
+      <c r="B134" s="51"/>
+      <c r="C134" s="51"/>
       <c r="D134" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="19"/>
-      <c r="B135" s="49"/>
-      <c r="C135" s="49"/>
+      <c r="B135" s="51"/>
+      <c r="C135" s="51"/>
       <c r="D135" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="19"/>
-      <c r="B136" s="49"/>
-      <c r="C136" s="49"/>
+      <c r="B136" s="51"/>
+      <c r="C136" s="51"/>
       <c r="D136" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="19"/>
-      <c r="B137" s="49"/>
-      <c r="C137" s="49">
+      <c r="B137" s="51"/>
+      <c r="C137" s="51">
         <v>3.9</v>
       </c>
       <c r="D137" s="7" t="s">
@@ -7234,40 +7239,40 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="19"/>
-      <c r="B138" s="49"/>
-      <c r="C138" s="49"/>
+      <c r="B138" s="51"/>
+      <c r="C138" s="51"/>
       <c r="D138" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="19"/>
-      <c r="B139" s="49"/>
-      <c r="C139" s="49"/>
+      <c r="B139" s="51"/>
+      <c r="C139" s="51"/>
       <c r="D139" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="19"/>
-      <c r="B140" s="49"/>
-      <c r="C140" s="49"/>
+      <c r="B140" s="51"/>
+      <c r="C140" s="51"/>
       <c r="D140" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="19"/>
-      <c r="B141" s="49"/>
-      <c r="C141" s="49"/>
+      <c r="B141" s="51"/>
+      <c r="C141" s="51"/>
       <c r="D141" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
-      <c r="B142" s="49"/>
-      <c r="C142" s="50">
+      <c r="B142" s="51"/>
+      <c r="C142" s="55">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -7276,122 +7281,122 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
-      <c r="B143" s="49"/>
-      <c r="C143" s="50"/>
+      <c r="B143" s="51"/>
+      <c r="C143" s="55"/>
       <c r="D143" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
-      <c r="B144" s="49"/>
-      <c r="C144" s="50"/>
+      <c r="B144" s="51"/>
+      <c r="C144" s="55"/>
       <c r="D144" s="7" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
-      <c r="B145" s="49"/>
-      <c r="C145" s="50"/>
+      <c r="B145" s="51"/>
+      <c r="C145" s="55"/>
       <c r="D145" s="7" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
-      <c r="B146" s="49"/>
-      <c r="C146" s="50"/>
+      <c r="B146" s="51"/>
+      <c r="C146" s="55"/>
       <c r="D146" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
-      <c r="B147" s="49"/>
-      <c r="C147" s="50"/>
+      <c r="B147" s="51"/>
+      <c r="C147" s="55"/>
       <c r="D147" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
-      <c r="B148" s="49"/>
-      <c r="C148" s="50"/>
+      <c r="B148" s="51"/>
+      <c r="C148" s="55"/>
       <c r="D148" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
-      <c r="B149" s="49"/>
-      <c r="C149" s="50"/>
+      <c r="B149" s="51"/>
+      <c r="C149" s="55"/>
       <c r="D149" s="7" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
-      <c r="B150" s="49"/>
-      <c r="C150" s="50"/>
+      <c r="B150" s="51"/>
+      <c r="C150" s="55"/>
       <c r="D150" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
-      <c r="B151" s="49"/>
-      <c r="C151" s="50"/>
+      <c r="B151" s="51"/>
+      <c r="C151" s="55"/>
       <c r="D151" s="7" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
-      <c r="B152" s="49"/>
-      <c r="C152" s="50"/>
+      <c r="B152" s="51"/>
+      <c r="C152" s="55"/>
       <c r="D152" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
-      <c r="B153" s="49"/>
-      <c r="C153" s="50"/>
+      <c r="B153" s="51"/>
+      <c r="C153" s="55"/>
       <c r="D153" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
-      <c r="B154" s="49"/>
-      <c r="C154" s="50"/>
+      <c r="B154" s="51"/>
+      <c r="C154" s="55"/>
       <c r="D154" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
-      <c r="B155" s="49"/>
-      <c r="C155" s="50"/>
+      <c r="B155" s="51"/>
+      <c r="C155" s="55"/>
       <c r="D155" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
-      <c r="B156" s="49"/>
-      <c r="C156" s="50"/>
+      <c r="B156" s="51"/>
+      <c r="C156" s="55"/>
       <c r="D156" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="20"/>
-      <c r="B157" s="49">
+      <c r="B157" s="51">
         <v>4</v>
       </c>
-      <c r="C157" s="49">
+      <c r="C157" s="51">
         <v>4.0999999999999996</v>
       </c>
       <c r="D157" s="7" t="s">
@@ -7400,32 +7405,32 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="19"/>
-      <c r="B158" s="49"/>
-      <c r="C158" s="49"/>
+      <c r="B158" s="51"/>
+      <c r="C158" s="51"/>
       <c r="D158" s="7" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="19"/>
-      <c r="B159" s="49"/>
-      <c r="C159" s="49"/>
+      <c r="B159" s="51"/>
+      <c r="C159" s="51"/>
       <c r="D159" s="7" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="19"/>
-      <c r="B160" s="49"/>
-      <c r="C160" s="49"/>
+      <c r="B160" s="51"/>
+      <c r="C160" s="51"/>
       <c r="D160" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="19"/>
-      <c r="B161" s="49"/>
-      <c r="C161" s="49">
+      <c r="B161" s="51"/>
+      <c r="C161" s="51">
         <v>4.2</v>
       </c>
       <c r="D161" s="7" t="s">
@@ -7434,56 +7439,56 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="19"/>
-      <c r="B162" s="49"/>
-      <c r="C162" s="49"/>
+      <c r="B162" s="51"/>
+      <c r="C162" s="51"/>
       <c r="D162" s="7" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="19"/>
-      <c r="B163" s="49"/>
-      <c r="C163" s="49"/>
+      <c r="B163" s="51"/>
+      <c r="C163" s="51"/>
       <c r="D163" s="7" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="19"/>
-      <c r="B164" s="49"/>
-      <c r="C164" s="49"/>
+      <c r="B164" s="51"/>
+      <c r="C164" s="51"/>
       <c r="D164" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="19"/>
-      <c r="B165" s="49"/>
-      <c r="C165" s="49"/>
+      <c r="B165" s="51"/>
+      <c r="C165" s="51"/>
       <c r="D165" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="19"/>
-      <c r="B166" s="49"/>
-      <c r="C166" s="49"/>
+      <c r="B166" s="51"/>
+      <c r="C166" s="51"/>
       <c r="D166" s="7" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="19"/>
-      <c r="B167" s="49"/>
-      <c r="C167" s="49"/>
+      <c r="B167" s="51"/>
+      <c r="C167" s="51"/>
       <c r="D167" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="19"/>
-      <c r="B168" s="49"/>
-      <c r="C168" s="49">
+      <c r="B168" s="51"/>
+      <c r="C168" s="51">
         <v>4.3</v>
       </c>
       <c r="D168" s="7" t="s">
@@ -7492,48 +7497,48 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="19"/>
-      <c r="B169" s="49"/>
-      <c r="C169" s="49"/>
+      <c r="B169" s="51"/>
+      <c r="C169" s="51"/>
       <c r="D169" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="19"/>
-      <c r="B170" s="49"/>
-      <c r="C170" s="49"/>
+      <c r="B170" s="51"/>
+      <c r="C170" s="51"/>
       <c r="D170" s="7" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="19"/>
-      <c r="B171" s="49"/>
-      <c r="C171" s="49"/>
+      <c r="B171" s="51"/>
+      <c r="C171" s="51"/>
       <c r="D171" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="19"/>
-      <c r="B172" s="49"/>
-      <c r="C172" s="49"/>
+      <c r="B172" s="51"/>
+      <c r="C172" s="51"/>
       <c r="D172" s="7" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="19"/>
-      <c r="B173" s="49"/>
-      <c r="C173" s="49"/>
+      <c r="B173" s="51"/>
+      <c r="C173" s="51"/>
       <c r="D173" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="19"/>
-      <c r="B174" s="49"/>
-      <c r="C174" s="49">
+      <c r="B174" s="51"/>
+      <c r="C174" s="51">
         <v>4.4000000000000004</v>
       </c>
       <c r="D174" s="7" t="s">
@@ -7542,56 +7547,56 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="19"/>
-      <c r="B175" s="49"/>
-      <c r="C175" s="49"/>
+      <c r="B175" s="51"/>
+      <c r="C175" s="51"/>
       <c r="D175" s="7" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="19"/>
-      <c r="B176" s="49"/>
-      <c r="C176" s="49"/>
+      <c r="B176" s="51"/>
+      <c r="C176" s="51"/>
       <c r="D176" s="7" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="19"/>
-      <c r="B177" s="49"/>
-      <c r="C177" s="49"/>
+      <c r="B177" s="51"/>
+      <c r="C177" s="51"/>
       <c r="D177" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="19"/>
-      <c r="B178" s="49"/>
-      <c r="C178" s="49"/>
+      <c r="B178" s="51"/>
+      <c r="C178" s="51"/>
       <c r="D178" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="19"/>
-      <c r="B179" s="49"/>
-      <c r="C179" s="49"/>
+      <c r="B179" s="51"/>
+      <c r="C179" s="51"/>
       <c r="D179" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="19"/>
-      <c r="B180" s="49"/>
-      <c r="C180" s="49"/>
+      <c r="B180" s="51"/>
+      <c r="C180" s="51"/>
       <c r="D180" s="7" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="19"/>
-      <c r="B181" s="49"/>
-      <c r="C181" s="49"/>
+      <c r="B181" s="51"/>
+      <c r="C181" s="51"/>
       <c r="D181" s="7" t="s">
         <v>57</v>
       </c>
@@ -7599,41 +7604,6 @@
   </sheetData>
   <autoFilter ref="A2:J181" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="51">
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -7650,6 +7620,41 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7659,7 +7664,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="15" customWidth="1"/>
@@ -7673,18 +7678,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
     </row>
     <row r="2" spans="1:12" s="4" customFormat="1">
       <c r="A2" s="32" t="s">
@@ -7723,10 +7728,10 @@
       <c r="L2" s="40"/>
     </row>
     <row r="3" spans="1:12" ht="129.6">
-      <c r="A3" s="45">
+      <c r="A3" s="56">
         <v>1</v>
       </c>
-      <c r="B3" s="45">
+      <c r="B3" s="56">
         <v>1</v>
       </c>
       <c r="C3" s="15">
@@ -7750,8 +7755,8 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="57.6">
-      <c r="A4" s="45"/>
-      <c r="B4" s="45"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="56"/>
       <c r="C4" s="15">
         <v>1.2</v>
       </c>
@@ -7773,8 +7778,8 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="43.2">
-      <c r="A5" s="45"/>
-      <c r="B5" s="45"/>
+      <c r="A5" s="56"/>
+      <c r="B5" s="56"/>
       <c r="C5" s="15">
         <v>1.3</v>
       </c>
@@ -7796,8 +7801,8 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="115.2">
-      <c r="A6" s="45"/>
-      <c r="B6" s="45"/>
+      <c r="A6" s="56"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="36">
         <v>1.4</v>
       </c>
@@ -7821,8 +7826,8 @@
       <c r="J6" s="38"/>
     </row>
     <row r="7" spans="1:12" ht="72">
-      <c r="A7" s="45"/>
-      <c r="B7" s="45">
+      <c r="A7" s="56"/>
+      <c r="B7" s="56">
         <v>2</v>
       </c>
       <c r="C7" s="15">
@@ -7846,8 +7851,8 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="57.6">
-      <c r="A8" s="45"/>
-      <c r="B8" s="45"/>
+      <c r="A8" s="56"/>
+      <c r="B8" s="56"/>
       <c r="C8" s="15">
         <v>2.2000000000000002</v>
       </c>
@@ -7869,8 +7874,8 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="100.8">
-      <c r="A9" s="45"/>
-      <c r="B9" s="45"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="56"/>
       <c r="C9" s="15">
         <v>2.2999999999999998</v>
       </c>
@@ -7892,8 +7897,8 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="115.2">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="56"/>
       <c r="C10" s="15">
         <v>2.4</v>
       </c>
@@ -7915,8 +7920,8 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="100.8">
-      <c r="A11" s="45"/>
-      <c r="B11" s="45"/>
+      <c r="A11" s="56"/>
+      <c r="B11" s="56"/>
       <c r="C11" s="15">
         <v>2.5</v>
       </c>
@@ -7938,8 +7943,8 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="115.2">
-      <c r="A12" s="45"/>
-      <c r="B12" s="45"/>
+      <c r="A12" s="56"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="15">
         <v>2.6</v>
       </c>
@@ -7961,8 +7966,8 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="158.4">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="56"/>
       <c r="C13" s="36">
         <v>2.7</v>
       </c>
@@ -8156,7 +8161,7 @@
       <c r="A23" s="15">
         <v>2</v>
       </c>
-      <c r="B23" s="47">
+      <c r="B23" s="57">
         <v>3</v>
       </c>
       <c r="C23" s="15">
@@ -8172,12 +8177,9 @@
         <f t="array" ref="F23">_xlfn.SWITCH(E23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="G23" t="s">
-        <v>241</v>
-      </c>
     </row>
     <row r="24" spans="1:10" ht="86.4">
-      <c r="B24" s="45"/>
+      <c r="B24" s="56"/>
       <c r="C24" s="15">
         <v>3.2</v>
       </c>
@@ -8196,7 +8198,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="86.4">
-      <c r="B25" s="45"/>
+      <c r="B25" s="56"/>
       <c r="C25" s="15">
         <v>3.3</v>
       </c>
@@ -8215,7 +8217,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="158.4">
-      <c r="B26" s="45"/>
+      <c r="B26" s="56"/>
       <c r="C26" s="15">
         <v>3.4</v>
       </c>
@@ -8234,7 +8236,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="72">
-      <c r="B27" s="45"/>
+      <c r="B27" s="56"/>
       <c r="C27" s="15">
         <v>3.5</v>
       </c>
@@ -8253,7 +8255,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="115.2">
-      <c r="B28" s="45"/>
+      <c r="B28" s="56"/>
       <c r="C28" s="15">
         <v>3.6</v>
       </c>
@@ -8272,7 +8274,7 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="B29" s="45"/>
+      <c r="B29" s="56"/>
       <c r="C29" s="15">
         <v>3.7</v>
       </c>
@@ -8291,7 +8293,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="86.4">
-      <c r="B30" s="45"/>
+      <c r="B30" s="56"/>
       <c r="C30" s="15">
         <v>3.8</v>
       </c>
@@ -8310,7 +8312,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="144">
-      <c r="B31" s="45"/>
+      <c r="B31" s="56"/>
       <c r="C31" s="15">
         <v>3.9</v>
       </c>
@@ -8329,7 +8331,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="144">
-      <c r="B32" s="45"/>
+      <c r="B32" s="56"/>
       <c r="C32" s="35">
         <v>3.1</v>
       </c>
@@ -8343,12 +8345,9 @@
         <f t="array" ref="F32">_xlfn.SWITCH(E32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="G32" t="s">
-        <v>241</v>
-      </c>
     </row>
     <row r="33" spans="2:7" ht="72">
-      <c r="B33" s="45"/>
+      <c r="B33" s="56"/>
       <c r="C33" s="15">
         <v>3.11</v>
       </c>
@@ -8366,13 +8365,13 @@
         <v>240</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="216">
-      <c r="B34" s="45"/>
-      <c r="C34" s="35">
+    <row r="34" spans="2:7">
+      <c r="B34" s="56"/>
+      <c r="C34" s="15">
         <v>3.12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>237</v>
+        <v>288</v>
       </c>
       <c r="E34" t="s">
         <v>20</v>
@@ -8381,38 +8380,30 @@
         <f t="array" ref="F34">_xlfn.SWITCH(E34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="G34" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" ht="57.6">
-      <c r="B35" s="45">
-        <v>4</v>
-      </c>
+    </row>
+    <row r="35" spans="2:7" ht="28.8">
+      <c r="B35" s="56"/>
       <c r="C35" s="15">
-        <v>4.0999999999999996</v>
+        <v>3.13</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>238</v>
+        <v>290</v>
       </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F35" cm="1">
         <f t="array" ref="F35">_xlfn.SWITCH(E35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="G35" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" ht="86.4">
-      <c r="B36" s="45"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="28.8">
+      <c r="B36" s="56"/>
       <c r="C36" s="15">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
@@ -8421,62 +8412,115 @@
         <f t="array" ref="F36">_xlfn.SWITCH(E36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="G36" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" ht="72">
-      <c r="B37" s="45"/>
-      <c r="C37" s="15">
-        <v>4.3</v>
+    </row>
+    <row r="37" spans="2:7" ht="216">
+      <c r="B37" s="56"/>
+      <c r="C37" s="35">
+        <v>3.15</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>278</v>
+        <v>237</v>
       </c>
       <c r="E37" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F37" cm="1">
         <f t="array" ref="F37">_xlfn.SWITCH(E37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G37" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" ht="115.2">
-      <c r="B38" s="45"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="57.6">
+      <c r="B38" s="56">
+        <v>4</v>
+      </c>
       <c r="C38" s="15">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E38" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F38" cm="1">
         <f t="array" ref="F38">_xlfn.SWITCH(E38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G38" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="86.4">
+      <c r="B39" s="56"/>
+      <c r="C39" s="15">
+        <v>4.2</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" cm="1">
+        <f t="array" ref="F39">_xlfn.SWITCH(E39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="G39" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="72">
+      <c r="B40" s="56"/>
+      <c r="C40" s="15">
+        <v>4.3</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" cm="1">
+        <f t="array" ref="F40">_xlfn.SWITCH(E40,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="115.2">
+      <c r="B41" s="56"/>
+      <c r="C41" s="15">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41" cm="1">
+        <f t="array" ref="F41">_xlfn.SWITCH(E41,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="G38" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7">
-      <c r="F39">
-        <f>SUM(F16:F38)</f>
-        <v>111</v>
+      <c r="G41" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7">
+      <c r="F42">
+        <f>SUM(F22:F41)</f>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B38:B41"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="B7:B13"/>
-    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="B23:B37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8726,7 +8770,7 @@
       <c r="B2" s="26">
         <v>46286</v>
       </c>
-      <c r="C2" s="58">
+      <c r="C2" s="46">
         <v>50</v>
       </c>
       <c r="D2" s="27">
@@ -8749,7 +8793,7 @@
         <f>50-SUM($E$2:E3)</f>
         <v>47</v>
       </c>
-      <c r="D3" s="57">
+      <c r="D3" s="45">
         <f>('Updated Sprint'!F21)*(1-(A3-1)/18)</f>
         <v>47.222222222222221</v>
       </c>
@@ -8768,7 +8812,7 @@
         <f>50-SUM($E$2:E4)</f>
         <v>43</v>
       </c>
-      <c r="D4" s="57">
+      <c r="D4" s="45">
         <f>('Updated Sprint'!F21)*(1-(A4-1)/18)</f>
         <v>44.444444444444443</v>
       </c>
@@ -8787,7 +8831,7 @@
         <f>50-SUM($E$2:E5)</f>
         <v>41</v>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="45">
         <f>('Updated Sprint'!F21)*(1-(A5-1)/18)</f>
         <v>41.666666666666671</v>
       </c>
@@ -8806,7 +8850,7 @@
         <f>50-SUM($E$2:E6)</f>
         <v>36</v>
       </c>
-      <c r="D6" s="57">
+      <c r="D6" s="45">
         <f>('Updated Sprint'!F21)*(1-(A6-1)/18)</f>
         <v>38.888888888888893</v>
       </c>
@@ -8825,7 +8869,7 @@
         <f>50-SUM($E$2:E7)</f>
         <v>36</v>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="45">
         <f>('Updated Sprint'!F21)*(1-(A7-1)/18)</f>
         <v>36.111111111111107</v>
       </c>
@@ -8844,7 +8888,7 @@
         <f>50-SUM($E$2:E8)</f>
         <v>36</v>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="45">
         <f>('Updated Sprint'!F21)*(1-(A8-1)/18)</f>
         <v>33.333333333333336</v>
       </c>
@@ -8863,7 +8907,7 @@
         <f>50-SUM($E$2:E9)</f>
         <v>32</v>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="45">
         <f>('Updated Sprint'!F21)*(1-(A9-1)/18)</f>
         <v>30.555555555555557</v>
       </c>
@@ -8882,7 +8926,7 @@
         <f>50-SUM($E$2:E10)</f>
         <v>28</v>
       </c>
-      <c r="D10" s="57">
+      <c r="D10" s="45">
         <f>('Updated Sprint'!F21)*(1-(A10-1)/18)</f>
         <v>27.777777777777779</v>
       </c>
@@ -8892,7 +8936,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="25" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B11" s="26">
         <v>46295</v>
@@ -8901,7 +8945,7 @@
         <f>50-SUM($E$2:E11)</f>
         <v>28</v>
       </c>
-      <c r="D11" s="57">
+      <c r="D11" s="45">
         <f>('Updated Sprint'!F21)*(1-(A11-1)/18)</f>
         <v>25</v>
       </c>
@@ -8911,7 +8955,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="25" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B12" s="26">
         <v>46296</v>
@@ -8920,7 +8964,7 @@
         <f>50-SUM($E$2:E12)</f>
         <v>26</v>
       </c>
-      <c r="D12" s="57">
+      <c r="D12" s="45">
         <f>('Updated Sprint'!F21)*(1-(A12-1)/18)</f>
         <v>22.222222222222221</v>
       </c>
@@ -8930,7 +8974,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="25" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B13" s="26">
         <v>46297</v>
@@ -8939,7 +8983,7 @@
         <f>50-SUM($E$2:E13)</f>
         <v>21</v>
       </c>
-      <c r="D13" s="57">
+      <c r="D13" s="45">
         <f>('Updated Sprint'!F21)*(1-(A13-1)/18)</f>
         <v>19.444444444444443</v>
       </c>
@@ -8949,7 +8993,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="25" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B14" s="26">
         <v>46298</v>
@@ -8958,7 +9002,7 @@
         <f>50-SUM($E$2:E14)</f>
         <v>21</v>
       </c>
-      <c r="D14" s="57">
+      <c r="D14" s="45">
         <f>('Updated Sprint'!F21)*(1-(A14-1)/18)</f>
         <v>16.666666666666668</v>
       </c>
@@ -8968,7 +9012,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="25" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B15" s="26">
         <v>46299</v>
@@ -8977,7 +9021,7 @@
         <f>50-SUM($E$2:E15)</f>
         <v>21</v>
       </c>
-      <c r="D15" s="57">
+      <c r="D15" s="45">
         <f>('Updated Sprint'!F21)*(1-(A15-1)/18)</f>
         <v>13.888888888888889</v>
       </c>
@@ -8987,7 +9031,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="25" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B16" s="26">
         <v>46300</v>
@@ -8996,7 +9040,7 @@
         <f>50-SUM($E$2:E16)</f>
         <v>17</v>
       </c>
-      <c r="D16" s="57">
+      <c r="D16" s="45">
         <f>('Updated Sprint'!F21)*(1-(A16-1)/18)</f>
         <v>11.111111111111111</v>
       </c>
@@ -9006,7 +9050,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B17" s="26">
         <v>46301</v>
@@ -9015,7 +9059,7 @@
         <f>50-SUM($E$2:E17)</f>
         <v>15</v>
       </c>
-      <c r="D17" s="57">
+      <c r="D17" s="45">
         <f>('Updated Sprint'!F21)*(1-(A17-1)/18)</f>
         <v>8.3333333333333321</v>
       </c>
@@ -9025,7 +9069,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="25" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B18" s="26">
         <v>46302</v>
@@ -9034,7 +9078,7 @@
         <f>50-SUM($E$2:E18)</f>
         <v>12</v>
       </c>
-      <c r="D18" s="57">
+      <c r="D18" s="45">
         <f>('Updated Sprint'!F21)*(1-(A18-1)/18)</f>
         <v>5.555555555555558</v>
       </c>
@@ -9044,7 +9088,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="25" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B19" s="26">
         <v>46303</v>
@@ -9053,7 +9097,7 @@
         <f>50-SUM($E$2:E19)</f>
         <v>7</v>
       </c>
-      <c r="D19" s="57">
+      <c r="D19" s="45">
         <f>('Updated Sprint'!F21)*(1-(A19-1)/18)</f>
         <v>2.777777777777779</v>
       </c>
@@ -9063,7 +9107,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="25" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B20" s="26">
         <v>46304</v>
@@ -9072,7 +9116,7 @@
         <f>50-SUM($E$2:E20)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="57">
+      <c r="D20" s="45">
         <f>('Updated Sprint'!F21)*(1-(A20-1)/18)</f>
         <v>0</v>
       </c>
@@ -9093,15 +9137,15 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="12" t="s">
